--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1570,16 +1570,16 @@
         <v>1801.204957885742</v>
       </c>
       <c r="G15" t="n">
-        <v>9.652882156612709</v>
+        <v>9.652882115869321</v>
       </c>
       <c r="H15" t="n">
         <v>2983.800048828125</v>
       </c>
       <c r="I15" t="n">
-        <v>1158.746695475609</v>
+        <v>1158.746573666689</v>
       </c>
       <c r="J15" t="n">
-        <v>142.5551769537203</v>
+        <v>142.5552024514304</v>
       </c>
       <c r="K15" t="n">
         <v>6.16238330441623</v>
@@ -1801,16 +1801,16 @@
         <v>1239.957984008789</v>
       </c>
       <c r="G18" t="n">
-        <v>8.648265126740572</v>
+        <v>8.648265213899119</v>
       </c>
       <c r="H18" t="n">
         <v>1898.300048828125</v>
       </c>
       <c r="I18" t="n">
-        <v>821.6033372206257</v>
+        <v>821.6033975811163</v>
       </c>
       <c r="J18" t="n">
-        <v>129.672874307384</v>
+        <v>129.6728574340758</v>
       </c>
       <c r="K18" t="n">
         <v>0.5988367158518804</v>
@@ -2103,13 +2103,13 @@
         <v>1198.9743359375</v>
       </c>
       <c r="E22" t="n">
-        <v>1037.196638997396</v>
+        <v>1037.196638590495</v>
       </c>
       <c r="F22" t="n">
-        <v>994.0775122070313</v>
+        <v>994.0775115966796</v>
       </c>
       <c r="G22" t="n">
-        <v>6.050200651556503</v>
+        <v>6.050200759075541</v>
       </c>
       <c r="H22" t="n">
         <v>1489.699951171875</v>
@@ -2565,13 +2565,13 @@
         <v>299.7897357177735</v>
       </c>
       <c r="E28" t="n">
-        <v>232.2009245808919</v>
+        <v>232.2009246826172</v>
       </c>
       <c r="F28" t="n">
-        <v>224.6525311279297</v>
+        <v>224.6525308990479</v>
       </c>
       <c r="G28" t="n">
-        <v>5.285127998721117</v>
+        <v>5.285128004390338</v>
       </c>
       <c r="H28" t="n">
         <v>376.5</v>
@@ -4185,19 +4185,19 @@
         <v>1747.982188313802</v>
       </c>
       <c r="F49" t="n">
-        <v>1711.569837646484</v>
+        <v>1711.569838256836</v>
       </c>
       <c r="G49" t="n">
-        <v>6.718870732389504</v>
+        <v>6.718870648606035</v>
       </c>
       <c r="H49" t="n">
         <v>2539.60009765625</v>
       </c>
       <c r="I49" t="n">
-        <v>1167.643304709368</v>
+        <v>1167.643424163666</v>
       </c>
       <c r="J49" t="n">
-        <v>96.08728867983727</v>
+        <v>96.08726861937282</v>
       </c>
       <c r="K49" t="n">
         <v>10.91893734001463</v>
@@ -5035,7 +5035,7 @@
         <v>8716.929860839844</v>
       </c>
       <c r="G60" t="n">
-        <v>4.343010214733778</v>
+        <v>4.343009848815216</v>
       </c>
       <c r="H60" t="n">
         <v>12060</v>
@@ -5497,7 +5497,7 @@
         <v>980.3681820678711</v>
       </c>
       <c r="G66" t="n">
-        <v>4.598714668690418</v>
+        <v>4.598714600575282</v>
       </c>
       <c r="H66" t="n">
         <v>1153.699951171875</v>
@@ -6113,7 +6113,7 @@
         <v>71.20183200836182</v>
       </c>
       <c r="G74" t="n">
-        <v>3.771192117917788</v>
+        <v>3.771192002531953</v>
       </c>
       <c r="H74" t="n">
         <v>94.5</v>
@@ -6726,10 +6726,10 @@
         <v>6636.553427734375</v>
       </c>
       <c r="F82" t="n">
-        <v>6234.196579589844</v>
+        <v>6234.196577148437</v>
       </c>
       <c r="G82" t="n">
-        <v>4.445433891286088</v>
+        <v>4.445433935825083</v>
       </c>
       <c r="H82" t="n">
         <v>7832.294844565128</v>
@@ -8808,7 +8808,7 @@
         <v>303.2552906799316</v>
       </c>
       <c r="G109" t="n">
-        <v>3.009378764315329</v>
+        <v>3.009378604143387</v>
       </c>
       <c r="H109" t="n">
         <v>380.4567148307952</v>
@@ -9723,25 +9723,25 @@
         <v>1937.300048828125</v>
       </c>
       <c r="D121" t="n">
-        <v>1780.932275390625</v>
+        <v>1780.932280273438</v>
       </c>
       <c r="E121" t="n">
         <v>1561.728019205729</v>
       </c>
       <c r="F121" t="n">
-        <v>1537.917697143555</v>
+        <v>1537.917707519531</v>
       </c>
       <c r="G121" t="n">
-        <v>2.635917386416642</v>
+        <v>2.63591732635724</v>
       </c>
       <c r="H121" t="n">
         <v>1988.900024414062</v>
       </c>
       <c r="I121" t="n">
-        <v>1266.16157090969</v>
+        <v>1266.161452106784</v>
       </c>
       <c r="J121" t="n">
-        <v>53.00575324176415</v>
+        <v>53.00576759817033</v>
       </c>
       <c r="K121" t="n">
         <v>2.663499421122206</v>
@@ -11112,13 +11112,13 @@
         <v>362.1056860351562</v>
       </c>
       <c r="E139" t="n">
-        <v>380.0789654541015</v>
+        <v>380.0789656575521</v>
       </c>
       <c r="F139" t="n">
-        <v>357.1276152801514</v>
+        <v>357.1276156616211</v>
       </c>
       <c r="G139" t="n">
-        <v>5.044393303527306</v>
+        <v>5.044393368585887</v>
       </c>
       <c r="H139" t="n">
         <v>443.3731066930094</v>
@@ -11805,13 +11805,13 @@
         <v>2127.470229492188</v>
       </c>
       <c r="E148" t="n">
-        <v>1904.141841634115</v>
+        <v>1904.141842447917</v>
       </c>
       <c r="F148" t="n">
-        <v>1783.215220947266</v>
+        <v>1783.215223999023</v>
       </c>
       <c r="G148" t="n">
-        <v>5.558396514969832</v>
+        <v>5.558396504928553</v>
       </c>
       <c r="H148" t="n">
         <v>2295</v>
@@ -13656,10 +13656,10 @@
         <v>1107.88543741862</v>
       </c>
       <c r="F172" t="n">
-        <v>1085.749305114746</v>
+        <v>1085.74930480957</v>
       </c>
       <c r="G172" t="n">
-        <v>1.961950805588186</v>
+        <v>1.961950981477156</v>
       </c>
       <c r="H172" t="n">
         <v>1596.696405272527</v>
@@ -14115,13 +14115,13 @@
         <v>1115.377805175781</v>
       </c>
       <c r="E178" t="n">
-        <v>971.9282767740885</v>
+        <v>971.9282771809895</v>
       </c>
       <c r="F178" t="n">
-        <v>940.9790393066406</v>
+        <v>940.9790383911132</v>
       </c>
       <c r="G178" t="n">
-        <v>2.418691411940999</v>
+        <v>2.418691312292531</v>
       </c>
       <c r="H178" t="n">
         <v>1303.791320684363</v>
@@ -14198,7 +14198,7 @@
         <v>168.2965731811524</v>
       </c>
       <c r="G179" t="n">
-        <v>2.47714464545068</v>
+        <v>2.477144883484583</v>
       </c>
       <c r="H179" t="n">
         <v>211.8067938496122</v>
@@ -14660,7 +14660,7 @@
         <v>1510.479366455078</v>
       </c>
       <c r="G185" t="n">
-        <v>0.4036666390880406</v>
+        <v>0.403666557618676</v>
       </c>
       <c r="H185" t="n">
         <v>1975.809187899259</v>
@@ -16277,7 +16277,7 @@
         <v>503.8814953613281</v>
       </c>
       <c r="G206" t="n">
-        <v>1.750542694834678</v>
+        <v>1.750542726186688</v>
       </c>
       <c r="H206" t="n">
         <v>609.0499877929688</v>
@@ -16348,13 +16348,13 @@
         <v>397.6540063476563</v>
       </c>
       <c r="E207" t="n">
-        <v>397.5328778076172</v>
+        <v>397.5328776041667</v>
       </c>
       <c r="F207" t="n">
-        <v>395.8611708068848</v>
+        <v>395.861170501709</v>
       </c>
       <c r="G207" t="n">
-        <v>0.2578665501538513</v>
+        <v>0.2578668215671653</v>
       </c>
       <c r="H207" t="n">
         <v>490.7000122070312</v>
@@ -18119,16 +18119,16 @@
         <v>166.1548626708984</v>
       </c>
       <c r="E230" t="n">
-        <v>147.3812511698405</v>
+        <v>147.3812510681152</v>
       </c>
       <c r="F230" t="n">
-        <v>151.3245009994507</v>
+        <v>151.3245006942749</v>
       </c>
       <c r="G230" t="n">
-        <v>-0.3070329899123481</v>
+        <v>-0.3070331408546179</v>
       </c>
       <c r="H230" t="n">
-        <v>209.3573902779376</v>
+        <v>209.3574059154358</v>
       </c>
       <c r="I230" t="n">
         <v>115.0300392216107</v>
@@ -18137,7 +18137,7 @@
         <v>48.67421190997161</v>
       </c>
       <c r="K230" t="n">
-        <v>22.41690155988967</v>
+        <v>22.41691070355578</v>
       </c>
       <c r="L230" t="n">
         <v>70.93184979137691</v>
@@ -18196,22 +18196,22 @@
         <v>826.1882055664063</v>
       </c>
       <c r="E231" t="n">
-        <v>710.6685388183594</v>
+        <v>710.6685384114584</v>
       </c>
       <c r="F231" t="n">
-        <v>664.9467436218262</v>
+        <v>664.9467443847657</v>
       </c>
       <c r="G231" t="n">
-        <v>2.896142609882824</v>
+        <v>2.896142606463648</v>
       </c>
       <c r="H231" t="n">
         <v>1093.53919041171</v>
       </c>
       <c r="I231" t="n">
-        <v>491.2850813456647</v>
+        <v>491.2850236715819</v>
       </c>
       <c r="J231" t="n">
-        <v>48.30492584677118</v>
+        <v>48.30494325693058</v>
       </c>
       <c r="K231" t="n">
         <v>50.08773360612453</v>
@@ -18504,13 +18504,13 @@
         <v>1459.055649414063</v>
       </c>
       <c r="E235" t="n">
-        <v>1368.145655110677</v>
+        <v>1368.145654296875</v>
       </c>
       <c r="F235" t="n">
-        <v>1340.567661743164</v>
+        <v>1340.567659301758</v>
       </c>
       <c r="G235" t="n">
-        <v>2.160590385501893</v>
+        <v>2.160590437039733</v>
       </c>
       <c r="H235" t="n">
         <v>1553</v>
@@ -18889,13 +18889,13 @@
         <v>1833.216862792969</v>
       </c>
       <c r="E240" t="n">
-        <v>1663.103330891927</v>
+        <v>1663.103330078125</v>
       </c>
       <c r="F240" t="n">
-        <v>1664.417301635742</v>
+        <v>1664.417303466797</v>
       </c>
       <c r="G240" t="n">
-        <v>1.04246747014578</v>
+        <v>1.042467468986996</v>
       </c>
       <c r="H240" t="n">
         <v>1983.954544928268</v>
@@ -19043,13 +19043,13 @@
         <v>1445.979838867187</v>
       </c>
       <c r="E242" t="n">
-        <v>1354.808014322917</v>
+        <v>1354.808015136719</v>
       </c>
       <c r="F242" t="n">
-        <v>1364.172682495117</v>
+        <v>1364.172680664062</v>
       </c>
       <c r="G242" t="n">
-        <v>1.428824557462427</v>
+        <v>1.428824697495279</v>
       </c>
       <c r="H242" t="n">
         <v>1563.400024414062</v>
@@ -19431,10 +19431,10 @@
         <v>292.6972496541341</v>
       </c>
       <c r="F247" t="n">
-        <v>282.9097332000732</v>
+        <v>282.9097328186035</v>
       </c>
       <c r="G247" t="n">
-        <v>2.060855995132949</v>
+        <v>2.060855969878461</v>
       </c>
       <c r="H247" t="n">
         <v>359.3387168134344</v>
@@ -19588,7 +19588,7 @@
         <v>590.2835250854492</v>
       </c>
       <c r="G249" t="n">
-        <v>2.784269652263016</v>
+        <v>2.784269788810212</v>
       </c>
       <c r="H249" t="n">
         <v>741</v>
@@ -19659,13 +19659,13 @@
         <v>8779.1715625</v>
       </c>
       <c r="E250" t="n">
-        <v>8054.947034505209</v>
+        <v>8054.947037760417</v>
       </c>
       <c r="F250" t="n">
-        <v>7841.080227050781</v>
+        <v>7841.080219726562</v>
       </c>
       <c r="G250" t="n">
-        <v>1.503699330861696</v>
+        <v>1.503699300207884</v>
       </c>
       <c r="H250" t="n">
         <v>9039.4765625</v>
@@ -20204,7 +20204,7 @@
         <v>1105.473973083496</v>
       </c>
       <c r="G257" t="n">
-        <v>0.5714569564903238</v>
+        <v>0.5714570123348972</v>
       </c>
       <c r="H257" t="n">
         <v>1229.065274432971</v>
@@ -21051,7 +21051,7 @@
         <v>277.2046047973633</v>
       </c>
       <c r="G268" t="n">
-        <v>0.5495905491399888</v>
+        <v>0.5495906604438439</v>
       </c>
       <c r="H268" t="n">
         <v>322.6775170144611</v>
@@ -21353,13 +21353,13 @@
         <v>1179.596005859375</v>
       </c>
       <c r="E272" t="n">
-        <v>1138.970662027995</v>
+        <v>1138.970665283203</v>
       </c>
       <c r="F272" t="n">
-        <v>1170.641242370605</v>
+        <v>1170.641246032715</v>
       </c>
       <c r="G272" t="n">
-        <v>0.1236292125237126</v>
+        <v>0.1236291598692763</v>
       </c>
       <c r="H272" t="n">
         <v>1378.852549646065</v>
@@ -21584,22 +21584,22 @@
         <v>346.9813970947266</v>
       </c>
       <c r="E275" t="n">
-        <v>339.9652062988282</v>
+        <v>339.965205485026</v>
       </c>
       <c r="F275" t="n">
-        <v>334.8838290405274</v>
+        <v>334.8838279724121</v>
       </c>
       <c r="G275" t="n">
-        <v>0.2729517528608838</v>
+        <v>0.2729516162933265</v>
       </c>
       <c r="H275" t="n">
         <v>386.0870554430863</v>
       </c>
       <c r="I275" t="n">
-        <v>282.670901059285</v>
+        <v>282.6708709611926</v>
       </c>
       <c r="J275" t="n">
-        <v>23.05830023535407</v>
+        <v>23.05831333829631</v>
       </c>
       <c r="K275" t="n">
         <v>10.99239576502749</v>
@@ -23047,13 +23047,13 @@
         <v>1188.550494384766</v>
       </c>
       <c r="E294" t="n">
-        <v>1084.131554361979</v>
+        <v>1084.131553548177</v>
       </c>
       <c r="F294" t="n">
-        <v>1147.905987548828</v>
+        <v>1147.90598449707</v>
       </c>
       <c r="G294" t="n">
-        <v>-0.3527621755705423</v>
+        <v>-0.3527623348942632</v>
       </c>
       <c r="H294" t="n">
         <v>1423.547927723126</v>
@@ -23509,13 +23509,13 @@
         <v>5205.38755859375</v>
       </c>
       <c r="E300" t="n">
-        <v>5185.605367838541</v>
+        <v>5185.605358072917</v>
       </c>
       <c r="F300" t="n">
-        <v>5309.102822265625</v>
+        <v>5309.102810058594</v>
       </c>
       <c r="G300" t="n">
-        <v>0.6065045342490638</v>
+        <v>0.6065045356520526</v>
       </c>
       <c r="H300" t="n">
         <v>6175.521739453033</v>
@@ -24510,16 +24510,16 @@
         <v>1816.721994628906</v>
       </c>
       <c r="E313" t="n">
-        <v>1745.420701497396</v>
+        <v>1745.42069905599</v>
       </c>
       <c r="F313" t="n">
-        <v>1763.262103881836</v>
+        <v>1763.262099609375</v>
       </c>
       <c r="G313" t="n">
-        <v>-1.894905053416374</v>
+        <v>-1.894905024605309</v>
       </c>
       <c r="H313" t="n">
-        <v>2269.472253037084</v>
+        <v>2269.472002658311</v>
       </c>
       <c r="I313" t="n">
         <v>1353.205955540699</v>
@@ -24528,7 +24528,7 @@
         <v>43.19327691678914</v>
       </c>
       <c r="K313" t="n">
-        <v>17.12196471205776</v>
+        <v>17.12195179061591</v>
       </c>
       <c r="L313" t="n">
         <v>54.65924895688457</v>
@@ -25126,16 +25126,16 @@
         <v>5172.117373046875</v>
       </c>
       <c r="E321" t="n">
-        <v>5156.606422526042</v>
+        <v>5156.60642578125</v>
       </c>
       <c r="F321" t="n">
-        <v>5434.156357421875</v>
+        <v>5434.156352539063</v>
       </c>
       <c r="G321" t="n">
-        <v>-0.2967424983631894</v>
+        <v>-0.2967423199857766</v>
       </c>
       <c r="H321" t="n">
-        <v>6552.654210942315</v>
+        <v>6552.654707500795</v>
       </c>
       <c r="I321" t="n">
         <v>4229.809203861739</v>
@@ -25144,7 +25144,7 @@
         <v>32.16908211594924</v>
       </c>
       <c r="K321" t="n">
-        <v>17.21052161599705</v>
+        <v>17.21053049818075</v>
       </c>
       <c r="L321" t="n">
         <v>51.7385257301808</v>
@@ -25203,16 +25203,16 @@
         <v>2459.68123046875</v>
       </c>
       <c r="E322" t="n">
-        <v>2441.833020833333</v>
+        <v>2441.833017578125</v>
       </c>
       <c r="F322" t="n">
-        <v>2468.973774414063</v>
+        <v>2468.973767089844</v>
       </c>
       <c r="G322" t="n">
-        <v>-1.195135493228328</v>
+        <v>-1.195135689799276</v>
       </c>
       <c r="H322" t="n">
-        <v>3039.742679715149</v>
+        <v>3039.742428602358</v>
       </c>
       <c r="I322" t="n">
         <v>2053.692522278021</v>
@@ -25221,7 +25221,7 @@
         <v>27.81854983277958</v>
       </c>
       <c r="K322" t="n">
-        <v>15.79972113200567</v>
+        <v>15.79971156580413</v>
       </c>
       <c r="L322" t="n">
         <v>51.18219749652295</v>
@@ -27282,13 +27282,13 @@
         <v>2919.426958007813</v>
       </c>
       <c r="E349" t="n">
-        <v>2804.024073893229</v>
+        <v>2804.024077148437</v>
       </c>
       <c r="F349" t="n">
-        <v>2771.869204101562</v>
+        <v>2771.869201660156</v>
       </c>
       <c r="G349" t="n">
-        <v>-1.114427602535839</v>
+        <v>-1.114427732695122</v>
       </c>
       <c r="H349" t="n">
         <v>3415.14446256242</v>
@@ -27513,16 +27513,16 @@
         <v>1113.923071289063</v>
       </c>
       <c r="E352" t="n">
-        <v>1081.579396972656</v>
+        <v>1081.579394938151</v>
       </c>
       <c r="F352" t="n">
-        <v>1090.869985351562</v>
+        <v>1090.869985656738</v>
       </c>
       <c r="G352" t="n">
-        <v>-1.424423261181307</v>
+        <v>-1.424423260788488</v>
       </c>
       <c r="H352" t="n">
-        <v>1341.921323996723</v>
+        <v>1341.921447537333</v>
       </c>
       <c r="I352" t="n">
         <v>885.652283987356</v>
@@ -27531,7 +27531,7 @@
         <v>25.92978858552208</v>
       </c>
       <c r="K352" t="n">
-        <v>20.31931007325925</v>
+        <v>20.31932115015371</v>
       </c>
       <c r="L352" t="n">
         <v>31.29346314325452</v>
@@ -27590,13 +27590,13 @@
         <v>1377.746071777344</v>
       </c>
       <c r="E353" t="n">
-        <v>1385.084869791667</v>
+        <v>1385.084868977865</v>
       </c>
       <c r="F353" t="n">
-        <v>1308.615979614258</v>
+        <v>1308.615982055664</v>
       </c>
       <c r="G353" t="n">
-        <v>2.678304621223626</v>
+        <v>2.678304566920198</v>
       </c>
       <c r="H353" t="n">
         <v>1766.733188761222</v>
@@ -29284,16 +29284,16 @@
         <v>494.8478070068359</v>
       </c>
       <c r="E375" t="n">
-        <v>487.8859452311198</v>
+        <v>487.8859454345703</v>
       </c>
       <c r="F375" t="n">
-        <v>493.1022909545898</v>
+        <v>493.1022923278808</v>
       </c>
       <c r="G375" t="n">
-        <v>-0.2221362812713346</v>
+        <v>-0.2221365271112052</v>
       </c>
       <c r="H375" t="n">
-        <v>561.4379586860567</v>
+        <v>561.4378970396333</v>
       </c>
       <c r="I375" t="n">
         <v>420.1655789001589</v>
@@ -29302,7 +29302,7 @@
         <v>23.04672870950506</v>
       </c>
       <c r="K375" t="n">
-        <v>8.595349842564159</v>
+        <v>8.595337918691159</v>
       </c>
       <c r="L375" t="n">
         <v>48.12239221140473</v>
@@ -29367,7 +29367,7 @@
         <v>672.9854289245606</v>
       </c>
       <c r="G376" t="n">
-        <v>-0.6550466245293762</v>
+        <v>-0.6550467140382321</v>
       </c>
       <c r="H376" t="n">
         <v>965.127357372077</v>
@@ -30442,10 +30442,10 @@
         <v>2267.833340657552</v>
       </c>
       <c r="F390" t="n">
-        <v>2285.874242553711</v>
+        <v>2285.874241333008</v>
       </c>
       <c r="G390" t="n">
-        <v>0.510273742260936</v>
+        <v>0.5102736885864045</v>
       </c>
       <c r="H390" t="n">
         <v>2765.379504159864</v>
@@ -30522,7 +30522,7 @@
         <v>740.9787213134765</v>
       </c>
       <c r="G391" t="n">
-        <v>0.2812551112079786</v>
+        <v>0.2812549041204981</v>
       </c>
       <c r="H391" t="n">
         <v>837.8765073351432</v>
@@ -30593,13 +30593,13 @@
         <v>4291.635766601563</v>
       </c>
       <c r="E392" t="n">
-        <v>4221.925719401042</v>
+        <v>4221.925716145834</v>
       </c>
       <c r="F392" t="n">
-        <v>4282.245913085938</v>
+        <v>4282.245932617187</v>
       </c>
       <c r="G392" t="n">
-        <v>-0.6734178197799312</v>
+        <v>-0.6734179854702038</v>
       </c>
       <c r="H392" t="n">
         <v>5300.049076984566</v>
@@ -31064,7 +31064,7 @@
         <v>-2.417199217532262</v>
       </c>
       <c r="H398" t="n">
-        <v>595.0073081354498</v>
+        <v>595.0072462602649</v>
       </c>
       <c r="I398" t="n">
         <v>327.0399977629436</v>
@@ -31073,7 +31073,7 @@
         <v>36.94043822374952</v>
       </c>
       <c r="K398" t="n">
-        <v>32.85861338090959</v>
+        <v>32.85859956485866</v>
       </c>
       <c r="L398" t="n">
         <v>38.66481223922114</v>
@@ -31446,7 +31446,7 @@
         <v>217.2095184326172</v>
       </c>
       <c r="G403" t="n">
-        <v>-1.091463176646235</v>
+        <v>-1.091463107922186</v>
       </c>
       <c r="H403" t="n">
         <v>272.0997840702363</v>
@@ -33442,16 +33442,16 @@
         <v>434.0719232177734</v>
       </c>
       <c r="E429" t="n">
-        <v>430.8430285644531</v>
+        <v>430.8430289713542</v>
       </c>
       <c r="F429" t="n">
-        <v>450.1680479431153</v>
+        <v>450.1680490112305</v>
       </c>
       <c r="G429" t="n">
-        <v>-1.368612014082271</v>
+        <v>-1.368612274673853</v>
       </c>
       <c r="H429" t="n">
-        <v>533.7088183031568</v>
+        <v>533.7087547028075</v>
       </c>
       <c r="I429" t="n">
         <v>363.2227809620478</v>
@@ -33460,7 +33460,7 @@
         <v>21.97747801486656</v>
       </c>
       <c r="K429" t="n">
-        <v>20.46243832706111</v>
+        <v>20.46242397194295</v>
       </c>
       <c r="L429" t="n">
         <v>39.77746870653686</v>
@@ -33599,13 +33599,13 @@
         <v>880.8134737141927</v>
       </c>
       <c r="F431" t="n">
-        <v>936.8532272338867</v>
+        <v>936.8532266235352</v>
       </c>
       <c r="G431" t="n">
-        <v>-2.329903728901062</v>
+        <v>-2.329903730383598</v>
       </c>
       <c r="H431" t="n">
-        <v>1304.859850069017</v>
+        <v>1304.859727076846</v>
       </c>
       <c r="I431" t="n">
         <v>734.1152411860135</v>
@@ -33614,7 +33614,7 @@
         <v>38.58859853806918</v>
       </c>
       <c r="K431" t="n">
-        <v>28.2543560799015</v>
+        <v>28.25434399103111</v>
       </c>
       <c r="L431" t="n">
         <v>38.38664812239222</v>
@@ -34286,19 +34286,19 @@
         <v>299.4500122070312</v>
       </c>
       <c r="D440" t="n">
-        <v>300.0463537597656</v>
+        <v>300.0463525390625</v>
       </c>
       <c r="E440" t="n">
-        <v>275.6052380371094</v>
+        <v>275.6052377319336</v>
       </c>
       <c r="F440" t="n">
-        <v>293.9109297180176</v>
+        <v>293.9109299468994</v>
       </c>
       <c r="G440" t="n">
-        <v>-1.567755955615657</v>
+        <v>-1.567755702907492</v>
       </c>
       <c r="H440" t="n">
-        <v>411.0263693591629</v>
+        <v>411.0263372414121</v>
       </c>
       <c r="I440" t="n">
         <v>203.5784807586748</v>
@@ -34307,7 +34307,7 @@
         <v>47.09315596180528</v>
       </c>
       <c r="K440" t="n">
-        <v>37.26042831983285</v>
+        <v>37.2604175942528</v>
       </c>
       <c r="L440" t="n">
         <v>32.96244784422809</v>
@@ -34757,7 +34757,7 @@
         <v>569.7603265380859</v>
       </c>
       <c r="G446" t="n">
-        <v>-2.500240237322693</v>
+        <v>-2.500240186405445</v>
       </c>
       <c r="H446" t="n">
         <v>807.5037961542022</v>
@@ -35053,31 +35053,31 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>110.7099990844727</v>
+        <v>110.2099990844727</v>
       </c>
       <c r="D450" t="n">
-        <v>105.7389999389648</v>
+        <v>105.2614500427246</v>
       </c>
       <c r="E450" t="n">
-        <v>103.5067998758952</v>
+        <v>103.0393314615885</v>
       </c>
       <c r="F450" t="n">
-        <v>113.7839999008179</v>
+        <v>113.2701168823242</v>
       </c>
       <c r="G450" t="n">
-        <v>-5.101867308456187</v>
+        <v>-5.101867327127485</v>
       </c>
       <c r="H450" t="n">
-        <v>181.5500030517578</v>
+        <v>180.7300708679145</v>
       </c>
       <c r="I450" t="n">
-        <v>86.34999847412109</v>
+        <v>85.96001645922374</v>
       </c>
       <c r="J450" t="n">
-        <v>28.21077132694125</v>
+        <v>28.21077010467095</v>
       </c>
       <c r="K450" t="n">
-        <v>63.98699715753193</v>
+        <v>63.98699969990045</v>
       </c>
       <c r="L450" t="n">
         <v>16.55076495132128</v>
@@ -35832,13 +35832,13 @@
         <v>620.7981178792318</v>
       </c>
       <c r="F460" t="n">
-        <v>639.6512409973144</v>
+        <v>639.6512413024902</v>
       </c>
       <c r="G460" t="n">
-        <v>-1.706532932112825</v>
+        <v>-1.706533023503021</v>
       </c>
       <c r="H460" t="n">
-        <v>859.7877679261235</v>
+        <v>859.7877065596524</v>
       </c>
       <c r="I460" t="n">
         <v>502</v>
@@ -35847,7 +35847,7 @@
         <v>25.06971625217878</v>
       </c>
       <c r="K460" t="n">
-        <v>36.94159454632953</v>
+        <v>36.94158477226352</v>
       </c>
       <c r="L460" t="n">
         <v>48.40055632823366</v>
@@ -35909,10 +35909,10 @@
         <v>159.2814719645182</v>
       </c>
       <c r="F461" t="n">
-        <v>154.3155361175537</v>
+        <v>154.3155358886719</v>
       </c>
       <c r="G461" t="n">
-        <v>1.218613257205159</v>
+        <v>1.218613056424522</v>
       </c>
       <c r="H461" t="n">
         <v>203.5447632528218</v>
@@ -35983,25 +35983,25 @@
         <v>242.5095440673828</v>
       </c>
       <c r="E462" t="n">
-        <v>226.9388553873698</v>
+        <v>226.9388555908203</v>
       </c>
       <c r="F462" t="n">
-        <v>228.548258895874</v>
+        <v>228.5482592010498</v>
       </c>
       <c r="G462" t="n">
-        <v>0.2923727943955567</v>
+        <v>0.2923726932716031</v>
       </c>
       <c r="H462" t="n">
-        <v>286.08038637852</v>
+        <v>286.0804516993438</v>
       </c>
       <c r="I462" t="n">
-        <v>171.952833032562</v>
+        <v>171.9528178807998</v>
       </c>
       <c r="J462" t="n">
-        <v>30.03566278037038</v>
+        <v>30.03567423856837</v>
       </c>
       <c r="K462" t="n">
-        <v>27.94292422607496</v>
+        <v>27.94295343932271</v>
       </c>
       <c r="L462" t="n">
         <v>46.31432545201669</v>
@@ -36907,13 +36907,13 @@
         <v>4537.360185546875</v>
       </c>
       <c r="E474" t="n">
-        <v>4728.264412434896</v>
+        <v>4728.264415690104</v>
       </c>
       <c r="F474" t="n">
-        <v>4768.107342529297</v>
+        <v>4768.107344970703</v>
       </c>
       <c r="G474" t="n">
-        <v>0.02668687044988793</v>
+        <v>0.0266869728965391</v>
       </c>
       <c r="H474" t="n">
         <v>5612.405266256894</v>
@@ -37064,10 +37064,10 @@
         <v>1288.223666585287</v>
       </c>
       <c r="F476" t="n">
-        <v>1362.906603698731</v>
+        <v>1362.906606750488</v>
       </c>
       <c r="G476" t="n">
-        <v>-0.9322469462576977</v>
+        <v>-0.9322468562857344</v>
       </c>
       <c r="H476" t="n">
         <v>1729.008500794829</v>
@@ -37215,13 +37215,13 @@
         <v>351.4259497070312</v>
       </c>
       <c r="E478" t="n">
-        <v>344.8985697428386</v>
+        <v>344.8985703531901</v>
       </c>
       <c r="F478" t="n">
-        <v>344.8132922363282</v>
+        <v>344.813293762207</v>
       </c>
       <c r="G478" t="n">
-        <v>-0.2905767290785177</v>
+        <v>-0.2905769037784833</v>
       </c>
       <c r="H478" t="n">
         <v>381.3442016302781</v>
@@ -37292,13 +37292,13 @@
         <v>132229.1275</v>
       </c>
       <c r="E479" t="n">
-        <v>132968.9260416667</v>
+        <v>132968.9258333333</v>
       </c>
       <c r="F479" t="n">
-        <v>137684.05</v>
+        <v>137684.049765625</v>
       </c>
       <c r="G479" t="n">
-        <v>-1.907963137484814</v>
+        <v>-1.907963632049481</v>
       </c>
       <c r="H479" t="n">
         <v>163308.4863287346</v>
@@ -37523,13 +37523,13 @@
         <v>437.2216021728516</v>
       </c>
       <c r="E482" t="n">
-        <v>409.451254679362</v>
+        <v>409.4512548828125</v>
       </c>
       <c r="F482" t="n">
-        <v>423.2635185241699</v>
+        <v>423.2635197448731</v>
       </c>
       <c r="G482" t="n">
-        <v>-5.120491416334128</v>
+        <v>-5.120491142699124</v>
       </c>
       <c r="H482" t="n">
         <v>684.5682054144123</v>
@@ -37606,7 +37606,7 @@
         <v>4798.817147216797</v>
       </c>
       <c r="G483" t="n">
-        <v>-2.066156369471883</v>
+        <v>-2.066156418266463</v>
       </c>
       <c r="H483" t="n">
         <v>6344.474916122625</v>
@@ -37683,7 +37683,7 @@
         <v>261.2901779937744</v>
       </c>
       <c r="G484" t="n">
-        <v>-1.804399534048728</v>
+        <v>-1.804399590358152</v>
       </c>
       <c r="H484" t="n">
         <v>347.6028003347344</v>
@@ -37834,10 +37834,10 @@
         <v>127.0976028442383</v>
       </c>
       <c r="F486" t="n">
-        <v>130.7580132293701</v>
+        <v>130.7580133056641</v>
       </c>
       <c r="G486" t="n">
-        <v>-3.15694453961648</v>
+        <v>-3.156944592554223</v>
       </c>
       <c r="H486" t="n">
         <v>190.7660872777346</v>
@@ -37982,25 +37982,25 @@
         <v>523.4500122070312</v>
       </c>
       <c r="D488" t="n">
-        <v>533.8344073486328</v>
+        <v>533.8344122314453</v>
       </c>
       <c r="E488" t="n">
-        <v>518.7572774251302</v>
+        <v>518.7572792561849</v>
       </c>
       <c r="F488" t="n">
-        <v>556.8276208496094</v>
+        <v>556.8276222229003</v>
       </c>
       <c r="G488" t="n">
-        <v>-3.689742512723071</v>
+        <v>-3.689742351449865</v>
       </c>
       <c r="H488" t="n">
         <v>872.0425606177564</v>
       </c>
       <c r="I488" t="n">
-        <v>406.1171468902937</v>
+        <v>406.117116732523</v>
       </c>
       <c r="J488" t="n">
-        <v>28.89138422624475</v>
+        <v>28.89139379756458</v>
       </c>
       <c r="K488" t="n">
         <v>66.59519348198091</v>
@@ -38524,13 +38524,13 @@
         <v>407.926743774414</v>
       </c>
       <c r="E495" t="n">
-        <v>422.8836791992188</v>
+        <v>422.8836785888672</v>
       </c>
       <c r="F495" t="n">
-        <v>418.342080078125</v>
+        <v>418.3420794677734</v>
       </c>
       <c r="G495" t="n">
-        <v>-0.2434537166788986</v>
+        <v>-0.2434536081420746</v>
       </c>
       <c r="H495" t="n">
         <v>472.8081629796919</v>
@@ -39528,19 +39528,19 @@
         <v>967.5347066243489</v>
       </c>
       <c r="F508" t="n">
-        <v>946.3726348876953</v>
+        <v>946.3726351928711</v>
       </c>
       <c r="G508" t="n">
-        <v>1.012695255622109</v>
+        <v>1.01269525529224</v>
       </c>
       <c r="H508" t="n">
         <v>1224.72508309492</v>
       </c>
       <c r="I508" t="n">
-        <v>784.9092044208618</v>
+        <v>784.9091438882253</v>
       </c>
       <c r="J508" t="n">
-        <v>9.999987202483428</v>
+        <v>9.999995685744567</v>
       </c>
       <c r="K508" t="n">
         <v>41.84909062587376</v>
@@ -39750,31 +39750,31 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>364.1000061035156</v>
+        <v>360.1999816894531</v>
       </c>
       <c r="D511" t="n">
-        <v>404.8984802246094</v>
+        <v>400.5614611816407</v>
       </c>
       <c r="E511" t="n">
-        <v>412.7961547851563</v>
+        <v>408.3745416259766</v>
       </c>
       <c r="F511" t="n">
-        <v>397.0236824035645</v>
+        <v>392.7710137939453</v>
       </c>
       <c r="G511" t="n">
-        <v>0.248268977842625</v>
+        <v>0.2482687795707594</v>
       </c>
       <c r="H511" t="n">
-        <v>481.9916794589248</v>
+        <v>476.8288845013619</v>
       </c>
       <c r="I511" t="n">
-        <v>321.1028454240115</v>
+        <v>317.6634042148347</v>
       </c>
       <c r="J511" t="n">
-        <v>13.39046392526575</v>
+        <v>13.3904557182958</v>
       </c>
       <c r="K511" t="n">
-        <v>32.37892649798304</v>
+        <v>32.37893079974125</v>
       </c>
       <c r="L511" t="n">
         <v>31.15438108484005</v>
@@ -40301,7 +40301,7 @@
         <v>1917.128778686523</v>
       </c>
       <c r="G518" t="n">
-        <v>-1.735086998422652</v>
+        <v>-1.735086875456471</v>
       </c>
       <c r="H518" t="n">
         <v>2484.339731207416</v>
@@ -42226,7 +42226,7 @@
         <v>160.0568105316162</v>
       </c>
       <c r="G543" t="n">
-        <v>-0.6092714988192083</v>
+        <v>-0.6092714517314746</v>
       </c>
       <c r="H543" t="n">
         <v>197.1955548334318</v>
@@ -43067,13 +43067,13 @@
         <v>714.6933142089844</v>
       </c>
       <c r="E554" t="n">
-        <v>734.969473063151</v>
+        <v>734.9694734700521</v>
       </c>
       <c r="F554" t="n">
-        <v>746.3083404541015</v>
+        <v>746.3083401489258</v>
       </c>
       <c r="G554" t="n">
-        <v>-0.6628209941309637</v>
+        <v>-0.6628209944001928</v>
       </c>
       <c r="H554" t="n">
         <v>879.2203373423794</v>
@@ -43686,10 +43686,10 @@
         <v>3093.214021809896</v>
       </c>
       <c r="F562" t="n">
-        <v>3231.007095947265</v>
+        <v>3231.007102050781</v>
       </c>
       <c r="G562" t="n">
-        <v>-1.82696155065607</v>
+        <v>-1.826961438028873</v>
       </c>
       <c r="H562" t="n">
         <v>4112.487734005053</v>
@@ -43760,16 +43760,16 @@
         <v>124.6543998718262</v>
       </c>
       <c r="E563" t="n">
-        <v>123.8198503112793</v>
+        <v>123.8198501078288</v>
       </c>
       <c r="F563" t="n">
-        <v>127.0208605194092</v>
+        <v>127.0208612442017</v>
       </c>
       <c r="G563" t="n">
-        <v>-0.8274799604907623</v>
+        <v>-0.8274796604372692</v>
       </c>
       <c r="H563" t="n">
-        <v>155.8999606999571</v>
+        <v>155.8999783750524</v>
       </c>
       <c r="I563" t="n">
         <v>112.8155071321618</v>
@@ -43778,7 +43778,7 @@
         <v>8.14116170845085</v>
       </c>
       <c r="K563" t="n">
-        <v>27.78685303275177</v>
+        <v>27.78686752053476</v>
       </c>
       <c r="L563" t="n">
         <v>27.39916550764951</v>
@@ -43840,10 +43840,10 @@
         <v>1081.395000813802</v>
       </c>
       <c r="F564" t="n">
-        <v>1113.768211669922</v>
+        <v>1113.76821105957</v>
       </c>
       <c r="G564" t="n">
-        <v>-1.845259402779564</v>
+        <v>-1.845259350975281</v>
       </c>
       <c r="H564" t="n">
         <v>1400.476774401248</v>
@@ -43914,16 +43914,16 @@
         <v>198.5411529541016</v>
       </c>
       <c r="E565" t="n">
-        <v>194.6922651163737</v>
+        <v>194.692265218099</v>
       </c>
       <c r="F565" t="n">
-        <v>200.2659353637695</v>
+        <v>200.2659349822998</v>
       </c>
       <c r="G565" t="n">
-        <v>-1.652856164846184</v>
+        <v>-1.652856094247801</v>
       </c>
       <c r="H565" t="n">
-        <v>239.2187192222334</v>
+        <v>239.2187037807859</v>
       </c>
       <c r="I565" t="n">
         <v>156.7442971017576</v>
@@ -43932,7 +43932,7 @@
         <v>19.27068506159122</v>
       </c>
       <c r="K565" t="n">
-        <v>27.95866441680768</v>
+        <v>27.95865615714053</v>
       </c>
       <c r="L565" t="n">
         <v>26.56467315716273</v>
@@ -44459,19 +44459,19 @@
         <v>36379.73055664063</v>
       </c>
       <c r="G572" t="n">
-        <v>-0.7706216724461701</v>
+        <v>-0.7706218310349122</v>
       </c>
       <c r="H572" t="n">
-        <v>46547.9774954976</v>
+        <v>46547.97355089381</v>
       </c>
       <c r="I572" t="n">
-        <v>29525.27549507192</v>
+        <v>29525.27356749276</v>
       </c>
       <c r="J572" t="n">
-        <v>19.06747493640744</v>
+        <v>19.06748270981493</v>
       </c>
       <c r="K572" t="n">
-        <v>32.40784382164017</v>
+        <v>32.40783260103488</v>
       </c>
       <c r="L572" t="n">
         <v>24.06119610570236</v>
@@ -44530,16 +44530,16 @@
         <v>20.09274887084961</v>
       </c>
       <c r="E573" t="n">
-        <v>20.69203909556071</v>
+        <v>20.69203907012939</v>
       </c>
       <c r="F573" t="n">
-        <v>20.77396909713745</v>
+        <v>20.77396904945374</v>
       </c>
       <c r="G573" t="n">
-        <v>-1.130340885089576</v>
+        <v>-1.130341201781393</v>
       </c>
       <c r="H573" t="n">
-        <v>23.83526224893035</v>
+        <v>23.83526024888653</v>
       </c>
       <c r="I573" t="n">
         <v>18.76000022888184</v>
@@ -44548,7 +44548,7 @@
         <v>3.731337137795676</v>
       </c>
       <c r="K573" t="n">
-        <v>22.48336778159854</v>
+        <v>22.48335750388058</v>
       </c>
       <c r="L573" t="n">
         <v>23.9221140472879</v>
@@ -44921,10 +44921,10 @@
         <v>444.3571166992188</v>
       </c>
       <c r="G578" t="n">
-        <v>-0.9109807827398897</v>
+        <v>-0.9109808164561084</v>
       </c>
       <c r="H578" t="n">
-        <v>566.8734333795863</v>
+        <v>566.8733711713968</v>
       </c>
       <c r="I578" t="n">
         <v>394.4382907843191</v>
@@ -44933,7 +44933,7 @@
         <v>8.39464569801498</v>
       </c>
       <c r="K578" t="n">
-        <v>32.5864693169122</v>
+        <v>32.58645476699024</v>
       </c>
       <c r="L578" t="n">
         <v>21.557719054242</v>
@@ -45075,7 +45075,7 @@
         <v>130.4684894943237</v>
       </c>
       <c r="G580" t="n">
-        <v>-1.899854843843918</v>
+        <v>-1.899854900120002</v>
       </c>
       <c r="H580" t="n">
         <v>161.771226720913</v>
@@ -45768,7 +45768,7 @@
         <v>99.53585285186767</v>
       </c>
       <c r="G589" t="n">
-        <v>-2.217568612131382</v>
+        <v>-2.217568648775337</v>
       </c>
       <c r="H589" t="n">
         <v>125.4787772411715</v>
@@ -45993,22 +45993,22 @@
         <v>846.5494262695313</v>
       </c>
       <c r="E592" t="n">
-        <v>958.6672916666666</v>
+        <v>958.6672932942708</v>
       </c>
       <c r="F592" t="n">
-        <v>926.2497128295898</v>
+        <v>926.2497155761719</v>
       </c>
       <c r="G592" t="n">
-        <v>-0.3529845828608824</v>
+        <v>-0.3529847781095219</v>
       </c>
       <c r="H592" t="n">
         <v>1282.80960014975</v>
       </c>
       <c r="I592" t="n">
-        <v>743.4272688553443</v>
+        <v>743.4273285628773</v>
       </c>
       <c r="J592" t="n">
-        <v>7.044767004344998</v>
+        <v>7.044758407164453</v>
       </c>
       <c r="K592" t="n">
         <v>61.19748929720756</v>
@@ -46455,16 +46455,16 @@
         <v>2236.379436035156</v>
       </c>
       <c r="E598" t="n">
-        <v>2403.595869954427</v>
+        <v>2403.595850423177</v>
       </c>
       <c r="F598" t="n">
-        <v>2573.830305786133</v>
+        <v>2573.830294799805</v>
       </c>
       <c r="G598" t="n">
-        <v>-2.260383128362753</v>
+        <v>-2.260383319023596</v>
       </c>
       <c r="H598" t="n">
-        <v>3287.161645949698</v>
+        <v>3287.161392369851</v>
       </c>
       <c r="I598" t="n">
         <v>1966.020518717901</v>
@@ -46473,7 +46473,7 @@
         <v>15.46166372059701</v>
       </c>
       <c r="K598" t="n">
-        <v>44.80888308148447</v>
+        <v>44.8088719105661</v>
       </c>
       <c r="L598" t="n">
         <v>13.63004172461753</v>
@@ -46769,7 +46769,7 @@
         <v>1298.890830383301</v>
       </c>
       <c r="G602" t="n">
-        <v>-2.440394353462949</v>
+        <v>-2.440394264013546</v>
       </c>
       <c r="H602" t="n">
         <v>1691.399159307065</v>
@@ -47610,13 +47610,13 @@
         <v>139.8083261108399</v>
       </c>
       <c r="E613" t="n">
-        <v>146.5239614868164</v>
+        <v>146.5239616902669</v>
       </c>
       <c r="F613" t="n">
-        <v>149.4153604888916</v>
+        <v>149.4153608703613</v>
       </c>
       <c r="G613" t="n">
-        <v>-0.8132854016685953</v>
+        <v>-0.8132853996090983</v>
       </c>
       <c r="H613" t="n">
         <v>184.9587904135824</v>
@@ -47835,31 +47835,31 @@
         </is>
       </c>
       <c r="C616" t="n">
-        <v>2204</v>
+        <v>2200.35009765625</v>
       </c>
       <c r="D616" t="n">
-        <v>2265.192016601562</v>
+        <v>2261.440747070313</v>
       </c>
       <c r="E616" t="n">
-        <v>2283.889998372396</v>
+        <v>2280.10775390625</v>
       </c>
       <c r="F616" t="n">
-        <v>2351.835498046875</v>
+        <v>2347.940729980469</v>
       </c>
       <c r="G616" t="n">
-        <v>-1.348437104755829</v>
+        <v>-1.348437065455277</v>
       </c>
       <c r="H616" t="n">
-        <v>2766.640003932077</v>
+        <v>2762.058191112182</v>
       </c>
       <c r="I616" t="n">
-        <v>2023.900024414062</v>
+        <v>2020.548311951282</v>
       </c>
       <c r="J616" t="n">
-        <v>8.898659687406152</v>
+        <v>8.898663033269916</v>
       </c>
       <c r="K616" t="n">
-        <v>25.52813084991275</v>
+        <v>25.52812364060826</v>
       </c>
       <c r="L616" t="n">
         <v>28.2336578581363</v>
@@ -48226,13 +48226,13 @@
         <v>2032.807890625</v>
       </c>
       <c r="E621" t="n">
-        <v>2035.852347005208</v>
+        <v>2035.852345377604</v>
       </c>
       <c r="F621" t="n">
         <v>2098.911813964844</v>
       </c>
       <c r="G621" t="n">
-        <v>-0.6574707158273019</v>
+        <v>-0.6574708306205324</v>
       </c>
       <c r="H621" t="n">
         <v>2486.766809421043</v>
@@ -48306,10 +48306,10 @@
         <v>33.72791913350423</v>
       </c>
       <c r="F622" t="n">
-        <v>34.48615404129028</v>
+        <v>34.48615413665772</v>
       </c>
       <c r="G622" t="n">
-        <v>-2.058060023914909</v>
+        <v>-2.058059965286141</v>
       </c>
       <c r="H622" t="n">
         <v>40.26070662850351</v>
@@ -48774,7 +48774,7 @@
         <v>-2.486287738815418</v>
       </c>
       <c r="H628" t="n">
-        <v>294.6532543042141</v>
+        <v>294.6532203195111</v>
       </c>
       <c r="I628" t="n">
         <v>213.7350670269712</v>
@@ -48783,7 +48783,7 @@
         <v>5.350049152454295</v>
       </c>
       <c r="K628" t="n">
-        <v>30.85813238899413</v>
+        <v>30.85811729608512</v>
       </c>
       <c r="L628" t="n">
         <v>18.77607788595271</v>
@@ -48848,10 +48848,10 @@
         <v>2060.72713256836</v>
       </c>
       <c r="G629" t="n">
-        <v>-1.01817583207493</v>
+        <v>-1.018175774038532</v>
       </c>
       <c r="H629" t="n">
-        <v>2448.345479475883</v>
+        <v>2448.345231432346</v>
       </c>
       <c r="I629" t="n">
         <v>1761.237851420491</v>
@@ -48860,7 +48860,7 @@
         <v>5.607541792260151</v>
       </c>
       <c r="K629" t="n">
-        <v>31.63147739117651</v>
+        <v>31.63146405550248</v>
       </c>
       <c r="L629" t="n">
         <v>18.63699582753825</v>
@@ -48919,22 +48919,22 @@
         <v>465.8306628417969</v>
       </c>
       <c r="E630" t="n">
-        <v>468.9475262451172</v>
+        <v>468.9475266520182</v>
       </c>
       <c r="F630" t="n">
         <v>470.8764637756348</v>
       </c>
       <c r="G630" t="n">
-        <v>-0.4916013872550473</v>
+        <v>-0.4916012268187719</v>
       </c>
       <c r="H630" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I630" t="n">
-        <v>379.7399002549519</v>
+        <v>379.7399306767125</v>
       </c>
       <c r="J630" t="n">
-        <v>10.93119256553729</v>
+        <v>10.9311836786073</v>
       </c>
       <c r="K630" t="n">
         <v>31.79448034789032</v>
@@ -49381,16 +49381,16 @@
         <v>296.3701397705078</v>
       </c>
       <c r="E636" t="n">
-        <v>305.9752106730143</v>
+        <v>305.9752110799154</v>
       </c>
       <c r="F636" t="n">
-        <v>315.5437122344971</v>
+        <v>315.5437120819092</v>
       </c>
       <c r="G636" t="n">
-        <v>-2.725635475400101</v>
+        <v>-2.725635385168279</v>
       </c>
       <c r="H636" t="n">
-        <v>408.5542426067486</v>
+        <v>408.5542740377988</v>
       </c>
       <c r="I636" t="n">
         <v>243.9284560598348</v>
@@ -49399,7 +49399,7 @@
         <v>15.15671374871517</v>
       </c>
       <c r="K636" t="n">
-        <v>45.44473174937364</v>
+        <v>45.444742938783</v>
       </c>
       <c r="L636" t="n">
         <v>16.41168289290681</v>
@@ -49458,13 +49458,13 @@
         <v>492.9577587890625</v>
       </c>
       <c r="E637" t="n">
-        <v>539.0047780354818</v>
+        <v>539.0047784423828</v>
       </c>
       <c r="F637" t="n">
-        <v>541.7615257263184</v>
+        <v>541.761527557373</v>
       </c>
       <c r="G637" t="n">
-        <v>-1.374260513553638</v>
+        <v>-1.374260399387406</v>
       </c>
       <c r="H637" t="n">
         <v>653.9340000086492</v>
@@ -50465,7 +50465,7 @@
         <v>358.2679244995117</v>
       </c>
       <c r="G650" t="n">
-        <v>-1.396908852533141</v>
+        <v>-1.396908686897724</v>
       </c>
       <c r="H650" t="n">
         <v>467.1017114386881</v>
@@ -51158,7 +51158,7 @@
         <v>459.6133813476562</v>
       </c>
       <c r="G659" t="n">
-        <v>-1.95144868745154</v>
+        <v>-1.951448527871058</v>
       </c>
       <c r="H659" t="n">
         <v>566.6192163890048</v>
@@ -51614,16 +51614,16 @@
         <v>1023.887087402344</v>
       </c>
       <c r="E665" t="n">
-        <v>1061.330559082031</v>
+        <v>1061.330555826823</v>
       </c>
       <c r="F665" t="n">
-        <v>1086.30336730957</v>
+        <v>1086.303366088867</v>
       </c>
       <c r="G665" t="n">
-        <v>-1.139736333483365</v>
+        <v>-1.139736334749519</v>
       </c>
       <c r="H665" t="n">
-        <v>1284.135218376752</v>
+        <v>1284.135475005729</v>
       </c>
       <c r="I665" t="n">
         <v>902.8120757721283</v>
@@ -51632,7 +51632,7 @@
         <v>2.213961527236541</v>
       </c>
       <c r="K665" t="n">
-        <v>39.15639741695027</v>
+        <v>39.15642522676612</v>
       </c>
       <c r="L665" t="n">
         <v>9.179415855354661</v>
@@ -51922,16 +51922,16 @@
         <v>177.906803894043</v>
       </c>
       <c r="E669" t="n">
-        <v>193.7196807861328</v>
+        <v>193.7196806844076</v>
       </c>
       <c r="F669" t="n">
-        <v>207.2172761535645</v>
+        <v>207.2172757720947</v>
       </c>
       <c r="G669" t="n">
-        <v>-2.650825811763402</v>
+        <v>-2.650825851406224</v>
       </c>
       <c r="H669" t="n">
-        <v>263.2205288662585</v>
+        <v>263.220498300555</v>
       </c>
       <c r="I669" t="n">
         <v>167.0916913788894</v>
@@ -51940,7 +51940,7 @@
         <v>6.139332626279392</v>
       </c>
       <c r="K669" t="n">
-        <v>48.41867482802451</v>
+        <v>48.41865759334594</v>
       </c>
       <c r="L669" t="n">
         <v>8.484005563282336</v>
@@ -52233,13 +52233,13 @@
         <v>538.8566294352214</v>
       </c>
       <c r="F673" t="n">
-        <v>571.8121583557129</v>
+        <v>571.8121589660644</v>
       </c>
       <c r="G673" t="n">
-        <v>-3.823652175717429</v>
+        <v>-3.823652221158724</v>
       </c>
       <c r="H673" t="n">
-        <v>729.6617501297184</v>
+        <v>729.6618113637422</v>
       </c>
       <c r="I673" t="n">
         <v>481</v>
@@ -52248,7 +52248,7 @@
         <v>2.234927234927242</v>
       </c>
       <c r="K673" t="n">
-        <v>48.38063042800578</v>
+        <v>48.38064288027295</v>
       </c>
       <c r="L673" t="n">
         <v>7.37134909596662</v>
@@ -53770,13 +53770,13 @@
         <v>229.6380801391602</v>
       </c>
       <c r="E693" t="n">
-        <v>265.9076697794596</v>
+        <v>265.9076699829101</v>
       </c>
       <c r="F693" t="n">
-        <v>281.2778220367431</v>
+        <v>281.2778221893311</v>
       </c>
       <c r="G693" t="n">
-        <v>-3.864157656755374</v>
+        <v>-3.86415775501342</v>
       </c>
       <c r="H693" t="n">
         <v>398.2045017598045</v>
@@ -54315,7 +54315,7 @@
         <v>410.4168014526367</v>
       </c>
       <c r="G700" t="n">
-        <v>-3.732589588232871</v>
+        <v>-3.732589553777776</v>
       </c>
       <c r="H700" t="n">
         <v>541.6977805031639</v>
@@ -55772,13 +55772,13 @@
         <v>608.8729235839844</v>
       </c>
       <c r="E719" t="n">
-        <v>720.6081681315104</v>
+        <v>720.6081693522135</v>
       </c>
       <c r="F719" t="n">
-        <v>837.4291815185547</v>
+        <v>837.4291848754883</v>
       </c>
       <c r="G719" t="n">
-        <v>-6.710605116508217</v>
+        <v>-6.710605091413147</v>
       </c>
       <c r="H719" t="n">
         <v>1313.886868193049</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1724,16 +1724,16 @@
         <v>1808.590012207031</v>
       </c>
       <c r="G17" t="n">
-        <v>9.659776236588137</v>
+        <v>9.659776196006021</v>
       </c>
       <c r="H17" t="n">
         <v>2983.800048828125</v>
       </c>
       <c r="I17" t="n">
-        <v>1158.746695475609</v>
+        <v>1158.746573666689</v>
       </c>
       <c r="J17" t="n">
-        <v>144.2380296493214</v>
+        <v>144.2380553239351</v>
       </c>
       <c r="K17" t="n">
         <v>5.430901588928316</v>
@@ -1878,16 +1878,16 @@
         <v>1249.432555847168</v>
       </c>
       <c r="G19" t="n">
-        <v>8.610348051316329</v>
+        <v>8.610348166566006</v>
       </c>
       <c r="H19" t="n">
         <v>1938.5</v>
       </c>
       <c r="I19" t="n">
-        <v>821.6033372206257</v>
+        <v>821.6033975811163</v>
       </c>
       <c r="J19" t="n">
-        <v>135.9411059061282</v>
+        <v>135.9410885723137</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2337,10 +2337,10 @@
         <v>1040.961384277344</v>
       </c>
       <c r="F25" t="n">
-        <v>995.9313748168945</v>
+        <v>995.931374206543</v>
       </c>
       <c r="G25" t="n">
-        <v>6.040246790881021</v>
+        <v>6.040246898173685</v>
       </c>
       <c r="H25" t="n">
         <v>1489.699951171875</v>
@@ -3184,19 +3184,19 @@
         <v>609.8349696858724</v>
       </c>
       <c r="F36" t="n">
-        <v>577.447481842041</v>
+        <v>577.4474826049805</v>
       </c>
       <c r="G36" t="n">
-        <v>6.789119111998487</v>
+        <v>6.789119132553867</v>
       </c>
       <c r="H36" t="n">
         <v>844</v>
       </c>
       <c r="I36" t="n">
-        <v>399.8350028638013</v>
+        <v>399.8349725758499</v>
       </c>
       <c r="J36" t="n">
-        <v>103.8340800986899</v>
+        <v>103.8340955393521</v>
       </c>
       <c r="K36" t="n">
         <v>3.558282208588959</v>
@@ -4496,16 +4496,16 @@
         <v>1716.051952514649</v>
       </c>
       <c r="G53" t="n">
-        <v>6.743528603658522</v>
+        <v>6.743528725236225</v>
       </c>
       <c r="H53" t="n">
         <v>2539.60009765625</v>
       </c>
       <c r="I53" t="n">
-        <v>1167.643424163666</v>
+        <v>1167.643304709368</v>
       </c>
       <c r="J53" t="n">
-        <v>96.53260587424577</v>
+        <v>96.53262598026988</v>
       </c>
       <c r="K53" t="n">
         <v>10.6675982054792</v>
@@ -4573,7 +4573,7 @@
         <v>8756.291496582031</v>
       </c>
       <c r="G54" t="n">
-        <v>4.498341353380431</v>
+        <v>4.498340988021376</v>
       </c>
       <c r="H54" t="n">
         <v>12275</v>
@@ -4878,10 +4878,10 @@
         <v>135.3292643737793</v>
       </c>
       <c r="F58" t="n">
-        <v>130.3690501022339</v>
+        <v>130.3690500640869</v>
       </c>
       <c r="G58" t="n">
-        <v>5.223745970030325</v>
+        <v>5.223745874445807</v>
       </c>
       <c r="H58" t="n">
         <v>173.2700042724609</v>
@@ -5420,7 +5420,7 @@
         <v>1719.430389404297</v>
       </c>
       <c r="G65" t="n">
-        <v>3.873505097009633</v>
+        <v>3.873505135310196</v>
       </c>
       <c r="H65" t="n">
         <v>2230</v>
@@ -5876,13 +5876,13 @@
         <v>10746.3005859375</v>
       </c>
       <c r="E71" t="n">
-        <v>10352.39270507813</v>
+        <v>10352.39269856771</v>
       </c>
       <c r="F71" t="n">
-        <v>10064.87529541016</v>
+        <v>10064.87531982422</v>
       </c>
       <c r="G71" t="n">
-        <v>3.592138437316139</v>
+        <v>3.592138610504447</v>
       </c>
       <c r="H71" t="n">
         <v>12865.82946046676</v>
@@ -6421,7 +6421,7 @@
         <v>71.34833003997802</v>
       </c>
       <c r="G78" t="n">
-        <v>3.793896762675342</v>
+        <v>3.793896647476025</v>
       </c>
       <c r="H78" t="n">
         <v>94.5</v>
@@ -8192,7 +8192,7 @@
         <v>467.9723748779297</v>
       </c>
       <c r="G101" t="n">
-        <v>4.216170184541279</v>
+        <v>4.216170219954862</v>
       </c>
       <c r="H101" t="n">
         <v>662</v>
@@ -8429,10 +8429,10 @@
         <v>394.5</v>
       </c>
       <c r="I104" t="n">
-        <v>241.7427848010177</v>
+        <v>241.7427995975111</v>
       </c>
       <c r="J104" t="n">
-        <v>58.01919396040307</v>
+        <v>58.01918428842959</v>
       </c>
       <c r="K104" t="n">
         <v>3.27225130890052</v>
@@ -8879,13 +8879,13 @@
         <v>4862.506005859375</v>
       </c>
       <c r="E110" t="n">
-        <v>4456.044943033854</v>
+        <v>4456.044939778646</v>
       </c>
       <c r="F110" t="n">
-        <v>4292.578587646484</v>
+        <v>4292.578580322265</v>
       </c>
       <c r="G110" t="n">
-        <v>3.674116320233267</v>
+        <v>3.674116357298129</v>
       </c>
       <c r="H110" t="n">
         <v>5250</v>
@@ -9267,10 +9267,10 @@
         <v>279.564404296875</v>
       </c>
       <c r="F115" t="n">
-        <v>265.5349858093261</v>
+        <v>265.5349859619141</v>
       </c>
       <c r="G115" t="n">
-        <v>2.129445763664228</v>
+        <v>2.129445762414517</v>
       </c>
       <c r="H115" t="n">
         <v>368.75</v>
@@ -9347,7 +9347,7 @@
         <v>598.5929852294922</v>
       </c>
       <c r="G116" t="n">
-        <v>2.745024171628696</v>
+        <v>2.74502401017005</v>
       </c>
       <c r="H116" t="n">
         <v>769</v>
@@ -9880,13 +9880,13 @@
         <v>1786.570537109375</v>
       </c>
       <c r="E123" t="n">
-        <v>1565.384928385417</v>
+        <v>1565.384929199219</v>
       </c>
       <c r="F123" t="n">
-        <v>1539.997164306641</v>
+        <v>1539.997168579102</v>
       </c>
       <c r="G123" t="n">
-        <v>2.680249500277121</v>
+        <v>2.680249576214511</v>
       </c>
       <c r="H123" t="n">
         <v>1988.900024414062</v>
@@ -11426,16 +11426,16 @@
         <v>357.7914403533936</v>
       </c>
       <c r="G143" t="n">
-        <v>5.05769718175213</v>
+        <v>5.0576972288223</v>
       </c>
       <c r="H143" t="n">
         <v>443.3731066930094</v>
       </c>
       <c r="I143" t="n">
-        <v>175.4686316122085</v>
+        <v>175.4686014749105</v>
       </c>
       <c r="J143" t="n">
-        <v>121.8630100526085</v>
+        <v>121.8630481582958</v>
       </c>
       <c r="K143" t="n">
         <v>13.88983318663677</v>
@@ -12036,13 +12036,13 @@
         <v>2128.194426269531</v>
       </c>
       <c r="E151" t="n">
-        <v>1908.64681233724</v>
+        <v>1908.646811523437</v>
       </c>
       <c r="F151" t="n">
-        <v>1786.850877075195</v>
+        <v>1786.850874633789</v>
       </c>
       <c r="G151" t="n">
-        <v>5.476731167504267</v>
+        <v>5.476731213398911</v>
       </c>
       <c r="H151" t="n">
         <v>2295</v>
@@ -12963,10 +12963,10 @@
         <v>1424.93986328125</v>
       </c>
       <c r="F163" t="n">
-        <v>1512.063893432617</v>
+        <v>1512.063896484375</v>
       </c>
       <c r="G163" t="n">
-        <v>0.5146903424821936</v>
+        <v>0.5146904230021399</v>
       </c>
       <c r="H163" t="n">
         <v>2016.5</v>
@@ -13810,10 +13810,10 @@
         <v>1110.994391682943</v>
       </c>
       <c r="F174" t="n">
-        <v>1086.23972442627</v>
+        <v>1086.239723510742</v>
       </c>
       <c r="G174" t="n">
-        <v>1.963155413135542</v>
+        <v>1.963155590074317</v>
       </c>
       <c r="H174" t="n">
         <v>1596.696405272527</v>
@@ -13890,16 +13890,16 @@
         <v>1357.962288208008</v>
       </c>
       <c r="G175" t="n">
-        <v>2.131581796207138</v>
+        <v>2.13158174932444</v>
       </c>
       <c r="H175" t="n">
         <v>1670.788050106015</v>
       </c>
       <c r="I175" t="n">
-        <v>829.6099050486885</v>
+        <v>829.6099643486841</v>
       </c>
       <c r="J175" t="n">
-        <v>65.2222258714993</v>
+        <v>65.2222140615191</v>
       </c>
       <c r="K175" t="n">
         <v>21.89305534574364</v>
@@ -14731,13 +14731,13 @@
         <v>1113.654523925781</v>
       </c>
       <c r="E186" t="n">
-        <v>973.9560803222656</v>
+        <v>973.9560799153646</v>
       </c>
       <c r="F186" t="n">
-        <v>941.9554711914062</v>
+        <v>941.9554721069336</v>
       </c>
       <c r="G186" t="n">
-        <v>2.444912744315753</v>
+        <v>2.444912843886393</v>
       </c>
       <c r="H186" t="n">
         <v>1303.791320684363</v>
@@ -15045,7 +15045,7 @@
         <v>168.6533303833008</v>
       </c>
       <c r="G190" t="n">
-        <v>2.557134183694276</v>
+        <v>2.557134326435095</v>
       </c>
       <c r="H190" t="n">
         <v>211.8067938496122</v>
@@ -15270,22 +15270,22 @@
         <v>314.235478515625</v>
       </c>
       <c r="E193" t="n">
-        <v>293.2659330240886</v>
+        <v>293.2659339396159</v>
       </c>
       <c r="F193" t="n">
-        <v>283.249167098999</v>
+        <v>283.2491677856445</v>
       </c>
       <c r="G193" t="n">
-        <v>1.879397246399339</v>
+        <v>1.879397381543879</v>
       </c>
       <c r="H193" t="n">
         <v>359.3387168134344</v>
       </c>
       <c r="I193" t="n">
-        <v>206.1211021779015</v>
+        <v>206.1210871445057</v>
       </c>
       <c r="J193" t="n">
-        <v>42.63459533912779</v>
+        <v>42.63460574215046</v>
       </c>
       <c r="K193" t="n">
         <v>22.22405333790287</v>
@@ -15501,13 +15501,13 @@
         <v>5464.749228515625</v>
       </c>
       <c r="E196" t="n">
-        <v>5111.552322591146</v>
+        <v>5111.552314453125</v>
       </c>
       <c r="F196" t="n">
-        <v>4904.71301147461</v>
+        <v>4904.713004150391</v>
       </c>
       <c r="G196" t="n">
-        <v>2.849429135228077</v>
+        <v>2.849429271239035</v>
       </c>
       <c r="H196" t="n">
         <v>6049.821052103703</v>
@@ -15578,13 +15578,13 @@
         <v>1461.1130078125</v>
       </c>
       <c r="E197" t="n">
-        <v>1370.423152669271</v>
+        <v>1370.423153483073</v>
       </c>
       <c r="F197" t="n">
-        <v>1342.488110351562</v>
+        <v>1342.48811340332</v>
       </c>
       <c r="G197" t="n">
-        <v>2.053876488113393</v>
+        <v>2.053876483348605</v>
       </c>
       <c r="H197" t="n">
         <v>1553</v>
@@ -16351,10 +16351,10 @@
         <v>1665.467869466146</v>
       </c>
       <c r="F207" t="n">
-        <v>1664.878531494141</v>
+        <v>1664.878529663086</v>
       </c>
       <c r="G207" t="n">
-        <v>1.008898615555176</v>
+        <v>1.008898579272088</v>
       </c>
       <c r="H207" t="n">
         <v>1983.954544928268</v>
@@ -17660,10 +17660,10 @@
         <v>1776.000349121094</v>
       </c>
       <c r="F224" t="n">
-        <v>1623.4395703125</v>
+        <v>1623.439565429687</v>
       </c>
       <c r="G224" t="n">
-        <v>8.813007840162278</v>
+        <v>8.81300782449026</v>
       </c>
       <c r="H224" t="n">
         <v>2714.261178227147</v>
@@ -19505,13 +19505,13 @@
         <v>1453.612048339844</v>
       </c>
       <c r="E248" t="n">
-        <v>1357.513280436198</v>
+        <v>1357.51328125</v>
       </c>
       <c r="F248" t="n">
-        <v>1365.254739379883</v>
+        <v>1365.254736328125</v>
       </c>
       <c r="G248" t="n">
-        <v>1.368021254305596</v>
+        <v>1.368021303342992</v>
       </c>
       <c r="H248" t="n">
         <v>1563.400024414062</v>
@@ -20281,7 +20281,7 @@
         <v>451.4752644348144</v>
       </c>
       <c r="G258" t="n">
-        <v>1.266946061820584</v>
+        <v>1.266945957842291</v>
       </c>
       <c r="H258" t="n">
         <v>531</v>
@@ -20512,7 +20512,7 @@
         <v>1106.151983337402</v>
       </c>
       <c r="G261" t="n">
-        <v>0.6008997301617969</v>
+        <v>0.6008996743187778</v>
       </c>
       <c r="H261" t="n">
         <v>1229.065274432971</v>
@@ -21661,16 +21661,16 @@
         <v>181.7758578491211</v>
       </c>
       <c r="E276" t="n">
-        <v>177.8353560384114</v>
+        <v>177.8353559366862</v>
       </c>
       <c r="F276" t="n">
-        <v>177.7491371917725</v>
+        <v>177.7491367340088</v>
       </c>
       <c r="G276" t="n">
-        <v>0.03175010092315578</v>
+        <v>0.03175027280304388</v>
       </c>
       <c r="H276" t="n">
-        <v>198.2251564414815</v>
+        <v>198.2251721274962</v>
       </c>
       <c r="I276" t="n">
         <v>164.6038301743624</v>
@@ -21679,7 +21679,7 @@
         <v>12.53687432239095</v>
       </c>
       <c r="K276" t="n">
-        <v>7.00990637186989</v>
+        <v>7.009914839811082</v>
       </c>
       <c r="L276" t="n">
         <v>46.11111111111111</v>
@@ -22893,16 +22893,16 @@
         <v>1202.532025146484</v>
       </c>
       <c r="E292" t="n">
-        <v>1084.43528889974</v>
+        <v>1084.435289713542</v>
       </c>
       <c r="F292" t="n">
-        <v>1147.834253540039</v>
+        <v>1147.834255981445</v>
       </c>
       <c r="G292" t="n">
-        <v>-0.2676649541146214</v>
+        <v>-0.2676650593266494</v>
       </c>
       <c r="H292" t="n">
-        <v>1423.547927723126</v>
+        <v>1423.548053270148</v>
       </c>
       <c r="I292" t="n">
         <v>905.5050975494345</v>
@@ -22911,7 +22911,7 @@
         <v>49.52980426773144</v>
       </c>
       <c r="K292" t="n">
-        <v>5.136479152372653</v>
+        <v>5.136488424678554</v>
       </c>
       <c r="L292" t="n">
         <v>64.30555555555556</v>
@@ -22970,13 +22970,13 @@
         <v>1920.381740722656</v>
       </c>
       <c r="E293" t="n">
-        <v>1809.051086425781</v>
+        <v>1809.051087239583</v>
       </c>
       <c r="F293" t="n">
-        <v>1791.519638671875</v>
+        <v>1791.519639282227</v>
       </c>
       <c r="G293" t="n">
-        <v>1.642434830000949</v>
+        <v>1.642435040615631</v>
       </c>
       <c r="H293" t="n">
         <v>2046.900024414062</v>
@@ -23586,16 +23586,16 @@
         <v>1824.377993164062</v>
       </c>
       <c r="E301" t="n">
-        <v>1749.119825846354</v>
+        <v>1749.11982421875</v>
       </c>
       <c r="F301" t="n">
-        <v>1762.708652954102</v>
+        <v>1762.708649291992</v>
       </c>
       <c r="G301" t="n">
-        <v>-1.716960699536563</v>
+        <v>-1.716960569254544</v>
       </c>
       <c r="H301" t="n">
-        <v>2269.472253037084</v>
+        <v>2269.472002658311</v>
       </c>
       <c r="I301" t="n">
         <v>1353.205955540699</v>
@@ -23604,7 +23604,7 @@
         <v>46.68129535544045</v>
       </c>
       <c r="K301" t="n">
-        <v>14.33685450767357</v>
+        <v>14.33684189349806</v>
       </c>
       <c r="L301" t="n">
         <v>60.97222222222223</v>
@@ -24279,13 +24279,13 @@
         <v>5231.35576171875</v>
       </c>
       <c r="E310" t="n">
-        <v>5188.8761328125</v>
+        <v>5188.876126302083</v>
       </c>
       <c r="F310" t="n">
-        <v>5311.920812988281</v>
+        <v>5311.92080078125</v>
       </c>
       <c r="G310" t="n">
-        <v>0.6936375724211796</v>
+        <v>0.6936375740262735</v>
       </c>
       <c r="H310" t="n">
         <v>6175.521739453033</v>
@@ -25046,16 +25046,16 @@
         <v>762</v>
       </c>
       <c r="D320" t="n">
-        <v>775.6521630859374</v>
+        <v>775.6521655273438</v>
       </c>
       <c r="E320" t="n">
-        <v>739.5026928710937</v>
+        <v>739.5026953125</v>
       </c>
       <c r="F320" t="n">
-        <v>740.7939297485351</v>
+        <v>740.7939294433594</v>
       </c>
       <c r="G320" t="n">
-        <v>0.1944487168187514</v>
+        <v>0.1944488409674205</v>
       </c>
       <c r="H320" t="n">
         <v>837.8765073351432</v>
@@ -25286,7 +25286,7 @@
         <v>1504.623753662109</v>
       </c>
       <c r="G323" t="n">
-        <v>0.1852651672359373</v>
+        <v>0.1852652079514572</v>
       </c>
       <c r="H323" t="n">
         <v>1765.922465821425</v>
@@ -25437,13 +25437,13 @@
         <v>4223.270854492188</v>
       </c>
       <c r="F325" t="n">
-        <v>4282.448302001953</v>
+        <v>4282.448316650391</v>
       </c>
       <c r="G325" t="n">
-        <v>-0.6604758813353429</v>
+        <v>-0.6604757665730432</v>
       </c>
       <c r="H325" t="n">
-        <v>5143.904461376938</v>
+        <v>5143.90496192873</v>
       </c>
       <c r="I325" t="n">
         <v>3669.905008549105</v>
@@ -25452,7 +25452,7 @@
         <v>28.15591096653227</v>
       </c>
       <c r="K325" t="n">
-        <v>9.37030633957856</v>
+        <v>9.370316982370074</v>
       </c>
       <c r="L325" t="n">
         <v>52.5</v>
@@ -25742,13 +25742,13 @@
         <v>706.9836450195312</v>
       </c>
       <c r="E329" t="n">
-        <v>663.1683821614583</v>
+        <v>663.1683817545573</v>
       </c>
       <c r="F329" t="n">
         <v>671.1600549316406</v>
       </c>
       <c r="G329" t="n">
-        <v>0.8424217621912256</v>
+        <v>0.8424218546696727</v>
       </c>
       <c r="H329" t="n">
         <v>792.3323631991859</v>
@@ -26204,22 +26204,22 @@
         <v>346.7916577148437</v>
       </c>
       <c r="E335" t="n">
-        <v>340.3090171305338</v>
+        <v>340.3090165201823</v>
       </c>
       <c r="F335" t="n">
-        <v>334.895704498291</v>
+        <v>334.8957035827636</v>
       </c>
       <c r="G335" t="n">
-        <v>0.3032247725542225</v>
+        <v>0.303224681706582</v>
       </c>
       <c r="H335" t="n">
         <v>386.0870554430863</v>
       </c>
       <c r="I335" t="n">
-        <v>282.670901059285</v>
+        <v>282.6708709611926</v>
       </c>
       <c r="J335" t="n">
-        <v>21.53709013044658</v>
+        <v>21.53710307141417</v>
       </c>
       <c r="K335" t="n">
         <v>12.38162397367089</v>
@@ -27051,13 +27051,13 @@
         <v>2911.732436523438</v>
       </c>
       <c r="E346" t="n">
-        <v>2808.025812174479</v>
+        <v>2808.025813802083</v>
       </c>
       <c r="F346" t="n">
-        <v>2771.243059082031</v>
+        <v>2771.243055419922</v>
       </c>
       <c r="G346" t="n">
-        <v>-1.08134924814951</v>
+        <v>-1.081349421968814</v>
       </c>
       <c r="H346" t="n">
         <v>3415.14446256242</v>
@@ -27208,22 +27208,22 @@
         <v>1388.42851155599</v>
       </c>
       <c r="F348" t="n">
-        <v>1310.908576660156</v>
+        <v>1310.90857421875</v>
       </c>
       <c r="G348" t="n">
-        <v>2.579606825954017</v>
+        <v>2.579606389949518</v>
       </c>
       <c r="H348" t="n">
-        <v>1766.733188761222</v>
+        <v>1766.733060850261</v>
       </c>
       <c r="I348" t="n">
-        <v>894.2209017899434</v>
+        <v>894.2208429182053</v>
       </c>
       <c r="J348" t="n">
-        <v>49.80638149974889</v>
+        <v>49.80639136237077</v>
       </c>
       <c r="K348" t="n">
-        <v>31.88513145414607</v>
+        <v>31.88512190570145</v>
       </c>
       <c r="L348" t="n">
         <v>73.61111111111111</v>
@@ -27673,7 +27673,7 @@
         <v>44.42986679077148</v>
       </c>
       <c r="G354" t="n">
-        <v>-1.269204000982882</v>
+        <v>-1.269204252062572</v>
       </c>
       <c r="H354" t="n">
         <v>57.70003380709684</v>
@@ -28514,13 +28514,13 @@
         <v>496.3080352783203</v>
       </c>
       <c r="E365" t="n">
-        <v>488.0736673990885</v>
+        <v>488.0736678059896</v>
       </c>
       <c r="F365" t="n">
-        <v>492.9580834960938</v>
+        <v>492.958084564209</v>
       </c>
       <c r="G365" t="n">
-        <v>-0.2459668868821208</v>
+        <v>-0.2459669479533577</v>
       </c>
       <c r="H365" t="n">
         <v>561.4378970396333</v>
@@ -29056,10 +29056,10 @@
         <v>2522.332967122396</v>
       </c>
       <c r="F372" t="n">
-        <v>2592.119732666016</v>
+        <v>2592.119733886719</v>
       </c>
       <c r="G372" t="n">
-        <v>0.9173620527027859</v>
+        <v>0.9173619563451085</v>
       </c>
       <c r="H372" t="n">
         <v>2960.01877635178</v>
@@ -29974,25 +29974,25 @@
         <v>2352.10009765625</v>
       </c>
       <c r="D384" t="n">
-        <v>2260.417368164062</v>
+        <v>2260.41734375</v>
       </c>
       <c r="E384" t="n">
-        <v>2267.516888834635</v>
+        <v>2267.516849772136</v>
       </c>
       <c r="F384" t="n">
-        <v>2286.101973266601</v>
+        <v>2286.101940307617</v>
       </c>
       <c r="G384" t="n">
-        <v>0.5764315082190885</v>
+        <v>0.5764316246056111</v>
       </c>
       <c r="H384" t="n">
         <v>2765.379504159864</v>
       </c>
       <c r="I384" t="n">
-        <v>1963.170361427068</v>
+        <v>1963.170239604111</v>
       </c>
       <c r="J384" t="n">
-        <v>19.81130847688948</v>
+        <v>19.81131591168424</v>
       </c>
       <c r="K384" t="n">
         <v>17.5706555565142</v>
@@ -32829,13 +32829,13 @@
         <v>881.0550858561198</v>
       </c>
       <c r="F421" t="n">
-        <v>935.7610592651367</v>
+        <v>935.7610586547852</v>
       </c>
       <c r="G421" t="n">
-        <v>-2.317758479445908</v>
+        <v>-2.317758480922627</v>
       </c>
       <c r="H421" t="n">
-        <v>1304.859850069017</v>
+        <v>1304.859727076846</v>
       </c>
       <c r="I421" t="n">
         <v>734.1152411860135</v>
@@ -32844,7 +32844,7 @@
         <v>39.64429110038124</v>
       </c>
       <c r="K421" t="n">
-        <v>27.28476993548585</v>
+        <v>27.28475793800573</v>
       </c>
       <c r="L421" t="n">
         <v>41.25</v>
@@ -33448,7 +33448,7 @@
         <v>516.4328897094726</v>
       </c>
       <c r="G429" t="n">
-        <v>-1.024625422570247</v>
+        <v>-1.024625596235029</v>
       </c>
       <c r="H429" t="n">
         <v>750.0847124549373</v>
@@ -34135,16 +34135,16 @@
         <v>1111.951091308594</v>
       </c>
       <c r="E438" t="n">
-        <v>1081.739626057943</v>
+        <v>1081.739628092448</v>
       </c>
       <c r="F438" t="n">
-        <v>1090.43849029541</v>
+        <v>1090.438490600586</v>
       </c>
       <c r="G438" t="n">
-        <v>-1.36639575069174</v>
+        <v>-1.366395695860712</v>
       </c>
       <c r="H438" t="n">
-        <v>1341.921447537333</v>
+        <v>1341.921323996723</v>
       </c>
       <c r="I438" t="n">
         <v>885.652283987356</v>
@@ -34153,7 +34153,7 @@
         <v>23.38928816489412</v>
       </c>
       <c r="K438" t="n">
-        <v>22.79661306534124</v>
+        <v>22.79660176038117</v>
       </c>
       <c r="L438" t="n">
         <v>26.38888888888889</v>
@@ -35062,10 +35062,10 @@
         <v>159.5852546183268</v>
       </c>
       <c r="F450" t="n">
-        <v>154.4423838043213</v>
+        <v>154.4423841094971</v>
       </c>
       <c r="G450" t="n">
-        <v>1.273933340813049</v>
+        <v>1.273933591595089</v>
       </c>
       <c r="H450" t="n">
         <v>203.5447632528218</v>
@@ -35213,22 +35213,22 @@
         <v>418.4333111572266</v>
       </c>
       <c r="E452" t="n">
-        <v>434.2775122070312</v>
+        <v>434.2775115966797</v>
       </c>
       <c r="F452" t="n">
         <v>422.4203099060059</v>
       </c>
       <c r="G452" t="n">
-        <v>1.0611886863096</v>
+        <v>1.061188760095622</v>
       </c>
       <c r="H452" t="n">
         <v>484.7737901614043</v>
       </c>
       <c r="I452" t="n">
-        <v>349.5720248388532</v>
+        <v>349.5720548957738</v>
       </c>
       <c r="J452" t="n">
-        <v>14.71169644792205</v>
+        <v>14.71168658477568</v>
       </c>
       <c r="K452" t="n">
         <v>20.89121949162202</v>
@@ -35521,22 +35521,22 @@
         <v>241.9923602294922</v>
       </c>
       <c r="E456" t="n">
-        <v>227.0623474121094</v>
+        <v>227.0623477172851</v>
       </c>
       <c r="F456" t="n">
-        <v>228.3732853698731</v>
+        <v>228.373285446167</v>
       </c>
       <c r="G456" t="n">
-        <v>0.09498397775664635</v>
+        <v>0.09498407813803844</v>
       </c>
       <c r="H456" t="n">
         <v>286.0804190389319</v>
       </c>
       <c r="I456" t="n">
-        <v>171.952833032562</v>
+        <v>171.9528178807998</v>
       </c>
       <c r="J456" t="n">
-        <v>29.22148069881763</v>
+        <v>29.22149208527332</v>
       </c>
       <c r="K456" t="n">
         <v>28.74906524214291</v>
@@ -35758,7 +35758,7 @@
         <v>327.1692991638184</v>
       </c>
       <c r="G459" t="n">
-        <v>-0.5655886517533792</v>
+        <v>-0.5655887439788509</v>
       </c>
       <c r="H459" t="n">
         <v>391.6499938964844</v>
@@ -35983,16 +35983,16 @@
         <v>78.32427246093749</v>
       </c>
       <c r="E462" t="n">
-        <v>77.48818517049153</v>
+        <v>77.48818501790365</v>
       </c>
       <c r="F462" t="n">
-        <v>77.4134306716919</v>
+        <v>77.41343086242676</v>
       </c>
       <c r="G462" t="n">
-        <v>-0.8736356275715451</v>
+        <v>-0.8736355770181281</v>
       </c>
       <c r="H462" t="n">
-        <v>87.39771312453149</v>
+        <v>87.39772087555167</v>
       </c>
       <c r="I462" t="n">
         <v>71.42454681386315</v>
@@ -36001,7 +36001,7 @@
         <v>4.753901890074053</v>
       </c>
       <c r="K462" t="n">
-        <v>16.81063015371458</v>
+        <v>16.81064051327112</v>
       </c>
       <c r="L462" t="n">
         <v>40</v>
@@ -36060,16 +36060,16 @@
         <v>218.5812469482422</v>
       </c>
       <c r="E463" t="n">
-        <v>211.9720264689128</v>
+        <v>211.9720266723633</v>
       </c>
       <c r="F463" t="n">
-        <v>216.9518092346191</v>
+        <v>216.9518093109131</v>
       </c>
       <c r="G463" t="n">
-        <v>-1.064588279511147</v>
+        <v>-1.06458845124846</v>
       </c>
       <c r="H463" t="n">
-        <v>272.0997840702363</v>
+        <v>272.099752952214</v>
       </c>
       <c r="I463" t="n">
         <v>173.9540675101702</v>
@@ -36078,7 +36078,7 @@
         <v>24.74557399315376</v>
       </c>
       <c r="K463" t="n">
-        <v>25.39160556232087</v>
+        <v>25.39159122221841</v>
       </c>
       <c r="L463" t="n">
         <v>38.47222222222222</v>
@@ -36137,16 +36137,16 @@
         <v>5533.550712890625</v>
       </c>
       <c r="E464" t="n">
-        <v>5476.59654296875</v>
+        <v>5476.596549479166</v>
       </c>
       <c r="F464" t="n">
-        <v>5509.985437011719</v>
+        <v>5509.985451660156</v>
       </c>
       <c r="G464" t="n">
-        <v>0.03262667458947544</v>
+        <v>0.03262676317807855</v>
       </c>
       <c r="H464" t="n">
-        <v>5875.533923201399</v>
+        <v>5875.534417311879</v>
       </c>
       <c r="I464" t="n">
         <v>5065.93337960459</v>
@@ -36155,7 +36155,7 @@
         <v>5.015198609170035</v>
       </c>
       <c r="K464" t="n">
-        <v>10.44236697746992</v>
+        <v>10.44237626526088</v>
       </c>
       <c r="L464" t="n">
         <v>38.05555555555556</v>
@@ -36217,10 +36217,10 @@
         <v>1283.621469319661</v>
       </c>
       <c r="F465" t="n">
-        <v>1360.641666564941</v>
+        <v>1360.641667785645</v>
       </c>
       <c r="G465" t="n">
-        <v>-1.043136348852458</v>
+        <v>-1.043136084366436</v>
       </c>
       <c r="H465" t="n">
         <v>1729.008500794829</v>
@@ -36368,13 +36368,13 @@
         <v>350.1240020751953</v>
       </c>
       <c r="E467" t="n">
-        <v>344.5143798828125</v>
+        <v>344.5143782552083</v>
       </c>
       <c r="F467" t="n">
-        <v>344.5140760803222</v>
+        <v>344.5140737915039</v>
       </c>
       <c r="G467" t="n">
-        <v>-0.4105516252417507</v>
+        <v>-0.410551671885917</v>
       </c>
       <c r="H467" t="n">
         <v>381.3442016302781</v>
@@ -36445,13 +36445,13 @@
         <v>132303.960625</v>
       </c>
       <c r="E468" t="n">
-        <v>132927.5711458333</v>
+        <v>132927.5713541667</v>
       </c>
       <c r="F468" t="n">
-        <v>137564.330859375</v>
+        <v>137564.33109375</v>
       </c>
       <c r="G468" t="n">
-        <v>-1.922312355198608</v>
+        <v>-1.922311914953045</v>
       </c>
       <c r="H468" t="n">
         <v>163308.4863287346</v>
@@ -36596,16 +36596,16 @@
         <v>289.5</v>
       </c>
       <c r="D470" t="n">
-        <v>299.7629028320313</v>
+        <v>299.7629040527344</v>
       </c>
       <c r="E470" t="n">
-        <v>275.51560740153</v>
+        <v>275.5156079101562</v>
       </c>
       <c r="F470" t="n">
-        <v>293.545623550415</v>
+        <v>293.5456233215332</v>
       </c>
       <c r="G470" t="n">
-        <v>-1.583013292927093</v>
+        <v>-1.583013243793585</v>
       </c>
       <c r="H470" t="n">
         <v>411.0263372414121</v>
@@ -36990,7 +36990,7 @@
         <v>4792.96223022461</v>
       </c>
       <c r="G475" t="n">
-        <v>-2.091531996821483</v>
+        <v>-2.091532045650346</v>
       </c>
       <c r="H475" t="n">
         <v>6344.474916122625</v>
@@ -37067,7 +37067,7 @@
         <v>261.1450283050537</v>
       </c>
       <c r="G476" t="n">
-        <v>-1.815777283110143</v>
+        <v>-1.815777226782489</v>
       </c>
       <c r="H476" t="n">
         <v>347.6028003347344</v>
@@ -37834,13 +37834,13 @@
         <v>621.1822015380859</v>
       </c>
       <c r="F486" t="n">
-        <v>638.8529026794433</v>
+        <v>638.8529032897949</v>
       </c>
       <c r="G486" t="n">
-        <v>-1.712005657609461</v>
+        <v>-1.712005702149533</v>
       </c>
       <c r="H486" t="n">
-        <v>859.7877679261235</v>
+        <v>859.7877065596524</v>
       </c>
       <c r="I486" t="n">
         <v>502</v>
@@ -37849,7 +37849,7 @@
         <v>24.23307259244274</v>
       </c>
       <c r="K486" t="n">
-        <v>37.86382334129135</v>
+        <v>37.8638135014022</v>
       </c>
       <c r="L486" t="n">
         <v>44.58333333333334</v>
@@ -38222,7 +38222,7 @@
         <v>357.3649751281739</v>
       </c>
       <c r="G491" t="n">
-        <v>0.2552937695959656</v>
+        <v>0.2552938125123028</v>
       </c>
       <c r="H491" t="n">
         <v>414.3999938964844</v>
@@ -38613,10 +38613,10 @@
         <v>1224.72508309492</v>
       </c>
       <c r="I496" t="n">
-        <v>784.9092044208618</v>
+        <v>784.9091438882253</v>
       </c>
       <c r="J496" t="n">
-        <v>8.77691113622976</v>
+        <v>8.776919525166571</v>
       </c>
       <c r="K496" t="n">
         <v>43.44402677502656</v>
@@ -38758,10 +38758,10 @@
         <v>2653.279962565104</v>
       </c>
       <c r="F498" t="n">
-        <v>2726.519274902344</v>
+        <v>2726.519282226563</v>
       </c>
       <c r="G498" t="n">
-        <v>-1.622436296357399</v>
+        <v>-1.622436205408795</v>
       </c>
       <c r="H498" t="n">
         <v>3198.009229338596</v>
@@ -39060,16 +39060,16 @@
         <v>352</v>
       </c>
       <c r="D502" t="n">
-        <v>397.8544989013672</v>
+        <v>397.8544995117188</v>
       </c>
       <c r="E502" t="n">
-        <v>408.4564984130859</v>
+        <v>408.4564971923828</v>
       </c>
       <c r="F502" t="n">
-        <v>392.7343984985351</v>
+        <v>392.7343978881836</v>
       </c>
       <c r="G502" t="n">
-        <v>0.1553629435735671</v>
+        <v>0.1553627879213426</v>
       </c>
       <c r="H502" t="n">
         <v>476.8288845013619</v>
@@ -39377,7 +39377,7 @@
         <v>3658.214260253906</v>
       </c>
       <c r="G506" t="n">
-        <v>-1.586558140601946</v>
+        <v>-1.586558172920349</v>
       </c>
       <c r="H506" t="n">
         <v>4673.303227225188</v>
@@ -40908,25 +40908,25 @@
         <v>509.3500061035156</v>
       </c>
       <c r="D526" t="n">
-        <v>532.7692651367188</v>
+        <v>532.7692602539063</v>
       </c>
       <c r="E526" t="n">
-        <v>517.5088004557292</v>
+        <v>517.5087990315756</v>
       </c>
       <c r="F526" t="n">
-        <v>555.1336294555664</v>
+        <v>555.1336280822754</v>
       </c>
       <c r="G526" t="n">
-        <v>-3.640954042690447</v>
+        <v>-3.640954255542128</v>
       </c>
       <c r="H526" t="n">
         <v>872.0425606177564</v>
       </c>
       <c r="I526" t="n">
-        <v>406.117116732523</v>
+        <v>406.1171468902937</v>
       </c>
       <c r="J526" t="n">
-        <v>25.41948741327835</v>
+        <v>25.41947809977811</v>
       </c>
       <c r="K526" t="n">
         <v>71.20694025093042</v>
@@ -41068,10 +41068,10 @@
         <v>852.0646655273438</v>
       </c>
       <c r="F528" t="n">
-        <v>863.5024591064453</v>
+        <v>863.5024584960937</v>
       </c>
       <c r="G528" t="n">
-        <v>-0.2097396859188416</v>
+        <v>-0.2097397212603158</v>
       </c>
       <c r="H528" t="n">
         <v>962.6932158005569</v>
@@ -41764,7 +41764,7 @@
         <v>390.4115493774414</v>
       </c>
       <c r="G537" t="n">
-        <v>-1.814382755196342</v>
+        <v>-1.814382792874802</v>
       </c>
       <c r="H537" t="n">
         <v>483.5386775606495</v>
@@ -42220,16 +42220,16 @@
         <v>124.6036000061035</v>
       </c>
       <c r="E543" t="n">
-        <v>123.7624845886231</v>
+        <v>123.7624847920736</v>
       </c>
       <c r="F543" t="n">
-        <v>126.8840169143677</v>
+        <v>126.8840163421631</v>
       </c>
       <c r="G543" t="n">
-        <v>-0.9122147769826672</v>
+        <v>-0.9122148991326906</v>
       </c>
       <c r="H543" t="n">
-        <v>155.8999783750524</v>
+        <v>155.8999606999571</v>
       </c>
       <c r="I543" t="n">
         <v>112.8155071321618</v>
@@ -42238,7 +42238,7 @@
         <v>7.963883820573336</v>
       </c>
       <c r="K543" t="n">
-        <v>27.99669496625883</v>
+        <v>27.99668045468675</v>
       </c>
       <c r="L543" t="n">
         <v>31.38888888888889</v>
@@ -42303,7 +42303,7 @@
         <v>579.3138049316407</v>
       </c>
       <c r="G544" t="n">
-        <v>-0.5671520063829649</v>
+        <v>-0.5671523188809369</v>
       </c>
       <c r="H544" t="n">
         <v>732.5560380476754</v>
@@ -42836,13 +42836,13 @@
         <v>39288.1</v>
       </c>
       <c r="E551" t="n">
-        <v>36328.75600260417</v>
+        <v>36328.75604166667</v>
       </c>
       <c r="F551" t="n">
         <v>36363.23086914062</v>
       </c>
       <c r="G551" t="n">
-        <v>-0.7971306869307027</v>
+        <v>-0.7971306340720408</v>
       </c>
       <c r="H551" t="n">
         <v>46547.97355089381</v>
@@ -43144,16 +43144,16 @@
         <v>197.5735784912109</v>
       </c>
       <c r="E555" t="n">
-        <v>194.4699740600586</v>
+        <v>194.4699739583333</v>
       </c>
       <c r="F555" t="n">
-        <v>199.8766606903076</v>
+        <v>199.8766605377197</v>
       </c>
       <c r="G555" t="n">
-        <v>-1.70658024760868</v>
+        <v>-1.706580212010489</v>
       </c>
       <c r="H555" t="n">
-        <v>239.2186728978909</v>
+        <v>239.2186883393384</v>
       </c>
       <c r="I555" t="n">
         <v>156.7443123050878</v>
@@ -43162,7 +43162,7 @@
         <v>16.89738085736687</v>
       </c>
       <c r="K555" t="n">
-        <v>30.5565019242845</v>
+        <v>30.55651035164237</v>
       </c>
       <c r="L555" t="n">
         <v>26.52777777777778</v>
@@ -43689,7 +43689,7 @@
         <v>1915.293689575195</v>
       </c>
       <c r="G562" t="n">
-        <v>-1.622592523687338</v>
+        <v>-1.622592462004346</v>
       </c>
       <c r="H562" t="n">
         <v>2484.339731207416</v>
@@ -44151,10 +44151,10 @@
         <v>443.9974435424805</v>
       </c>
       <c r="G568" t="n">
-        <v>-0.8639067948420953</v>
+        <v>-0.8639068286176999</v>
       </c>
       <c r="H568" t="n">
-        <v>566.8733711713968</v>
+        <v>566.8734333795863</v>
       </c>
       <c r="I568" t="n">
         <v>394.4382907843191</v>
@@ -44163,7 +44163,7 @@
         <v>6.873495206243674</v>
       </c>
       <c r="K568" t="n">
-        <v>34.47358263233995</v>
+        <v>34.47359738935367</v>
       </c>
       <c r="L568" t="n">
         <v>22.63888888888889</v>
@@ -44453,13 +44453,13 @@
         <v>95.74608688354492</v>
       </c>
       <c r="E572" t="n">
-        <v>94.46557200113932</v>
+        <v>94.4655717976888</v>
       </c>
       <c r="F572" t="n">
-        <v>98.78023910522461</v>
+        <v>98.78023891448974</v>
       </c>
       <c r="G572" t="n">
-        <v>-2.286222623147038</v>
+        <v>-2.28622281182268</v>
       </c>
       <c r="H572" t="n">
         <v>124.8273096544699</v>
@@ -44539,7 +44539,7 @@
         <v>-2.456033281118153</v>
       </c>
       <c r="H573" t="n">
-        <v>294.6532543042141</v>
+        <v>294.6532203195111</v>
       </c>
       <c r="I573" t="n">
         <v>213.7350670269712</v>
@@ -44548,7 +44548,7 @@
         <v>5.803882598783772</v>
       </c>
       <c r="K573" t="n">
-        <v>30.29683165272965</v>
+        <v>30.29681662455992</v>
       </c>
       <c r="L573" t="n">
         <v>20.69444444444444</v>
@@ -44610,13 +44610,13 @@
         <v>234.7162721761068</v>
       </c>
       <c r="F574" t="n">
-        <v>241.5537034606934</v>
+        <v>241.5537037658691</v>
       </c>
       <c r="G574" t="n">
-        <v>-2.343318753292833</v>
+        <v>-2.34331869015818</v>
       </c>
       <c r="H574" t="n">
-        <v>308.0746845932235</v>
+        <v>308.0746526166167</v>
       </c>
       <c r="I574" t="n">
         <v>185.2067002350832</v>
@@ -44625,7 +44625,7 @@
         <v>19.03457403756825</v>
       </c>
       <c r="K574" t="n">
-        <v>39.74175596985739</v>
+        <v>39.74174146536416</v>
       </c>
       <c r="L574" t="n">
         <v>20.13888888888889</v>
@@ -44992,16 +44992,16 @@
         <v>2242.093479003906</v>
       </c>
       <c r="E579" t="n">
-        <v>2393.162985839844</v>
+        <v>2393.162966308594</v>
       </c>
       <c r="F579" t="n">
-        <v>2567.009053344726</v>
+        <v>2567.009048461914</v>
       </c>
       <c r="G579" t="n">
-        <v>-2.333677207594675</v>
+        <v>-2.333677257289979</v>
       </c>
       <c r="H579" t="n">
-        <v>3287.161645949698</v>
+        <v>3287.161392369851</v>
       </c>
       <c r="I579" t="n">
         <v>1966.020518717901</v>
@@ -45010,7 +45010,7 @@
         <v>19.12388389147057</v>
       </c>
       <c r="K579" t="n">
-        <v>40.35703014302723</v>
+        <v>40.35701931553588</v>
       </c>
       <c r="L579" t="n">
         <v>19.02777777777778</v>
@@ -45614,7 +45614,7 @@
         <v>1295.081230163574</v>
       </c>
       <c r="G587" t="n">
-        <v>-2.49399697010404</v>
+        <v>-2.493996880490068</v>
       </c>
       <c r="H587" t="n">
         <v>1691.399159307065</v>
@@ -45762,22 +45762,22 @@
         <v>844.4441674804688</v>
       </c>
       <c r="E589" t="n">
-        <v>958.7904964192709</v>
+        <v>958.7904947916667</v>
       </c>
       <c r="F589" t="n">
-        <v>926.4151766967774</v>
+        <v>926.4151742553711</v>
       </c>
       <c r="G589" t="n">
-        <v>-0.3627908658180523</v>
+        <v>-0.3627906378497081</v>
       </c>
       <c r="H589" t="n">
         <v>1282.80960014975</v>
       </c>
       <c r="I589" t="n">
-        <v>743.4273285628773</v>
+        <v>743.4272688553443</v>
       </c>
       <c r="J589" t="n">
-        <v>6.674850025491708</v>
+        <v>6.67485859296344</v>
       </c>
       <c r="K589" t="n">
         <v>61.7564617483654</v>
@@ -46298,16 +46298,16 @@
         <v>681.5999755859375</v>
       </c>
       <c r="D596" t="n">
-        <v>678.54080078125</v>
+        <v>678.5407971191406</v>
       </c>
       <c r="E596" t="n">
-        <v>694.9209297688802</v>
+        <v>694.9209261067708</v>
       </c>
       <c r="F596" t="n">
-        <v>750.2772933959961</v>
+        <v>750.2772900390624</v>
       </c>
       <c r="G596" t="n">
-        <v>-5.122905660235566</v>
+        <v>-5.122905901668484</v>
       </c>
       <c r="H596" t="n">
         <v>1223.985164326833</v>
@@ -47231,7 +47231,7 @@
         <v>159.9045571899414</v>
       </c>
       <c r="G608" t="n">
-        <v>-0.711225015242356</v>
+        <v>-0.7112250622782756</v>
       </c>
       <c r="H608" t="n">
         <v>197.1955548334318</v>
@@ -47767,13 +47767,13 @@
         <v>1080.962776692708</v>
       </c>
       <c r="F615" t="n">
-        <v>1112.72266784668</v>
+        <v>1112.722667236328</v>
       </c>
       <c r="G615" t="n">
-        <v>-1.880130670532776</v>
+        <v>-1.880130460309115</v>
       </c>
       <c r="H615" t="n">
-        <v>1400.476774401248</v>
+        <v>1400.476649260813</v>
       </c>
       <c r="I615" t="n">
         <v>941.5197177909594</v>
@@ -47782,7 +47782,7 @@
         <v>9.227667247048842</v>
       </c>
       <c r="K615" t="n">
-        <v>36.18015763848111</v>
+        <v>36.18014547002204</v>
       </c>
       <c r="L615" t="n">
         <v>24.16666666666667</v>
@@ -48075,13 +48075,13 @@
         <v>1254.581009114583</v>
       </c>
       <c r="F619" t="n">
-        <v>1295.099750976563</v>
+        <v>1295.099752197266</v>
       </c>
       <c r="G619" t="n">
-        <v>-1.601896203806652</v>
+        <v>-1.601896065431008</v>
       </c>
       <c r="H619" t="n">
-        <v>1608.140938678776</v>
+        <v>1608.140814494163</v>
       </c>
       <c r="I619" t="n">
         <v>1123.599975585938</v>
@@ -48090,7 +48090,7 @@
         <v>8.83766918705582</v>
       </c>
       <c r="K619" t="n">
-        <v>31.50224111323381</v>
+        <v>31.50223095830613</v>
       </c>
       <c r="L619" t="n">
         <v>22.36111111111111</v>
@@ -48152,10 +48152,10 @@
         <v>33.65268576304118</v>
       </c>
       <c r="F620" t="n">
-        <v>34.42287888526916</v>
+        <v>34.42287880897522</v>
       </c>
       <c r="G620" t="n">
-        <v>-2.090410374498453</v>
+        <v>-2.090410485268679</v>
       </c>
       <c r="H620" t="n">
         <v>40.26070662850351</v>
@@ -48457,13 +48457,13 @@
         <v>2030.052126464844</v>
       </c>
       <c r="E624" t="n">
-        <v>2033.70548421224</v>
+        <v>2033.705482584635</v>
       </c>
       <c r="F624" t="n">
         <v>2097.717621459961</v>
       </c>
       <c r="G624" t="n">
-        <v>-0.6658903990536147</v>
+        <v>-0.6658905138927307</v>
       </c>
       <c r="H624" t="n">
         <v>2486.766809421043</v>
@@ -49227,22 +49227,22 @@
         <v>461.2881726074219</v>
       </c>
       <c r="E634" t="n">
-        <v>468.0864721679687</v>
+        <v>468.0864727783203</v>
       </c>
       <c r="F634" t="n">
-        <v>470.4060908508301</v>
+        <v>470.4060914611816</v>
       </c>
       <c r="G634" t="n">
-        <v>-0.5893132678478352</v>
+        <v>-0.589313202975128</v>
       </c>
       <c r="H634" t="n">
         <v>555.1842484654879</v>
       </c>
       <c r="I634" t="n">
-        <v>379.7398698331913</v>
+        <v>379.7399306767125</v>
       </c>
       <c r="J634" t="n">
-        <v>9.021999765749689</v>
+        <v>9.021982297788544</v>
       </c>
       <c r="K634" t="n">
         <v>34.10247547475554</v>
@@ -49310,10 +49310,10 @@
         <v>2057.543096313477</v>
       </c>
       <c r="G635" t="n">
-        <v>-1.165577070268842</v>
+        <v>-1.165577128222051</v>
       </c>
       <c r="H635" t="n">
-        <v>2448.345231432346</v>
+        <v>2448.345479475883</v>
       </c>
       <c r="I635" t="n">
         <v>1761.237851420491</v>
@@ -49322,7 +49322,7 @@
         <v>3.728183160531828</v>
       </c>
       <c r="K635" t="n">
-        <v>34.01637739961159</v>
+        <v>34.01639097690283</v>
       </c>
       <c r="L635" t="n">
         <v>16.80555555555556</v>
@@ -49381,13 +49381,13 @@
         <v>7633.55123046875</v>
       </c>
       <c r="E636" t="n">
-        <v>7840.054182942708</v>
+        <v>7840.054169921875</v>
       </c>
       <c r="F636" t="n">
-        <v>7879.739538574218</v>
+        <v>7879.739536132813</v>
       </c>
       <c r="G636" t="n">
-        <v>-1.759940512023872</v>
+        <v>-1.759940482657196</v>
       </c>
       <c r="H636" t="n">
         <v>10437.38206257999</v>
@@ -49461,10 +49461,10 @@
         <v>538.5283217366537</v>
       </c>
       <c r="F637" t="n">
-        <v>541.351524810791</v>
+        <v>541.3515257263184</v>
       </c>
       <c r="G637" t="n">
-        <v>-1.384311734135102</v>
+        <v>-1.384311841472352</v>
       </c>
       <c r="H637" t="n">
         <v>653.9340000086492</v>
@@ -49541,7 +49541,7 @@
         <v>1817.083735961914</v>
       </c>
       <c r="G638" t="n">
-        <v>-2.069892919986294</v>
+        <v>-2.069892984413246</v>
       </c>
       <c r="H638" t="n">
         <v>2057.089271774458</v>
@@ -49618,7 +49618,7 @@
         <v>2220.435512695312</v>
       </c>
       <c r="G639" t="n">
-        <v>-1.925966287253134</v>
+        <v>-1.92596649876754</v>
       </c>
       <c r="H639" t="n">
         <v>2701.07684267753</v>
@@ -50542,7 +50542,7 @@
         <v>304.9063842010498</v>
       </c>
       <c r="G651" t="n">
-        <v>-3.302902590991774</v>
+        <v>-3.302902684577669</v>
       </c>
       <c r="H651" t="n">
         <v>398.6210131186603</v>
@@ -51152,16 +51152,16 @@
         <v>68.75150421142578</v>
       </c>
       <c r="E659" t="n">
-        <v>71.57847864786784</v>
+        <v>71.57847880045573</v>
       </c>
       <c r="F659" t="n">
         <v>72.51883171081543</v>
       </c>
       <c r="G659" t="n">
-        <v>-2.823841955152917</v>
+        <v>-2.823841905478974</v>
       </c>
       <c r="H659" t="n">
-        <v>97.92876001560526</v>
+        <v>97.9287679734358</v>
       </c>
       <c r="I659" t="n">
         <v>62.68610889438828</v>
@@ -51170,7 +51170,7 @@
         <v>3.499799872290499</v>
       </c>
       <c r="K659" t="n">
-        <v>50.93829248034722</v>
+        <v>50.93830474580787</v>
       </c>
       <c r="L659" t="n">
         <v>10.83333333333333</v>
@@ -51383,16 +51383,16 @@
         <v>1020.671945800781</v>
       </c>
       <c r="E662" t="n">
-        <v>1057.369074707031</v>
+        <v>1057.369073893229</v>
       </c>
       <c r="F662" t="n">
-        <v>1084.288985595703</v>
+        <v>1084.288984375</v>
       </c>
       <c r="G662" t="n">
-        <v>-1.284895803355413</v>
+        <v>-1.284895914489836</v>
       </c>
       <c r="H662" t="n">
-        <v>1284.135346691241</v>
+        <v>1284.135475005729</v>
       </c>
       <c r="I662" t="n">
         <v>902.8120757721283</v>
@@ -51401,7 +51401,7 @@
         <v>1.349995702865181</v>
       </c>
       <c r="K662" t="n">
-        <v>40.34266084057276</v>
+        <v>40.34267486401415</v>
       </c>
       <c r="L662" t="n">
         <v>10.41666666666667</v>
@@ -51620,7 +51620,7 @@
         <v>458.3298724365234</v>
       </c>
       <c r="G665" t="n">
-        <v>-2.131432218399554</v>
+        <v>-2.131432377839948</v>
       </c>
       <c r="H665" t="n">
         <v>566.6192163890048</v>
@@ -52313,7 +52313,7 @@
         <v>1775.973361206055</v>
       </c>
       <c r="G674" t="n">
-        <v>-3.833689935561557</v>
+        <v>-3.833689967344167</v>
       </c>
       <c r="H674" t="n">
         <v>2504.019782423858</v>
@@ -52929,7 +52929,7 @@
         <v>102.7890229797363</v>
       </c>
       <c r="G682" t="n">
-        <v>-3.555969536378656</v>
+        <v>-3.555969432820261</v>
       </c>
       <c r="H682" t="n">
         <v>135.7285614195044</v>
@@ -53394,7 +53394,7 @@
         <v>-2.249582865733035</v>
       </c>
       <c r="H688" t="n">
-        <v>372.3009385265751</v>
+        <v>372.3009694554414</v>
       </c>
       <c r="I688" t="n">
         <v>218.8999938964844</v>
@@ -53403,7 +53403,7 @@
         <v>9.195982386519287</v>
       </c>
       <c r="K688" t="n">
-        <v>55.75490123745139</v>
+        <v>55.75491417677549</v>
       </c>
       <c r="L688" t="n">
         <v>5.277777777777778</v>
@@ -53853,7 +53853,7 @@
         <v>562.944718170166</v>
       </c>
       <c r="G694" t="n">
-        <v>-4.765585083896672</v>
+        <v>-4.76558498556302</v>
       </c>
       <c r="H694" t="n">
         <v>845.3898333433813</v>
@@ -54078,13 +54078,13 @@
         <v>228.4416284179688</v>
       </c>
       <c r="E697" t="n">
-        <v>264.495295715332</v>
+        <v>264.4952955118815</v>
       </c>
       <c r="F697" t="n">
         <v>280.2781676483154</v>
       </c>
       <c r="G697" t="n">
-        <v>-3.808239432492699</v>
+        <v>-3.808239331744667</v>
       </c>
       <c r="H697" t="n">
         <v>398.2045017598045</v>
@@ -55310,13 +55310,13 @@
         <v>369.1592663574219</v>
       </c>
       <c r="E713" t="n">
-        <v>437.2381247965495</v>
+        <v>437.2381235758464</v>
       </c>
       <c r="F713" t="n">
-        <v>464.7286680603027</v>
+        <v>464.7286674499512</v>
       </c>
       <c r="G713" t="n">
-        <v>-5.137508962075077</v>
+        <v>-5.13750908666275</v>
       </c>
       <c r="H713" t="n">
         <v>606.8956852082865</v>
@@ -55396,7 +55396,7 @@
         <v>-5.207928502502379</v>
       </c>
       <c r="H714" t="n">
-        <v>1343.927068287785</v>
+        <v>1343.927192495164</v>
       </c>
       <c r="I714" t="n">
         <v>680.1500244140625</v>
@@ -55405,7 +55405,7 @@
         <v>1.154153540272262</v>
       </c>
       <c r="K714" t="n">
-        <v>95.33823666973622</v>
+        <v>95.33825472313431</v>
       </c>
       <c r="L714" t="n">
         <v>1.388888888888889</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -2180,22 +2180,22 @@
         <v>1244.952482910156</v>
       </c>
       <c r="E23" t="n">
-        <v>1064.65235555013</v>
+        <v>1064.652354736328</v>
       </c>
       <c r="F23" t="n">
-        <v>1007.846485900879</v>
+        <v>1007.846486206055</v>
       </c>
       <c r="G23" t="n">
-        <v>5.66373802336726</v>
+        <v>5.663737920133927</v>
       </c>
       <c r="H23" t="n">
         <v>1489.699951171875</v>
       </c>
       <c r="I23" t="n">
-        <v>651.3127246301497</v>
+        <v>651.3127841620155</v>
       </c>
       <c r="J23" t="n">
-        <v>122.96508209578</v>
+        <v>122.9650617161289</v>
       </c>
       <c r="K23" t="n">
         <v>2.582289027742957</v>
@@ -3800,19 +3800,19 @@
         <v>620.3661358642578</v>
       </c>
       <c r="F44" t="n">
-        <v>585.2124830627441</v>
+        <v>585.2124824523926</v>
       </c>
       <c r="G44" t="n">
-        <v>6.558630768571772</v>
+        <v>6.558630746254512</v>
       </c>
       <c r="H44" t="n">
         <v>844</v>
       </c>
       <c r="I44" t="n">
-        <v>399.8349725758499</v>
+        <v>399.8350028638013</v>
       </c>
       <c r="J44" t="n">
-        <v>97.33141273686969</v>
+        <v>97.33139778879307</v>
       </c>
       <c r="K44" t="n">
         <v>6.970849176172367</v>
@@ -4028,13 +4028,13 @@
         <v>316.9620193481445</v>
       </c>
       <c r="E47" t="n">
-        <v>240.5445523071289</v>
+        <v>240.5445524088542</v>
       </c>
       <c r="F47" t="n">
-        <v>230.3682939910889</v>
+        <v>230.3682941436768</v>
       </c>
       <c r="G47" t="n">
-        <v>6.424912050435116</v>
+        <v>6.424911970884861</v>
       </c>
       <c r="H47" t="n">
         <v>388.75</v>
@@ -5648,10 +5648,10 @@
         <v>76.4991712697347</v>
       </c>
       <c r="F68" t="n">
-        <v>72.14712705612183</v>
+        <v>72.14712699890137</v>
       </c>
       <c r="G68" t="n">
-        <v>3.875464541159013</v>
+        <v>3.875464344671586</v>
       </c>
       <c r="H68" t="n">
         <v>94.5</v>
@@ -6415,22 +6415,22 @@
         <v>10869.38630859375</v>
       </c>
       <c r="E78" t="n">
-        <v>10494.66207682292</v>
+        <v>10494.66203776042</v>
       </c>
       <c r="F78" t="n">
-        <v>10131.41168945313</v>
+        <v>10131.41166503906</v>
       </c>
       <c r="G78" t="n">
-        <v>3.329381326948488</v>
+        <v>3.329381566796807</v>
       </c>
       <c r="H78" t="n">
         <v>12865.82946046676</v>
       </c>
       <c r="I78" t="n">
-        <v>6492.523033421498</v>
+        <v>6492.522559926718</v>
       </c>
       <c r="J78" t="n">
-        <v>79.49878560320568</v>
+        <v>79.49879869391691</v>
       </c>
       <c r="K78" t="n">
         <v>10.3983993518685</v>
@@ -8038,7 +8038,7 @@
         <v>470.4523384094238</v>
       </c>
       <c r="G99" t="n">
-        <v>3.512231272641619</v>
+        <v>3.512231307394242</v>
       </c>
       <c r="H99" t="n">
         <v>662</v>
@@ -9039,7 +9039,7 @@
         <v>2996.056387939453</v>
       </c>
       <c r="G112" t="n">
-        <v>4.308208353776966</v>
+        <v>4.308208398106905</v>
       </c>
       <c r="H112" t="n">
         <v>3796</v>
@@ -10265,22 +10265,22 @@
         <v>1816.887590332031</v>
       </c>
       <c r="E128" t="n">
-        <v>1586.394236653646</v>
+        <v>1586.39423828125</v>
       </c>
       <c r="F128" t="n">
-        <v>1550.48192199707</v>
+        <v>1550.481926879883</v>
       </c>
       <c r="G128" t="n">
-        <v>2.695030399118203</v>
+        <v>2.69503034888654</v>
       </c>
       <c r="H128" t="n">
         <v>1988.900024414062</v>
       </c>
       <c r="I128" t="n">
-        <v>1266.161452106784</v>
+        <v>1266.16157090969</v>
       </c>
       <c r="J128" t="n">
-        <v>48.28282735001928</v>
+        <v>48.28281343676275</v>
       </c>
       <c r="K128" t="n">
         <v>5.933423404211058</v>
@@ -10961,10 +10961,10 @@
         <v>1811.279212239583</v>
       </c>
       <c r="F137" t="n">
-        <v>1650.450574951172</v>
+        <v>1650.450571289063</v>
       </c>
       <c r="G137" t="n">
-        <v>8.203093357531266</v>
+        <v>8.203093442171184</v>
       </c>
       <c r="H137" t="n">
         <v>2714.261178227147</v>
@@ -11195,16 +11195,16 @@
         <v>1849.530582885742</v>
       </c>
       <c r="G140" t="n">
-        <v>9.407025511910039</v>
+        <v>9.407025472408947</v>
       </c>
       <c r="H140" t="n">
         <v>2983.800048828125</v>
       </c>
       <c r="I140" t="n">
-        <v>1175.257587358084</v>
+        <v>1175.257470329055</v>
       </c>
       <c r="J140" t="n">
-        <v>108.8138059310841</v>
+        <v>108.8138267242104</v>
       </c>
       <c r="K140" t="n">
         <v>21.58428467028532</v>
@@ -12196,16 +12196,16 @@
         <v>989.3037023925781</v>
       </c>
       <c r="G153" t="n">
-        <v>3.989424581315903</v>
+        <v>3.989424547958009</v>
       </c>
       <c r="H153" t="n">
         <v>1153.699951171875</v>
       </c>
       <c r="I153" t="n">
-        <v>577.0989733310039</v>
+        <v>577.0990341682009</v>
       </c>
       <c r="J153" t="n">
-        <v>80.38500293829472</v>
+        <v>80.38498392228999</v>
       </c>
       <c r="K153" t="n">
         <v>10.82612403188041</v>
@@ -12735,7 +12735,7 @@
         <v>1000.267896728516</v>
       </c>
       <c r="G160" t="n">
-        <v>3.630223681663547</v>
+        <v>3.630223812722466</v>
       </c>
       <c r="H160" t="n">
         <v>1269.5</v>
@@ -13117,10 +13117,10 @@
         <v>1130.350380452474</v>
       </c>
       <c r="F165" t="n">
-        <v>1094.048709716797</v>
+        <v>1094.048710327148</v>
       </c>
       <c r="G165" t="n">
-        <v>2.065635616924477</v>
+        <v>2.065635528572929</v>
       </c>
       <c r="H165" t="n">
         <v>1596.696405272527</v>
@@ -13197,7 +13197,7 @@
         <v>1516.535418701172</v>
       </c>
       <c r="G166" t="n">
-        <v>0.7568166133281151</v>
+        <v>0.7568164498964025</v>
       </c>
       <c r="H166" t="n">
         <v>2021.199951171875</v>
@@ -14269,13 +14269,13 @@
         <v>308.8497998046875</v>
       </c>
       <c r="E180" t="n">
-        <v>294.3754621378581</v>
+        <v>294.3754627482097</v>
       </c>
       <c r="F180" t="n">
-        <v>283.5916653442383</v>
+        <v>283.5916655731201</v>
       </c>
       <c r="G180" t="n">
-        <v>1.425839683549968</v>
+        <v>1.425839516330418</v>
       </c>
       <c r="H180" t="n">
         <v>359.3387168134344</v>
@@ -15039,13 +15039,13 @@
         <v>1831.552009277344</v>
       </c>
       <c r="E190" t="n">
-        <v>1670.999096679687</v>
+        <v>1670.999095865885</v>
       </c>
       <c r="F190" t="n">
-        <v>1677.384904174805</v>
+        <v>1677.384903564453</v>
       </c>
       <c r="G190" t="n">
-        <v>1.132856229475299</v>
+        <v>1.132856155459816</v>
       </c>
       <c r="H190" t="n">
         <v>1952.5</v>
@@ -15809,13 +15809,13 @@
         <v>1855.686647949219</v>
       </c>
       <c r="E200" t="n">
-        <v>1681.45116780599</v>
+        <v>1681.451168619792</v>
       </c>
       <c r="F200" t="n">
-        <v>1669.113462524414</v>
+        <v>1669.113461914063</v>
       </c>
       <c r="G200" t="n">
-        <v>0.8247414978973078</v>
+        <v>0.8247416097205917</v>
       </c>
       <c r="H200" t="n">
         <v>1983.954544928268</v>
@@ -17201,7 +17201,7 @@
         <v>361.4543772888184</v>
       </c>
       <c r="G218" t="n">
-        <v>4.819079270377769</v>
+        <v>4.819079223996026</v>
       </c>
       <c r="H218" t="n">
         <v>443.3731066930094</v>
@@ -17891,19 +17891,19 @@
         <v>719.4185656738281</v>
       </c>
       <c r="F227" t="n">
-        <v>671.5628533935546</v>
+        <v>671.5628526306152</v>
       </c>
       <c r="G227" t="n">
-        <v>3.08295896575197</v>
+        <v>3.082958969362393</v>
       </c>
       <c r="H227" t="n">
         <v>1093.53919041171</v>
       </c>
       <c r="I227" t="n">
-        <v>491.2850236715819</v>
+        <v>491.2850813456647</v>
       </c>
       <c r="J227" t="n">
-        <v>54.78794906546609</v>
+        <v>54.78793089423857</v>
       </c>
       <c r="K227" t="n">
         <v>43.80158759389907</v>
@@ -18972,7 +18972,7 @@
         <v>595.9170075988769</v>
       </c>
       <c r="G241" t="n">
-        <v>2.828381663215995</v>
+        <v>2.828381636141519</v>
       </c>
       <c r="H241" t="n">
         <v>741</v>
@@ -19197,13 +19197,13 @@
         <v>4683.6165625</v>
       </c>
       <c r="E244" t="n">
-        <v>4350.851041666667</v>
+        <v>4350.851043294271</v>
       </c>
       <c r="F244" t="n">
-        <v>4358.652951660156</v>
+        <v>4358.652979736328</v>
       </c>
       <c r="G244" t="n">
-        <v>0.542830480433576</v>
+        <v>0.5428304202953704</v>
       </c>
       <c r="H244" t="n">
         <v>5149.89990234375</v>
@@ -19588,7 +19588,7 @@
         <v>1487.232166137695</v>
       </c>
       <c r="G249" t="n">
-        <v>1.614137125322479</v>
+        <v>1.614137167697471</v>
       </c>
       <c r="H249" t="n">
         <v>1807.040094106148</v>
@@ -19659,13 +19659,13 @@
         <v>1151.590783691406</v>
       </c>
       <c r="E250" t="n">
-        <v>1101.543180338542</v>
+        <v>1101.543179931641</v>
       </c>
       <c r="F250" t="n">
-        <v>1065.962764587402</v>
+        <v>1065.962762451172</v>
       </c>
       <c r="G250" t="n">
-        <v>1.877828789253977</v>
+        <v>1.877828971374473</v>
       </c>
       <c r="H250" t="n">
         <v>1238.748718225596</v>
@@ -19819,7 +19819,7 @@
         <v>675.7994026184082</v>
       </c>
       <c r="G252" t="n">
-        <v>0.04903088586154514</v>
+        <v>0.04903084065950303</v>
       </c>
       <c r="H252" t="n">
         <v>965.127357372077</v>
@@ -20897,7 +20897,7 @@
         <v>164.5688024902344</v>
       </c>
       <c r="G266" t="n">
-        <v>-0.1402571589651957</v>
+        <v>-0.1402572051951378</v>
       </c>
       <c r="H266" t="n">
         <v>181.8519567776652</v>
@@ -21199,13 +21199,13 @@
         <v>1200.318005371094</v>
       </c>
       <c r="E270" t="n">
-        <v>1144.464964599609</v>
+        <v>1144.464966227214</v>
       </c>
       <c r="F270" t="n">
-        <v>1169.292454528809</v>
+        <v>1169.29245880127</v>
       </c>
       <c r="G270" t="n">
-        <v>0.1195442044929607</v>
+        <v>0.1195442563789006</v>
       </c>
       <c r="H270" t="n">
         <v>1378.852549646065</v>
@@ -21750,10 +21750,10 @@
         <v>758.8333740234375</v>
       </c>
       <c r="I277" t="n">
-        <v>238.6845018119064</v>
+        <v>238.684486798652</v>
       </c>
       <c r="J277" t="n">
-        <v>118.552113963874</v>
+        <v>118.5521277108021</v>
       </c>
       <c r="K277" t="n">
         <v>45.46790731502188</v>
@@ -22046,25 +22046,25 @@
         <v>1360.426264648438</v>
       </c>
       <c r="E281" t="n">
-        <v>1395.159729817708</v>
+        <v>1395.159731445312</v>
       </c>
       <c r="F281" t="n">
-        <v>1316.629532470703</v>
+        <v>1316.629529418945</v>
       </c>
       <c r="G281" t="n">
-        <v>2.289706644460976</v>
+        <v>2.289706480124609</v>
       </c>
       <c r="H281" t="n">
-        <v>1766.733188761222</v>
+        <v>1766.733060850261</v>
       </c>
       <c r="I281" t="n">
-        <v>919.3268967152227</v>
+        <v>919.3269575259613</v>
       </c>
       <c r="J281" t="n">
-        <v>48.98943521241967</v>
+        <v>48.98942535721251</v>
       </c>
       <c r="K281" t="n">
-        <v>28.98687681558705</v>
+        <v>28.98686747697521</v>
       </c>
       <c r="L281" t="n">
         <v>75.97222222222221</v>
@@ -22126,13 +22126,13 @@
         <v>148.6708328755697</v>
       </c>
       <c r="F282" t="n">
-        <v>151.3289000320435</v>
+        <v>151.3289001846314</v>
       </c>
       <c r="G282" t="n">
-        <v>-1.007015763577823</v>
+        <v>-1.007015861384075</v>
       </c>
       <c r="H282" t="n">
-        <v>209.3574059154358</v>
+        <v>209.3573902779376</v>
       </c>
       <c r="I282" t="n">
         <v>115.0300392216107</v>
@@ -22141,7 +22141,7 @@
         <v>48.22215236450007</v>
       </c>
       <c r="K282" t="n">
-        <v>22.79026739908259</v>
+        <v>22.79025822752938</v>
       </c>
       <c r="L282" t="n">
         <v>71.66666666666667</v>
@@ -22585,16 +22585,16 @@
         <v>1850.8219921875</v>
       </c>
       <c r="E288" t="n">
-        <v>1758.512989908854</v>
+        <v>1758.512990722656</v>
       </c>
       <c r="F288" t="n">
-        <v>1763.622484130859</v>
+        <v>1763.622487792969</v>
       </c>
       <c r="G288" t="n">
-        <v>-1.015862884456975</v>
+        <v>-1.015862950185531</v>
       </c>
       <c r="H288" t="n">
-        <v>2269.472002658311</v>
+        <v>2269.472253037084</v>
       </c>
       <c r="I288" t="n">
         <v>1353.205955540699</v>
@@ -22603,7 +22603,7 @@
         <v>52.06850371907304</v>
       </c>
       <c r="K288" t="n">
-        <v>10.28632271394536</v>
+        <v>10.28633488124862</v>
       </c>
       <c r="L288" t="n">
         <v>65.27777777777779</v>
@@ -22662,13 +22662,13 @@
         <v>5398.246494140625</v>
       </c>
       <c r="E289" t="n">
-        <v>5156.854005533854</v>
+        <v>5156.854012044271</v>
       </c>
       <c r="F289" t="n">
-        <v>4929.651175537109</v>
+        <v>4929.651182861328</v>
       </c>
       <c r="G289" t="n">
-        <v>2.361782233017728</v>
+        <v>2.361782099696108</v>
       </c>
       <c r="H289" t="n">
         <v>6049.821052103703</v>
@@ -22973,13 +22973,13 @@
         <v>1086.426433919271</v>
       </c>
       <c r="F293" t="n">
-        <v>1147.930803222656</v>
+        <v>1147.930802612305</v>
       </c>
       <c r="G293" t="n">
-        <v>-0.09246938763807222</v>
+        <v>-0.09246944075863572</v>
       </c>
       <c r="H293" t="n">
-        <v>1423.547927723126</v>
+        <v>1423.548053270148</v>
       </c>
       <c r="I293" t="n">
         <v>905.5050975494345</v>
@@ -22988,7 +22988,7 @@
         <v>45.7529120929187</v>
       </c>
       <c r="K293" t="n">
-        <v>7.86087854649804</v>
+        <v>7.860888059077009</v>
       </c>
       <c r="L293" t="n">
         <v>63.61111111111111</v>
@@ -23512,10 +23512,10 @@
         <v>1362.731831054688</v>
       </c>
       <c r="F300" t="n">
-        <v>1366.979508056641</v>
+        <v>1366.979505615234</v>
       </c>
       <c r="G300" t="n">
-        <v>1.099890777538537</v>
+        <v>1.099890825161776</v>
       </c>
       <c r="H300" t="n">
         <v>1563.400024414062</v>
@@ -23746,7 +23746,7 @@
         <v>44.3218419456482</v>
       </c>
       <c r="G303" t="n">
-        <v>-1.439956391565789</v>
+        <v>-1.439956600583969</v>
       </c>
       <c r="H303" t="n">
         <v>57.70003380709684</v>
@@ -23971,13 +23971,13 @@
         <v>608.6494262695312</v>
       </c>
       <c r="E306" t="n">
-        <v>573.1839400227865</v>
+        <v>573.1839398193359</v>
       </c>
       <c r="F306" t="n">
         <v>559.535824432373</v>
       </c>
       <c r="G306" t="n">
-        <v>1.191562616226061</v>
+        <v>1.19156236490825</v>
       </c>
       <c r="H306" t="n">
         <v>784.8771245029434</v>
@@ -24202,16 +24202,16 @@
         <v>4381.530405273437</v>
       </c>
       <c r="E309" t="n">
-        <v>4234.467177734375</v>
+        <v>4234.467166341145</v>
       </c>
       <c r="F309" t="n">
-        <v>4287.780246582031</v>
+        <v>4287.780235595703</v>
       </c>
       <c r="G309" t="n">
-        <v>-0.4160812275686987</v>
+        <v>-0.4160814544937996</v>
       </c>
       <c r="H309" t="n">
-        <v>5038.987542214121</v>
+        <v>5038.988033260187</v>
       </c>
       <c r="I309" t="n">
         <v>3669.905008549105</v>
@@ -24220,7 +24220,7 @@
         <v>30.84807341916644</v>
       </c>
       <c r="K309" t="n">
-        <v>4.935184136070836</v>
+        <v>4.935194361936412</v>
       </c>
       <c r="L309" t="n">
         <v>57.08333333333333</v>
@@ -24359,13 +24359,13 @@
         <v>5135.795569661458</v>
       </c>
       <c r="F311" t="n">
-        <v>5420.653361816407</v>
+        <v>5420.653356933593</v>
       </c>
       <c r="G311" t="n">
-        <v>-0.6026086635195771</v>
+        <v>-0.6026084860679903</v>
       </c>
       <c r="H311" t="n">
-        <v>6552.654210942315</v>
+        <v>6552.654707500795</v>
       </c>
       <c r="I311" t="n">
         <v>4229.809203861739</v>
@@ -24374,7 +24374,7 @@
         <v>33.41027285221385</v>
       </c>
       <c r="K311" t="n">
-        <v>16.12004626869246</v>
+        <v>16.12005506824021</v>
       </c>
       <c r="L311" t="n">
         <v>55.13888888888889</v>
@@ -27593,10 +27593,10 @@
         <v>741.6707450358073</v>
       </c>
       <c r="F353" t="n">
-        <v>740.1936993408203</v>
+        <v>740.193699645996</v>
       </c>
       <c r="G353" t="n">
-        <v>-0.03443730038769077</v>
+        <v>-0.03443717677112934</v>
       </c>
       <c r="H353" t="n">
         <v>837.8765073351432</v>
@@ -27821,16 +27821,16 @@
         <v>500.1782775878906</v>
       </c>
       <c r="E356" t="n">
-        <v>488.8227010091146</v>
+        <v>488.8227006022136</v>
       </c>
       <c r="F356" t="n">
-        <v>492.9074424743652</v>
+        <v>492.9074417114258</v>
       </c>
       <c r="G356" t="n">
-        <v>-0.2336421161549307</v>
+        <v>-0.2336420548912921</v>
       </c>
       <c r="H356" t="n">
-        <v>561.4378970396333</v>
+        <v>561.4379586860567</v>
       </c>
       <c r="I356" t="n">
         <v>420.1655789001589</v>
@@ -27839,7 +27839,7 @@
         <v>20.90471602403978</v>
       </c>
       <c r="K356" t="n">
-        <v>10.51927107079396</v>
+        <v>10.51928320591669</v>
       </c>
       <c r="L356" t="n">
         <v>47.36111111111111</v>
@@ -28434,25 +28434,25 @@
         <v>2284.60009765625</v>
       </c>
       <c r="D364" t="n">
-        <v>2271.031015625</v>
+        <v>2271.031025390625</v>
       </c>
       <c r="E364" t="n">
-        <v>2264.332513834635</v>
+        <v>2264.332551269531</v>
       </c>
       <c r="F364" t="n">
-        <v>2285.684403686524</v>
+        <v>2285.68442565918</v>
       </c>
       <c r="G364" t="n">
-        <v>0.3556643677923299</v>
+        <v>0.3556643643610968</v>
       </c>
       <c r="H364" t="n">
         <v>2765.379504159864</v>
       </c>
       <c r="I364" t="n">
-        <v>1963.170239604111</v>
+        <v>1963.170361427068</v>
       </c>
       <c r="J364" t="n">
-        <v>16.37299973113679</v>
+        <v>16.37299250970399</v>
       </c>
       <c r="K364" t="n">
         <v>21.0443572595852</v>
@@ -28668,13 +28668,13 @@
         <v>5283.817646484375</v>
       </c>
       <c r="E367" t="n">
-        <v>5191.783704427084</v>
+        <v>5191.783707682292</v>
       </c>
       <c r="F367" t="n">
-        <v>5308.635007324218</v>
+        <v>5308.635024414062</v>
       </c>
       <c r="G367" t="n">
-        <v>0.5754390308242208</v>
+        <v>0.5754391685215188</v>
       </c>
       <c r="H367" t="n">
         <v>6175.521739453033</v>
@@ -29287,10 +29287,10 @@
         <v>2446.273072916666</v>
       </c>
       <c r="F375" t="n">
-        <v>2459.972056884766</v>
+        <v>2459.972064208984</v>
       </c>
       <c r="G375" t="n">
-        <v>-0.898622512815983</v>
+        <v>-0.8986223152252948</v>
       </c>
       <c r="H375" t="n">
         <v>3039.742679715149</v>
@@ -29678,7 +29678,7 @@
         <v>-0.7175079930797468</v>
       </c>
       <c r="H380" t="n">
-        <v>1045.658437762529</v>
+        <v>1045.658313207837</v>
       </c>
       <c r="I380" t="n">
         <v>666.0087356197063</v>
@@ -29687,7 +29687,7 @@
         <v>29.75805961507583</v>
       </c>
       <c r="K380" t="n">
-        <v>20.99727181119579</v>
+        <v>20.99725739847995</v>
       </c>
       <c r="L380" t="n">
         <v>37.08333333333334</v>
@@ -30131,16 +30131,16 @@
         <v>783.0632104492188</v>
       </c>
       <c r="E386" t="n">
-        <v>767.3909525553386</v>
+        <v>767.3909529622396</v>
       </c>
       <c r="F386" t="n">
-        <v>795.0332019042969</v>
+        <v>795.0331997680664</v>
       </c>
       <c r="G386" t="n">
-        <v>-2.207784004169033</v>
+        <v>-2.207784120097522</v>
       </c>
       <c r="H386" t="n">
-        <v>1209.194260892545</v>
+        <v>1209.194135876196</v>
       </c>
       <c r="I386" t="n">
         <v>648.9423872407145</v>
@@ -30149,7 +30149,7 @@
         <v>28.84811361596362</v>
       </c>
       <c r="K386" t="n">
-        <v>44.61451002646275</v>
+        <v>44.61449507503708</v>
       </c>
       <c r="L386" t="n">
         <v>29.30555555555556</v>
@@ -31286,13 +31286,13 @@
         <v>410.9330133056641</v>
       </c>
       <c r="E401" t="n">
-        <v>428.4340368652344</v>
+        <v>428.4340374755859</v>
       </c>
       <c r="F401" t="n">
-        <v>418.0833332824707</v>
+        <v>418.0833335876465</v>
       </c>
       <c r="G401" t="n">
-        <v>0.9810503892815348</v>
+        <v>0.9810505002082692</v>
       </c>
       <c r="H401" t="n">
         <v>478.7148398145708</v>
@@ -32755,7 +32755,7 @@
         <v>514.1510260009766</v>
       </c>
       <c r="G420" t="n">
-        <v>-0.9402479074055337</v>
+        <v>-0.940248082138595</v>
       </c>
       <c r="H420" t="n">
         <v>750.0847124549373</v>
@@ -33057,25 +33057,25 @@
         <v>38790.08109375</v>
       </c>
       <c r="E424" t="n">
-        <v>36471.183359375</v>
+        <v>36471.1833984375</v>
       </c>
       <c r="F424" t="n">
-        <v>36261.88110351562</v>
+        <v>36261.88126953125</v>
       </c>
       <c r="G424" t="n">
-        <v>-1.025692976688297</v>
+        <v>-1.025693024803009</v>
       </c>
       <c r="H424" t="n">
-        <v>45150.85152546577</v>
+        <v>45150.8475731383</v>
       </c>
       <c r="I424" t="n">
-        <v>29525.27356749276</v>
+        <v>29525.27549507192</v>
       </c>
       <c r="J424" t="n">
-        <v>22.94551621010616</v>
+        <v>22.94550818351841</v>
       </c>
       <c r="K424" t="n">
-        <v>24.38251108943739</v>
+        <v>24.38250020148292</v>
       </c>
       <c r="L424" t="n">
         <v>32.36111111111111</v>
@@ -33291,10 +33291,10 @@
         <v>1662.974524739583</v>
       </c>
       <c r="F427" t="n">
-        <v>1774.630525512695</v>
+        <v>1774.630518188477</v>
       </c>
       <c r="G427" t="n">
-        <v>-2.406336841549617</v>
+        <v>-2.406336982273416</v>
       </c>
       <c r="H427" t="n">
         <v>2541.747782091032</v>
@@ -33679,7 +33679,7 @@
         <v>2564.701784667969</v>
       </c>
       <c r="G432" t="n">
-        <v>-0.276357837626362</v>
+        <v>-0.2763577902927805</v>
       </c>
       <c r="H432" t="n">
         <v>3339</v>
@@ -33753,10 +33753,10 @@
         <v>732.1738260904948</v>
       </c>
       <c r="F433" t="n">
-        <v>745.6483959960938</v>
+        <v>745.6483972167969</v>
       </c>
       <c r="G433" t="n">
-        <v>-0.5563547162532378</v>
+        <v>-0.5563545129803282</v>
       </c>
       <c r="H433" t="n">
         <v>879.2203373423794</v>
@@ -33981,16 +33981,16 @@
         <v>78.08859008789062</v>
       </c>
       <c r="E436" t="n">
-        <v>77.50556762695312</v>
+        <v>77.50556777954101</v>
       </c>
       <c r="F436" t="n">
-        <v>77.34354675292968</v>
+        <v>77.3435466003418</v>
       </c>
       <c r="G436" t="n">
-        <v>-0.7736157572499569</v>
+        <v>-0.7736157587643899</v>
       </c>
       <c r="H436" t="n">
-        <v>87.39772087555167</v>
+        <v>87.39771312453149</v>
       </c>
       <c r="I436" t="n">
         <v>71.42454681386315</v>
@@ -33999,7 +33999,7 @@
         <v>6.7560151256014</v>
       </c>
       <c r="K436" t="n">
-        <v>14.61996180400218</v>
+        <v>14.61995163872982</v>
       </c>
       <c r="L436" t="n">
         <v>46.38888888888889</v>
@@ -34837,7 +34837,7 @@
         <v>-0.7166843032007209</v>
       </c>
       <c r="H447" t="n">
-        <v>796.6711586352184</v>
+        <v>796.6710965617623</v>
       </c>
       <c r="I447" t="n">
         <v>553.7186859929476</v>
@@ -34846,7 +34846,7 @@
         <v>23.29365605258378</v>
       </c>
       <c r="K447" t="n">
-        <v>16.69417670870423</v>
+        <v>16.69416761635694</v>
       </c>
       <c r="L447" t="n">
         <v>37.22222222222222</v>
@@ -34911,7 +34911,7 @@
         <v>1511.314482421875</v>
       </c>
       <c r="G448" t="n">
-        <v>-1.848489213166316</v>
+        <v>-1.848489174260071</v>
       </c>
       <c r="H448" t="n">
         <v>1970.727757857954</v>
@@ -34985,10 +34985,10 @@
         <v>1272.152047119141</v>
       </c>
       <c r="F449" t="n">
-        <v>1354.830377502441</v>
+        <v>1354.830379943848</v>
       </c>
       <c r="G449" t="n">
-        <v>-1.331222907759855</v>
+        <v>-1.331222729958592</v>
       </c>
       <c r="H449" t="n">
         <v>1729.008500794829</v>
@@ -35136,16 +35136,16 @@
         <v>435.9657678222656</v>
       </c>
       <c r="E451" t="n">
-        <v>428.262944539388</v>
+        <v>428.2629447428386</v>
       </c>
       <c r="F451" t="n">
-        <v>447.3892227172852</v>
+        <v>447.389221496582</v>
       </c>
       <c r="G451" t="n">
-        <v>-1.610014170784091</v>
+        <v>-1.610014010021776</v>
       </c>
       <c r="H451" t="n">
-        <v>533.7087547028075</v>
+        <v>533.7088183031568</v>
       </c>
       <c r="I451" t="n">
         <v>363.2227809620478</v>
@@ -35154,7 +35154,7 @@
         <v>18.2607507864027</v>
       </c>
       <c r="K451" t="n">
-        <v>24.24834591312812</v>
+        <v>24.24836071940242</v>
       </c>
       <c r="L451" t="n">
         <v>32.63888888888889</v>
@@ -35441,16 +35441,16 @@
         <v>285.25</v>
       </c>
       <c r="D455" t="n">
-        <v>300.4292065429688</v>
+        <v>300.4292059326172</v>
       </c>
       <c r="E455" t="n">
-        <v>274.8845958455404</v>
+        <v>274.8845959472656</v>
       </c>
       <c r="F455" t="n">
-        <v>291.2335157012939</v>
+        <v>291.2335159301758</v>
       </c>
       <c r="G455" t="n">
-        <v>-2.05973115662389</v>
+        <v>-2.059731255553576</v>
       </c>
       <c r="H455" t="n">
         <v>411.0263372414121</v>
@@ -36303,10 +36303,10 @@
         <v>387.7999877929688</v>
       </c>
       <c r="I466" t="n">
-        <v>221.246969139635</v>
+        <v>221.2469540684675</v>
       </c>
       <c r="J466" t="n">
-        <v>23.41411448698288</v>
+        <v>23.41412289385472</v>
       </c>
       <c r="K466" t="n">
         <v>42.02527197584256</v>
@@ -36830,13 +36830,13 @@
         <v>4546.74939453125</v>
       </c>
       <c r="E473" t="n">
-        <v>4703.907931315104</v>
+        <v>4703.907934570312</v>
       </c>
       <c r="F473" t="n">
-        <v>4764.341053466796</v>
+        <v>4764.341051025391</v>
       </c>
       <c r="G473" t="n">
-        <v>-0.2212644178962608</v>
+        <v>-0.221264520042963</v>
       </c>
       <c r="H473" t="n">
         <v>5612.405266256894</v>
@@ -36984,16 +36984,16 @@
         <v>239.81611328125</v>
       </c>
       <c r="E475" t="n">
-        <v>227.1543802897135</v>
+        <v>227.154380086263</v>
       </c>
       <c r="F475" t="n">
-        <v>227.1902268218994</v>
+        <v>227.1902266693115</v>
       </c>
       <c r="G475" t="n">
-        <v>-1.029159592012252</v>
+        <v>-1.029159526908618</v>
       </c>
       <c r="H475" t="n">
-        <v>286.0804190389319</v>
+        <v>286.0804516993438</v>
       </c>
       <c r="I475" t="n">
         <v>171.9528178807998</v>
@@ -37002,7 +37002,7 @@
         <v>27.20931717722577</v>
       </c>
       <c r="K475" t="n">
-        <v>30.78559561793204</v>
+        <v>30.78561054908824</v>
       </c>
       <c r="L475" t="n">
         <v>42.36111111111111</v>
@@ -37523,16 +37523,16 @@
         <v>5517.569619140625</v>
       </c>
       <c r="E482" t="n">
-        <v>5460.178743489583</v>
+        <v>5460.178736979166</v>
       </c>
       <c r="F482" t="n">
-        <v>5497.810725097656</v>
+        <v>5497.810715332032</v>
       </c>
       <c r="G482" t="n">
-        <v>-0.3270592456063648</v>
+        <v>-0.3270592020685248</v>
       </c>
       <c r="H482" t="n">
-        <v>5875.534417311879</v>
+        <v>5875.533923201399</v>
       </c>
       <c r="I482" t="n">
         <v>5065.93337960459</v>
@@ -37541,7 +37541,7 @@
         <v>2.449037740900839</v>
       </c>
       <c r="K482" t="n">
-        <v>13.20875563221346</v>
+        <v>13.20874611178033</v>
       </c>
       <c r="L482" t="n">
         <v>36.66666666666666</v>
@@ -37600,16 +37600,16 @@
         <v>219.2686279296875</v>
       </c>
       <c r="E483" t="n">
-        <v>211.8142923990885</v>
+        <v>211.8142926025391</v>
       </c>
       <c r="F483" t="n">
-        <v>216.209571685791</v>
+        <v>216.2095718383789</v>
       </c>
       <c r="G483" t="n">
-        <v>-1.082969128651035</v>
+        <v>-1.082969093368147</v>
       </c>
       <c r="H483" t="n">
-        <v>272.0997840702363</v>
+        <v>272.099752952214</v>
       </c>
       <c r="I483" t="n">
         <v>173.9540675101702</v>
@@ -37618,7 +37618,7 @@
         <v>24.0557384719625</v>
       </c>
       <c r="K483" t="n">
-        <v>26.08886942646402</v>
+        <v>26.0888550066207</v>
       </c>
       <c r="L483" t="n">
         <v>36.38888888888889</v>
@@ -38447,13 +38447,13 @@
         <v>345.9271099853515</v>
       </c>
       <c r="E494" t="n">
-        <v>343.2607305908203</v>
+        <v>343.2607312011719</v>
       </c>
       <c r="F494" t="n">
-        <v>343.7914891052246</v>
+        <v>343.7914907836914</v>
       </c>
       <c r="G494" t="n">
-        <v>-0.7069631633236595</v>
+        <v>-0.7069631598965009</v>
       </c>
       <c r="H494" t="n">
         <v>381.3442016302781</v>
@@ -38524,13 +38524,13 @@
         <v>914.145732421875</v>
       </c>
       <c r="E495" t="n">
-        <v>968.4919596354167</v>
+        <v>968.4919584147135</v>
       </c>
       <c r="F495" t="n">
-        <v>947.483916015625</v>
+        <v>947.483913269043</v>
       </c>
       <c r="G495" t="n">
-        <v>0.7385911268509071</v>
+        <v>0.7385911290077596</v>
       </c>
       <c r="H495" t="n">
         <v>1224.72508309492</v>
@@ -38604,10 +38604,10 @@
         <v>2135.604155273437</v>
       </c>
       <c r="F496" t="n">
-        <v>2088.823259277344</v>
+        <v>2088.823254394531</v>
       </c>
       <c r="G496" t="n">
-        <v>-1.005132623588434</v>
+        <v>-1.005132769091555</v>
       </c>
       <c r="H496" t="n">
         <v>2641.640801358174</v>
@@ -39993,10 +39993,10 @@
         <v>634.086729888916</v>
       </c>
       <c r="G514" t="n">
-        <v>-1.924353908333842</v>
+        <v>-1.924353954627733</v>
       </c>
       <c r="H514" t="n">
-        <v>859.7877679261235</v>
+        <v>859.7877065596524</v>
       </c>
       <c r="I514" t="n">
         <v>502</v>
@@ -40005,7 +40005,7 @@
         <v>24.20318725099602</v>
       </c>
       <c r="K514" t="n">
-        <v>37.89699565775837</v>
+        <v>37.89698581550158</v>
       </c>
       <c r="L514" t="n">
         <v>40.41666666666666</v>
@@ -40141,13 +40141,13 @@
         <v>1351.856003417969</v>
       </c>
       <c r="E516" t="n">
-        <v>1441.57578125</v>
+        <v>1441.575784505208</v>
       </c>
       <c r="F516" t="n">
-        <v>1405.289747924805</v>
+        <v>1405.28974609375</v>
       </c>
       <c r="G516" t="n">
-        <v>-0.1151367489769628</v>
+        <v>-0.1151368791242446</v>
       </c>
       <c r="H516" t="n">
         <v>1817.803954384172</v>
@@ -40914,10 +40914,10 @@
         <v>407.986787109375</v>
       </c>
       <c r="F526" t="n">
-        <v>392.4603890991211</v>
+        <v>392.4603887939453</v>
       </c>
       <c r="G526" t="n">
-        <v>-0.126249239220011</v>
+        <v>-0.1262491229729212</v>
       </c>
       <c r="H526" t="n">
         <v>476.8288845013619</v>
@@ -41071,7 +41071,7 @@
         <v>20.69657948493958</v>
       </c>
       <c r="G528" t="n">
-        <v>-1.314445231544847</v>
+        <v>-1.314445276420295</v>
       </c>
       <c r="H528" t="n">
         <v>23.83526224893035</v>
@@ -41222,10 +41222,10 @@
         <v>409.705214436849</v>
       </c>
       <c r="F530" t="n">
-        <v>419.2841244506836</v>
+        <v>419.2841236877441</v>
       </c>
       <c r="G530" t="n">
-        <v>-4.492260296540007</v>
+        <v>-4.492260337543252</v>
       </c>
       <c r="H530" t="n">
         <v>684.5682054144123</v>
@@ -41761,10 +41761,10 @@
         <v>2646.354458007812</v>
       </c>
       <c r="F537" t="n">
-        <v>2718.719686279297</v>
+        <v>2718.719696044922</v>
       </c>
       <c r="G537" t="n">
-        <v>-1.455026300104745</v>
+        <v>-1.455026120543068</v>
       </c>
       <c r="H537" t="n">
         <v>3198.009229338596</v>
@@ -41912,16 +41912,16 @@
         <v>124.022200012207</v>
       </c>
       <c r="E539" t="n">
-        <v>123.6015547688802</v>
+        <v>123.6015548197428</v>
       </c>
       <c r="F539" t="n">
-        <v>126.524270324707</v>
+        <v>126.5242697525024</v>
       </c>
       <c r="G539" t="n">
-        <v>-1.138789247484207</v>
+        <v>-1.138789370444304</v>
       </c>
       <c r="H539" t="n">
-        <v>155.8999783750524</v>
+        <v>155.8999606999571</v>
       </c>
       <c r="I539" t="n">
         <v>112.8155071321618</v>
@@ -41930,7 +41930,7 @@
         <v>5.402179793251238</v>
       </c>
       <c r="K539" t="n">
-        <v>31.10753811601292</v>
+        <v>31.10752325175028</v>
       </c>
       <c r="L539" t="n">
         <v>25.97222222222222</v>
@@ -42374,25 +42374,25 @@
         <v>194.9868051147461</v>
       </c>
       <c r="E545" t="n">
-        <v>194.0252750651042</v>
+        <v>194.0252744547526</v>
       </c>
       <c r="F545" t="n">
-        <v>198.689979019165</v>
+        <v>198.689977722168</v>
       </c>
       <c r="G545" t="n">
-        <v>-1.998821444695009</v>
+        <v>-1.998821715633559</v>
       </c>
       <c r="H545" t="n">
-        <v>239.2186728978909</v>
+        <v>239.2187037807859</v>
       </c>
       <c r="I545" t="n">
-        <v>156.7443123050878</v>
+        <v>156.7442971017576</v>
       </c>
       <c r="J545" t="n">
-        <v>15.16845595079457</v>
+        <v>15.16846712149804</v>
       </c>
       <c r="K545" t="n">
-        <v>32.51643432094951</v>
+        <v>32.51645142869062</v>
       </c>
       <c r="L545" t="n">
         <v>24.16666666666667</v>
@@ -43920,10 +43920,10 @@
         <v>240.3016083526611</v>
       </c>
       <c r="G565" t="n">
-        <v>-2.468952073072483</v>
+        <v>-2.468952133474189</v>
       </c>
       <c r="H565" t="n">
-        <v>308.0746845932235</v>
+        <v>308.0746526166167</v>
       </c>
       <c r="I565" t="n">
         <v>185.2067002350832</v>
@@ -43932,7 +43932,7 @@
         <v>16.89102241893674</v>
       </c>
       <c r="K565" t="n">
-        <v>42.30434513197486</v>
+        <v>42.30433036149772</v>
       </c>
       <c r="L565" t="n">
         <v>17.77777777777778</v>
@@ -44068,16 +44068,16 @@
         <v>2268.329079589844</v>
       </c>
       <c r="E567" t="n">
-        <v>2368.147416178385</v>
+        <v>2368.14739827474</v>
       </c>
       <c r="F567" t="n">
-        <v>2550.787870483398</v>
+        <v>2550.787868041992</v>
       </c>
       <c r="G567" t="n">
-        <v>-2.539591782444872</v>
+        <v>-2.539591693901633</v>
       </c>
       <c r="H567" t="n">
-        <v>3287.161645949698</v>
+        <v>3287.161392369851</v>
       </c>
       <c r="I567" t="n">
         <v>1966.020518717901</v>
@@ -44086,7 +44086,7 @@
         <v>17.19104546795396</v>
       </c>
       <c r="K567" t="n">
-        <v>42.67194643878896</v>
+        <v>42.67193543271921</v>
       </c>
       <c r="L567" t="n">
         <v>17.5</v>
@@ -44459,7 +44459,7 @@
         <v>1286.435960388184</v>
       </c>
       <c r="G572" t="n">
-        <v>-2.642913666214863</v>
+        <v>-2.642913711185302</v>
       </c>
       <c r="H572" t="n">
         <v>1691.399159307065</v>
@@ -44761,22 +44761,22 @@
         <v>832.1171362304688</v>
       </c>
       <c r="E576" t="n">
-        <v>956.1952242024739</v>
+        <v>956.1952237955729</v>
       </c>
       <c r="F576" t="n">
-        <v>926.8351348876953</v>
+        <v>926.8351327514648</v>
       </c>
       <c r="G576" t="n">
-        <v>-0.3484425605944863</v>
+        <v>-0.3484423325116559</v>
       </c>
       <c r="H576" t="n">
         <v>1282.80960014975</v>
       </c>
       <c r="I576" t="n">
-        <v>743.4273285628773</v>
+        <v>743.4272688553443</v>
       </c>
       <c r="J576" t="n">
-        <v>3.352398555382452</v>
+        <v>3.352406856015211</v>
       </c>
       <c r="K576" t="n">
         <v>66.95641841746524</v>
@@ -45229,7 +45229,7 @@
         <v>396.4102890014648</v>
       </c>
       <c r="G582" t="n">
-        <v>-2.587274843695719</v>
+        <v>-2.587274916748461</v>
       </c>
       <c r="H582" t="n">
         <v>574.7140242073417</v>
@@ -45528,25 +45528,25 @@
         <v>501.5499877929688</v>
       </c>
       <c r="D586" t="n">
-        <v>530.3691241455078</v>
+        <v>530.3691278076171</v>
       </c>
       <c r="E586" t="n">
-        <v>514.8444938151042</v>
+        <v>514.8444948323568</v>
       </c>
       <c r="F586" t="n">
-        <v>550.615121459961</v>
+        <v>550.6151228332519</v>
       </c>
       <c r="G586" t="n">
-        <v>-3.614513048242007</v>
+        <v>-3.614512833591788</v>
       </c>
       <c r="H586" t="n">
         <v>872.0425606177564</v>
       </c>
       <c r="I586" t="n">
-        <v>406.1171468902937</v>
+        <v>406.117116732523</v>
       </c>
       <c r="J586" t="n">
-        <v>23.49884550145693</v>
+        <v>23.4988546723333</v>
       </c>
       <c r="K586" t="n">
         <v>73.86952085376595</v>
@@ -46150,10 +46150,10 @@
         <v>145.620680847168</v>
       </c>
       <c r="F594" t="n">
-        <v>148.5189080047607</v>
+        <v>148.5189074707031</v>
       </c>
       <c r="G594" t="n">
-        <v>-1.270438238378957</v>
+        <v>-1.27043819281637</v>
       </c>
       <c r="H594" t="n">
         <v>184.9587904135824</v>
@@ -47077,7 +47077,7 @@
         <v>34.24443413734436</v>
       </c>
       <c r="G606" t="n">
-        <v>-2.213591991068165</v>
+        <v>-2.213592044327672</v>
       </c>
       <c r="H606" t="n">
         <v>40.26070662850351</v>
@@ -47154,7 +47154,7 @@
         <v>1106.948691101074</v>
       </c>
       <c r="G607" t="n">
-        <v>-2.030551481156995</v>
+        <v>-2.030551534078695</v>
       </c>
       <c r="H607" t="n">
         <v>1400.476774401248</v>
@@ -47379,13 +47379,13 @@
         <v>3008.103618164062</v>
       </c>
       <c r="E610" t="n">
-        <v>3073.915525716146</v>
+        <v>3073.91552734375</v>
       </c>
       <c r="F610" t="n">
-        <v>3212.024738769531</v>
+        <v>3212.024744873047</v>
       </c>
       <c r="G610" t="n">
-        <v>-1.854286782512315</v>
+        <v>-1.854286632622859</v>
       </c>
       <c r="H610" t="n">
         <v>4112.487734005053</v>
@@ -48004,7 +48004,7 @@
         <v>-2.329559191847264</v>
       </c>
       <c r="H618" t="n">
-        <v>294.6532543042141</v>
+        <v>294.6532203195111</v>
       </c>
       <c r="I618" t="n">
         <v>213.7350670269712</v>
@@ -48013,7 +48013,7 @@
         <v>4.447065518263038</v>
       </c>
       <c r="K618" t="n">
-        <v>31.98944949552818</v>
+        <v>31.98943427213536</v>
       </c>
       <c r="L618" t="n">
         <v>20.83333333333334</v>
@@ -48223,16 +48223,16 @@
         <v>86.59999847412109</v>
       </c>
       <c r="D621" t="n">
-        <v>93.56574401855468</v>
+        <v>93.56574386596679</v>
       </c>
       <c r="E621" t="n">
-        <v>94.09136332194011</v>
+        <v>94.09136311848958</v>
       </c>
       <c r="F621" t="n">
-        <v>98.11523635864258</v>
+        <v>98.11523609161377</v>
       </c>
       <c r="G621" t="n">
-        <v>-2.543952068317901</v>
+        <v>-2.543952222772394</v>
       </c>
       <c r="H621" t="n">
         <v>124.8273096544699</v>
@@ -48386,7 +48386,7 @@
         <v>4373.333385009766</v>
       </c>
       <c r="G623" t="n">
-        <v>-1.391633273605963</v>
+        <v>-1.391633219324084</v>
       </c>
       <c r="H623" t="n">
         <v>5305.222747660049</v>
@@ -48460,10 +48460,10 @@
         <v>535.6848376464844</v>
       </c>
       <c r="F624" t="n">
-        <v>538.8343035888672</v>
+        <v>538.8343041992188</v>
       </c>
       <c r="G624" t="n">
-        <v>-1.519035501355859</v>
+        <v>-1.519035279946512</v>
       </c>
       <c r="H624" t="n">
         <v>653.9340000086492</v>
@@ -48925,7 +48925,7 @@
         <v>312.8056833648682</v>
       </c>
       <c r="G630" t="n">
-        <v>-2.674367500689556</v>
+        <v>-2.674367546895717</v>
       </c>
       <c r="H630" t="n">
         <v>408.5542740377988</v>
@@ -49381,7 +49381,7 @@
         <v>67.98149551391602</v>
       </c>
       <c r="E636" t="n">
-        <v>71.37594472249349</v>
+        <v>71.3759445699056</v>
       </c>
       <c r="F636" t="n">
         <v>72.11437274932861</v>
@@ -49390,7 +49390,7 @@
         <v>-2.746455340891829</v>
       </c>
       <c r="H636" t="n">
-        <v>93.44222215601812</v>
+        <v>93.44221530383422</v>
       </c>
       <c r="I636" t="n">
         <v>62.68610889438828</v>
@@ -49399,7 +49399,7 @@
         <v>4.058147023978131</v>
       </c>
       <c r="K636" t="n">
-        <v>43.25037152720876</v>
+        <v>43.25036102255822</v>
       </c>
       <c r="L636" t="n">
         <v>15.69444444444444</v>
@@ -49458,13 +49458,13 @@
         <v>7596.190888671875</v>
       </c>
       <c r="E637" t="n">
-        <v>7820.426318359375</v>
+        <v>7820.426324869792</v>
       </c>
       <c r="F637" t="n">
-        <v>7858.060393066407</v>
+        <v>7858.060397949219</v>
       </c>
       <c r="G637" t="n">
-        <v>-1.561341024966423</v>
+        <v>-1.561341144436235</v>
       </c>
       <c r="H637" t="n">
         <v>10437.38206257999</v>
@@ -49618,7 +49618,7 @@
         <v>2209.878492431641</v>
       </c>
       <c r="G639" t="n">
-        <v>-1.991559335599591</v>
+        <v>-1.991559600900428</v>
       </c>
       <c r="H639" t="n">
         <v>2701.07684267753</v>
@@ -50000,13 +50000,13 @@
         <v>1252.075344238281</v>
       </c>
       <c r="F644" t="n">
-        <v>1288.840504150391</v>
+        <v>1288.840504760742</v>
       </c>
       <c r="G644" t="n">
-        <v>-1.738936360437948</v>
+        <v>-1.738936313904826</v>
       </c>
       <c r="H644" t="n">
-        <v>1608.140938678776</v>
+        <v>1608.140814494163</v>
       </c>
       <c r="I644" t="n">
         <v>1123.599975585938</v>
@@ -50015,7 +50015,7 @@
         <v>2.705591409274422</v>
       </c>
       <c r="K644" t="n">
-        <v>39.35363420093376</v>
+        <v>39.35362343970215</v>
       </c>
       <c r="L644" t="n">
         <v>14.16666666666667</v>
@@ -50388,10 +50388,10 @@
         <v>2050.181427001953</v>
       </c>
       <c r="G649" t="n">
-        <v>-1.370371345427668</v>
+        <v>-1.370371287507122</v>
       </c>
       <c r="H649" t="n">
-        <v>2448.345479475883</v>
+        <v>2448.345231432346</v>
       </c>
       <c r="I649" t="n">
         <v>1761.237851420491</v>
@@ -50400,7 +50400,7 @@
         <v>3.858768973002169</v>
       </c>
       <c r="K649" t="n">
-        <v>33.84788677188371</v>
+        <v>33.84787321166374</v>
       </c>
       <c r="L649" t="n">
         <v>13.19444444444444</v>
@@ -50462,13 +50462,13 @@
         <v>191.1998132324219</v>
       </c>
       <c r="F650" t="n">
-        <v>205.251796875</v>
+        <v>205.2517964935303</v>
       </c>
       <c r="G650" t="n">
-        <v>-2.711629333284471</v>
+        <v>-2.711629373369862</v>
       </c>
       <c r="H650" t="n">
-        <v>263.2205288662585</v>
+        <v>263.220498300555</v>
       </c>
       <c r="I650" t="n">
         <v>167.0916913788894</v>
@@ -50477,7 +50477,7 @@
         <v>5.57077520777971</v>
       </c>
       <c r="K650" t="n">
-        <v>49.21799204864055</v>
+        <v>49.21797472114364</v>
       </c>
       <c r="L650" t="n">
         <v>12.77777777777778</v>
@@ -50696,7 +50696,7 @@
         <v>1805.041688232422</v>
       </c>
       <c r="G653" t="n">
-        <v>-2.390405964550313</v>
+        <v>-2.390405996766776</v>
       </c>
       <c r="H653" t="n">
         <v>2057.089271774458</v>
@@ -50850,7 +50850,7 @@
         <v>302.4809647369385</v>
       </c>
       <c r="G655" t="n">
-        <v>-3.365351813867035</v>
+        <v>-3.365351860974275</v>
       </c>
       <c r="H655" t="n">
         <v>398.6210131186603</v>
@@ -51466,7 +51466,7 @@
         <v>1755.072418823242</v>
       </c>
       <c r="G663" t="n">
-        <v>-3.916099627092218</v>
+        <v>-3.916099530774209</v>
       </c>
       <c r="H663" t="n">
         <v>2504.019782423858</v>
@@ -51774,7 +51774,7 @@
         <v>2222.92065612793</v>
       </c>
       <c r="G667" t="n">
-        <v>-4.280993711707593</v>
+        <v>-4.280993661394317</v>
       </c>
       <c r="H667" t="n">
         <v>3868.278555207404</v>
@@ -51842,16 +51842,16 @@
         <v>672.75</v>
       </c>
       <c r="D668" t="n">
-        <v>676.5981628417969</v>
+        <v>676.5981616210937</v>
       </c>
       <c r="E668" t="n">
-        <v>689.2616463216145</v>
+        <v>689.2616426595052</v>
       </c>
       <c r="F668" t="n">
-        <v>741.1321179199218</v>
+        <v>741.1321148681641</v>
       </c>
       <c r="G668" t="n">
-        <v>-4.782582944407753</v>
+        <v>-4.782583149821685</v>
       </c>
       <c r="H668" t="n">
         <v>1223.985164326833</v>
@@ -51922,16 +51922,16 @@
         <v>1008.023676757812</v>
       </c>
       <c r="E669" t="n">
-        <v>1048.405737711588</v>
+        <v>1048.40573445638</v>
       </c>
       <c r="F669" t="n">
-        <v>1078.48437286377</v>
+        <v>1078.484371643066</v>
       </c>
       <c r="G669" t="n">
-        <v>-1.750441605790665</v>
+        <v>-1.750441389219159</v>
       </c>
       <c r="H669" t="n">
-        <v>1284.135346691241</v>
+        <v>1284.135475005729</v>
       </c>
       <c r="I669" t="n">
         <v>859.5499877929688</v>
@@ -51940,7 +51940,7 @@
         <v>2.146473441806984</v>
       </c>
       <c r="K669" t="n">
-        <v>46.25687319945795</v>
+        <v>46.25688781386439</v>
       </c>
       <c r="L669" t="n">
         <v>8.194444444444445</v>
@@ -52082,7 +52082,7 @@
         <v>454.9757450866699</v>
       </c>
       <c r="G671" t="n">
-        <v>-2.517234356481735</v>
+        <v>-2.517234229000131</v>
       </c>
       <c r="H671" t="n">
         <v>566.6192163890048</v>
@@ -52313,7 +52313,7 @@
         <v>101.8630598449707</v>
       </c>
       <c r="G674" t="n">
-        <v>-3.667698454350832</v>
+        <v>-3.667698384845641</v>
       </c>
       <c r="H674" t="n">
         <v>135.7285614195044</v>
@@ -53385,13 +53385,13 @@
         <v>2595.991411132813</v>
       </c>
       <c r="E688" t="n">
-        <v>2832.207106119792</v>
+        <v>2832.207109375</v>
       </c>
       <c r="F688" t="n">
-        <v>2940.535313720703</v>
+        <v>2940.535317382813</v>
       </c>
       <c r="G688" t="n">
-        <v>-3.852246217151467</v>
+        <v>-3.852246212538735</v>
       </c>
       <c r="H688" t="n">
         <v>3812.926349899466</v>
@@ -53853,7 +53853,7 @@
         <v>404.683960723877</v>
       </c>
       <c r="G694" t="n">
-        <v>-4.605444204726306</v>
+        <v>-4.605444239038725</v>
       </c>
       <c r="H694" t="n">
         <v>541.6977805031639</v>
@@ -55464,13 +55464,13 @@
         <v>362.4108288574218</v>
       </c>
       <c r="E715" t="n">
-        <v>432.0797648111979</v>
+        <v>432.0797662353515</v>
       </c>
       <c r="F715" t="n">
-        <v>458.8093496704101</v>
+        <v>458.8093499755859</v>
       </c>
       <c r="G715" t="n">
-        <v>-5.259885815495813</v>
+        <v>-5.259885633076578</v>
       </c>
       <c r="H715" t="n">
         <v>606.8956852082865</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -2032,16 +2032,16 @@
         <v>1271.141482543945</v>
       </c>
       <c r="G21" t="n">
-        <v>8.274004680213709</v>
+        <v>8.274004595778074</v>
       </c>
       <c r="H21" t="n">
         <v>1949</v>
       </c>
       <c r="I21" t="n">
-        <v>821.6033975811163</v>
+        <v>821.6033372206257</v>
       </c>
       <c r="J21" t="n">
-        <v>123.9523358127713</v>
+        <v>123.9523522658117</v>
       </c>
       <c r="K21" t="n">
         <v>5.923913043478257</v>
@@ -3800,19 +3800,19 @@
         <v>620.3661358642578</v>
       </c>
       <c r="F44" t="n">
-        <v>585.2124824523926</v>
+        <v>585.2124830627441</v>
       </c>
       <c r="G44" t="n">
-        <v>6.558630746254512</v>
+        <v>6.558630768571772</v>
       </c>
       <c r="H44" t="n">
         <v>844</v>
       </c>
       <c r="I44" t="n">
-        <v>399.8350028638013</v>
+        <v>399.8349725758499</v>
       </c>
       <c r="J44" t="n">
-        <v>97.33139778879307</v>
+        <v>97.33141273686969</v>
       </c>
       <c r="K44" t="n">
         <v>6.970849176172367</v>
@@ -3951,13 +3951,13 @@
         <v>4378.082319335937</v>
       </c>
       <c r="E46" t="n">
-        <v>3651.8725</v>
+        <v>3651.872503255208</v>
       </c>
       <c r="F46" t="n">
-        <v>3474.930827636719</v>
+        <v>3474.930830078125</v>
       </c>
       <c r="G46" t="n">
-        <v>6.196788596623648</v>
+        <v>6.196788710852519</v>
       </c>
       <c r="H46" t="n">
         <v>4785.7998046875</v>
@@ -4028,13 +4028,13 @@
         <v>316.9620193481445</v>
       </c>
       <c r="E47" t="n">
-        <v>240.5445524088542</v>
+        <v>240.5445525105794</v>
       </c>
       <c r="F47" t="n">
-        <v>230.3682941436768</v>
+        <v>230.3682939910889</v>
       </c>
       <c r="G47" t="n">
-        <v>6.424911970884861</v>
+        <v>6.424912125456306</v>
       </c>
       <c r="H47" t="n">
         <v>388.75</v>
@@ -4804,7 +4804,7 @@
         <v>8860.886042480468</v>
       </c>
       <c r="G57" t="n">
-        <v>4.869453680890135</v>
+        <v>4.869453983902883</v>
       </c>
       <c r="H57" t="n">
         <v>12540</v>
@@ -5648,10 +5648,10 @@
         <v>76.4991712697347</v>
       </c>
       <c r="F68" t="n">
-        <v>72.14712699890137</v>
+        <v>72.14712705612183</v>
       </c>
       <c r="G68" t="n">
-        <v>3.875464344671586</v>
+        <v>3.875464541159013</v>
       </c>
       <c r="H68" t="n">
         <v>94.5</v>
@@ -7419,10 +7419,10 @@
         <v>227.8999305216471</v>
       </c>
       <c r="F91" t="n">
-        <v>218.941736831665</v>
+        <v>218.9417366790771</v>
       </c>
       <c r="G91" t="n">
-        <v>2.862184850294902</v>
+        <v>2.86218485234675</v>
       </c>
       <c r="H91" t="n">
         <v>289.6499938964844</v>
@@ -7878,13 +7878,13 @@
         <v>7323.856669921875</v>
       </c>
       <c r="E97" t="n">
-        <v>6755.950328776042</v>
+        <v>6755.950325520834</v>
       </c>
       <c r="F97" t="n">
-        <v>6323.685190429687</v>
+        <v>6323.685192871094</v>
       </c>
       <c r="G97" t="n">
-        <v>4.546347102863235</v>
+        <v>4.546347269818551</v>
       </c>
       <c r="H97" t="n">
         <v>7832.294844565128</v>
@@ -8038,7 +8038,7 @@
         <v>470.4523384094238</v>
       </c>
       <c r="G99" t="n">
-        <v>3.512231307394242</v>
+        <v>3.512231272641619</v>
       </c>
       <c r="H99" t="n">
         <v>662</v>
@@ -8731,7 +8731,7 @@
         <v>265.5827902984619</v>
       </c>
       <c r="G108" t="n">
-        <v>1.817142495321011</v>
+        <v>1.81714261444299</v>
       </c>
       <c r="H108" t="n">
         <v>367.499792159746</v>
@@ -9039,7 +9039,7 @@
         <v>2996.056387939453</v>
       </c>
       <c r="G112" t="n">
-        <v>4.308208398106905</v>
+        <v>4.308208353776966</v>
       </c>
       <c r="H112" t="n">
         <v>3796</v>
@@ -9569,25 +9569,25 @@
         <v>591.0999755859375</v>
       </c>
       <c r="D119" t="n">
-        <v>542.9138623046875</v>
+        <v>543.0109997558594</v>
       </c>
       <c r="E119" t="n">
-        <v>470.3613580322266</v>
+        <v>470.4466672770182</v>
       </c>
       <c r="F119" t="n">
-        <v>458.9738433837891</v>
+        <v>459.057250213623</v>
       </c>
       <c r="G119" t="n">
-        <v>0.8536418952463043</v>
+        <v>0.853523101629583</v>
       </c>
       <c r="H119" t="n">
         <v>609</v>
       </c>
       <c r="I119" t="n">
-        <v>326.9901756501101</v>
+        <v>327.0499877929688</v>
       </c>
       <c r="J119" t="n">
-        <v>80.76994955910644</v>
+        <v>80.73688966474425</v>
       </c>
       <c r="K119" t="n">
         <v>3.028256666111151</v>
@@ -10031,16 +10031,16 @@
         <v>1065.300048828125</v>
       </c>
       <c r="D125" t="n">
-        <v>1010.778583984375</v>
+        <v>1010.778586425781</v>
       </c>
       <c r="E125" t="n">
-        <v>918.870264078776</v>
+        <v>918.8702661132812</v>
       </c>
       <c r="F125" t="n">
-        <v>892.6633038330078</v>
+        <v>892.663306274414</v>
       </c>
       <c r="G125" t="n">
-        <v>1.820620023011088</v>
+        <v>1.820619982497806</v>
       </c>
       <c r="H125" t="n">
         <v>1111</v>
@@ -10265,13 +10265,13 @@
         <v>1816.887590332031</v>
       </c>
       <c r="E128" t="n">
-        <v>1586.39423828125</v>
+        <v>1586.394237467448</v>
       </c>
       <c r="F128" t="n">
-        <v>1550.481926879883</v>
+        <v>1550.481922607422</v>
       </c>
       <c r="G128" t="n">
-        <v>2.69503034888654</v>
+        <v>2.695030564091438</v>
       </c>
       <c r="H128" t="n">
         <v>1988.900024414062</v>
@@ -10961,10 +10961,10 @@
         <v>1811.279212239583</v>
       </c>
       <c r="F137" t="n">
-        <v>1650.450571289063</v>
+        <v>1650.450574951172</v>
       </c>
       <c r="G137" t="n">
-        <v>8.203093442171184</v>
+        <v>8.203093357531266</v>
       </c>
       <c r="H137" t="n">
         <v>2714.261178227147</v>
@@ -11195,16 +11195,16 @@
         <v>1849.530582885742</v>
       </c>
       <c r="G140" t="n">
-        <v>9.407025472408947</v>
+        <v>9.407025511910039</v>
       </c>
       <c r="H140" t="n">
         <v>2983.800048828125</v>
       </c>
       <c r="I140" t="n">
-        <v>1175.257470329055</v>
+        <v>1175.257587358084</v>
       </c>
       <c r="J140" t="n">
-        <v>108.8138267242104</v>
+        <v>108.8138059310841</v>
       </c>
       <c r="K140" t="n">
         <v>21.58428467028532</v>
@@ -12196,16 +12196,16 @@
         <v>989.3037023925781</v>
       </c>
       <c r="G153" t="n">
-        <v>3.989424547958009</v>
+        <v>3.989424581315903</v>
       </c>
       <c r="H153" t="n">
         <v>1153.699951171875</v>
       </c>
       <c r="I153" t="n">
-        <v>577.0990341682009</v>
+        <v>577.0989733310039</v>
       </c>
       <c r="J153" t="n">
-        <v>80.38498392228999</v>
+        <v>80.38500293829472</v>
       </c>
       <c r="K153" t="n">
         <v>10.82612403188041</v>
@@ -12501,19 +12501,19 @@
         <v>1932.661436360677</v>
       </c>
       <c r="F157" t="n">
-        <v>1806.057345581055</v>
+        <v>1806.057348632813</v>
       </c>
       <c r="G157" t="n">
-        <v>4.795652235437231</v>
+        <v>4.79565233828656</v>
       </c>
       <c r="H157" t="n">
         <v>2295</v>
       </c>
       <c r="I157" t="n">
-        <v>1123.303556351769</v>
+        <v>1123.303677487793</v>
       </c>
       <c r="J157" t="n">
-        <v>74.12924484567969</v>
+        <v>74.12922606774384</v>
       </c>
       <c r="K157" t="n">
         <v>17.33128834355828</v>
@@ -13117,10 +13117,10 @@
         <v>1130.350380452474</v>
       </c>
       <c r="F165" t="n">
-        <v>1094.048710327148</v>
+        <v>1094.048709716797</v>
       </c>
       <c r="G165" t="n">
-        <v>2.065635528572929</v>
+        <v>2.065635616924477</v>
       </c>
       <c r="H165" t="n">
         <v>1596.696405272527</v>
@@ -13188,16 +13188,16 @@
         <v>1972.800048828125</v>
       </c>
       <c r="D166" t="n">
-        <v>1688.969516601562</v>
+        <v>1688.96953125</v>
       </c>
       <c r="E166" t="n">
-        <v>1435.685918782552</v>
+        <v>1435.685924479167</v>
       </c>
       <c r="F166" t="n">
-        <v>1516.535418701172</v>
+        <v>1516.535424194336</v>
       </c>
       <c r="G166" t="n">
-        <v>0.7568164498964025</v>
+        <v>0.7568166105660579</v>
       </c>
       <c r="H166" t="n">
         <v>2021.199951171875</v>
@@ -13428,7 +13428,7 @@
         <v>601.2616787719727</v>
       </c>
       <c r="G169" t="n">
-        <v>2.57877512836906</v>
+        <v>2.578775235183883</v>
       </c>
       <c r="H169" t="n">
         <v>769</v>
@@ -14269,13 +14269,13 @@
         <v>308.8497998046875</v>
       </c>
       <c r="E180" t="n">
-        <v>294.3754627482097</v>
+        <v>294.3754621378581</v>
       </c>
       <c r="F180" t="n">
-        <v>283.5916655731201</v>
+        <v>283.5916654205323</v>
       </c>
       <c r="G180" t="n">
-        <v>1.425839516330418</v>
+        <v>1.425839600134737</v>
       </c>
       <c r="H180" t="n">
         <v>359.3387168134344</v>
@@ -14352,7 +14352,7 @@
         <v>305.556494140625</v>
       </c>
       <c r="G181" t="n">
-        <v>2.834804073069019</v>
+        <v>2.834804020259929</v>
       </c>
       <c r="H181" t="n">
         <v>380.4567148307952</v>
@@ -15347,13 +15347,13 @@
         <v>452.688232421875</v>
       </c>
       <c r="E194" t="n">
-        <v>464.1109313964844</v>
+        <v>464.1109307861328</v>
       </c>
       <c r="F194" t="n">
-        <v>452.4235473632813</v>
+        <v>452.4235456848144</v>
       </c>
       <c r="G194" t="n">
-        <v>1.391491473081885</v>
+        <v>1.391491408972234</v>
       </c>
       <c r="H194" t="n">
         <v>529.9163379046904</v>
@@ -15812,10 +15812,10 @@
         <v>1681.451168619792</v>
       </c>
       <c r="F200" t="n">
-        <v>1669.113461914063</v>
+        <v>1669.113459472656</v>
       </c>
       <c r="G200" t="n">
-        <v>0.8247416097205917</v>
+        <v>0.8247414994176916</v>
       </c>
       <c r="H200" t="n">
         <v>1983.954544928268</v>
@@ -16736,10 +16736,10 @@
         <v>401.6778019205729</v>
       </c>
       <c r="F212" t="n">
-        <v>396.9787664794922</v>
+        <v>396.978766784668</v>
       </c>
       <c r="G212" t="n">
-        <v>0.5456689387465019</v>
+        <v>0.5456687051772047</v>
       </c>
       <c r="H212" t="n">
         <v>490.7000122070312</v>
@@ -17891,19 +17891,19 @@
         <v>719.4185656738281</v>
       </c>
       <c r="F227" t="n">
-        <v>671.5628526306152</v>
+        <v>671.5628533935546</v>
       </c>
       <c r="G227" t="n">
-        <v>3.082958969362393</v>
+        <v>3.08295896575197</v>
       </c>
       <c r="H227" t="n">
         <v>1093.53919041171</v>
       </c>
       <c r="I227" t="n">
-        <v>491.2850813456647</v>
+        <v>491.2850236715819</v>
       </c>
       <c r="J227" t="n">
-        <v>54.78793089423857</v>
+        <v>54.78794906546609</v>
       </c>
       <c r="K227" t="n">
         <v>43.80158759389907</v>
@@ -19588,7 +19588,7 @@
         <v>1487.232166137695</v>
       </c>
       <c r="G249" t="n">
-        <v>1.614137167697471</v>
+        <v>1.614137125322479</v>
       </c>
       <c r="H249" t="n">
         <v>1807.040094106148</v>
@@ -19659,13 +19659,13 @@
         <v>1151.590783691406</v>
       </c>
       <c r="E250" t="n">
-        <v>1101.543179931641</v>
+        <v>1101.543180338542</v>
       </c>
       <c r="F250" t="n">
-        <v>1065.962762451172</v>
+        <v>1065.962764587402</v>
       </c>
       <c r="G250" t="n">
-        <v>1.877828971374473</v>
+        <v>1.877828789253977</v>
       </c>
       <c r="H250" t="n">
         <v>1238.748718225596</v>
@@ -20897,7 +20897,7 @@
         <v>164.5688024902344</v>
       </c>
       <c r="G266" t="n">
-        <v>-0.1402572051951378</v>
+        <v>-0.1402571589651957</v>
       </c>
       <c r="H266" t="n">
         <v>181.8519567776652</v>
@@ -21199,13 +21199,13 @@
         <v>1200.318005371094</v>
       </c>
       <c r="E270" t="n">
-        <v>1144.464966227214</v>
+        <v>1144.464964599609</v>
       </c>
       <c r="F270" t="n">
-        <v>1169.29245880127</v>
+        <v>1169.292454528809</v>
       </c>
       <c r="G270" t="n">
-        <v>0.1195442563789006</v>
+        <v>0.1195442044929607</v>
       </c>
       <c r="H270" t="n">
         <v>1378.852549646065</v>
@@ -21750,10 +21750,10 @@
         <v>758.8333740234375</v>
       </c>
       <c r="I277" t="n">
-        <v>238.684486798652</v>
+        <v>238.6845018119064</v>
       </c>
       <c r="J277" t="n">
-        <v>118.5521277108021</v>
+        <v>118.552113963874</v>
       </c>
       <c r="K277" t="n">
         <v>45.46790731502188</v>
@@ -22046,16 +22046,16 @@
         <v>1360.426264648438</v>
       </c>
       <c r="E281" t="n">
-        <v>1395.159731445312</v>
+        <v>1395.159729003906</v>
       </c>
       <c r="F281" t="n">
-        <v>1316.629529418945</v>
+        <v>1316.629531860352</v>
       </c>
       <c r="G281" t="n">
-        <v>2.289706480124609</v>
+        <v>2.289706597042396</v>
       </c>
       <c r="H281" t="n">
-        <v>1766.733060850261</v>
+        <v>1766.733188761222</v>
       </c>
       <c r="I281" t="n">
         <v>919.3269575259613</v>
@@ -22064,7 +22064,7 @@
         <v>48.98942535721251</v>
       </c>
       <c r="K281" t="n">
-        <v>28.98686747697521</v>
+        <v>28.98687681558705</v>
       </c>
       <c r="L281" t="n">
         <v>75.97222222222221</v>
@@ -22129,7 +22129,7 @@
         <v>151.3289001846314</v>
       </c>
       <c r="G282" t="n">
-        <v>-1.007015861384075</v>
+        <v>-1.007015762572683</v>
       </c>
       <c r="H282" t="n">
         <v>209.3573902779376</v>
@@ -22973,13 +22973,13 @@
         <v>1086.426433919271</v>
       </c>
       <c r="F293" t="n">
-        <v>1147.930802612305</v>
+        <v>1147.930799560547</v>
       </c>
       <c r="G293" t="n">
-        <v>-0.09246944075863572</v>
+        <v>-0.0924694940756754</v>
       </c>
       <c r="H293" t="n">
-        <v>1423.548053270148</v>
+        <v>1423.547927723126</v>
       </c>
       <c r="I293" t="n">
         <v>905.5050975494345</v>
@@ -22988,7 +22988,7 @@
         <v>45.7529120929187</v>
       </c>
       <c r="K293" t="n">
-        <v>7.860888059077009</v>
+        <v>7.86087854649804</v>
       </c>
       <c r="L293" t="n">
         <v>63.61111111111111</v>
@@ -23278,13 +23278,13 @@
         <v>1929.191655273437</v>
       </c>
       <c r="E297" t="n">
-        <v>1822.171727701823</v>
+        <v>1822.171726888021</v>
       </c>
       <c r="F297" t="n">
-        <v>1797.231825561523</v>
+        <v>1797.231826171875</v>
       </c>
       <c r="G297" t="n">
-        <v>1.399021024633451</v>
+        <v>1.399020884481561</v>
       </c>
       <c r="H297" t="n">
         <v>2046.900024414062</v>
@@ -23512,10 +23512,10 @@
         <v>1362.731831054688</v>
       </c>
       <c r="F300" t="n">
-        <v>1366.979505615234</v>
+        <v>1366.979508056641</v>
       </c>
       <c r="G300" t="n">
-        <v>1.099890825161776</v>
+        <v>1.099890777538537</v>
       </c>
       <c r="H300" t="n">
         <v>1563.400024414062</v>
@@ -24202,16 +24202,16 @@
         <v>4381.530405273437</v>
       </c>
       <c r="E309" t="n">
-        <v>4234.467166341145</v>
+        <v>4234.467164713542</v>
       </c>
       <c r="F309" t="n">
-        <v>4287.780235595703</v>
+        <v>4287.780251464844</v>
       </c>
       <c r="G309" t="n">
-        <v>-0.4160814544937996</v>
+        <v>-0.4160814529602819</v>
       </c>
       <c r="H309" t="n">
-        <v>5038.988033260187</v>
+        <v>5038.987051168056</v>
       </c>
       <c r="I309" t="n">
         <v>3669.905008549105</v>
@@ -24220,7 +24220,7 @@
         <v>30.84807341916644</v>
       </c>
       <c r="K309" t="n">
-        <v>4.935194361936412</v>
+        <v>4.935173910205237</v>
       </c>
       <c r="L309" t="n">
         <v>57.08333333333333</v>
@@ -24972,13 +24972,13 @@
         <v>713.5928796386719</v>
       </c>
       <c r="E319" t="n">
-        <v>665.3104402669271</v>
+        <v>665.310439860026</v>
       </c>
       <c r="F319" t="n">
-        <v>670.9563140869141</v>
+        <v>670.9563143920899</v>
       </c>
       <c r="G319" t="n">
-        <v>0.5372457035959677</v>
+        <v>0.5372456573765616</v>
       </c>
       <c r="H319" t="n">
         <v>792.3323631991859</v>
@@ -27593,10 +27593,10 @@
         <v>741.6707450358073</v>
       </c>
       <c r="F353" t="n">
-        <v>740.193699645996</v>
+        <v>740.1936993408203</v>
       </c>
       <c r="G353" t="n">
-        <v>-0.03443717677112934</v>
+        <v>-0.03443705318295631</v>
       </c>
       <c r="H353" t="n">
         <v>837.8765073351432</v>
@@ -27827,7 +27827,7 @@
         <v>492.9074417114258</v>
       </c>
       <c r="G356" t="n">
-        <v>-0.2336420548912921</v>
+        <v>-0.2336418083935587</v>
       </c>
       <c r="H356" t="n">
         <v>561.4379586860567</v>
@@ -28437,13 +28437,13 @@
         <v>2271.031025390625</v>
       </c>
       <c r="E364" t="n">
-        <v>2264.332551269531</v>
+        <v>2264.332549641927</v>
       </c>
       <c r="F364" t="n">
-        <v>2285.68442565918</v>
+        <v>2285.684424438477</v>
       </c>
       <c r="G364" t="n">
-        <v>0.3556643643610968</v>
+        <v>0.3556640956165591</v>
       </c>
       <c r="H364" t="n">
         <v>2765.379504159864</v>
@@ -29290,7 +29290,7 @@
         <v>2459.972064208984</v>
       </c>
       <c r="G375" t="n">
-        <v>-0.8986223152252948</v>
+        <v>-0.8986223639600999</v>
       </c>
       <c r="H375" t="n">
         <v>3039.742679715149</v>
@@ -29524,7 +29524,7 @@
         <v>-1.239539365503595</v>
       </c>
       <c r="H378" t="n">
-        <v>297.5473847088064</v>
+        <v>297.5474157032224</v>
       </c>
       <c r="I378" t="n">
         <v>165</v>
@@ -29533,7 +29533,7 @@
         <v>36.94545861446497</v>
       </c>
       <c r="K378" t="n">
-        <v>31.6814373640864</v>
+        <v>31.68145108085707</v>
       </c>
       <c r="L378" t="n">
         <v>38.47222222222222</v>
@@ -30131,16 +30131,16 @@
         <v>783.0632104492188</v>
       </c>
       <c r="E386" t="n">
-        <v>767.3909529622396</v>
+        <v>767.3909525553386</v>
       </c>
       <c r="F386" t="n">
-        <v>795.0331997680664</v>
+        <v>795.0332019042969</v>
       </c>
       <c r="G386" t="n">
-        <v>-2.207784120097522</v>
+        <v>-2.207784004169033</v>
       </c>
       <c r="H386" t="n">
-        <v>1209.194135876196</v>
+        <v>1209.194260892545</v>
       </c>
       <c r="I386" t="n">
         <v>648.9423872407145</v>
@@ -30149,7 +30149,7 @@
         <v>28.84811361596362</v>
       </c>
       <c r="K386" t="n">
-        <v>44.61449507503708</v>
+        <v>44.61451002646275</v>
       </c>
       <c r="L386" t="n">
         <v>29.30555555555556</v>
@@ -31286,13 +31286,13 @@
         <v>410.9330133056641</v>
       </c>
       <c r="E401" t="n">
-        <v>428.4340374755859</v>
+        <v>428.4340368652344</v>
       </c>
       <c r="F401" t="n">
-        <v>418.0833335876465</v>
+        <v>418.0833332824707</v>
       </c>
       <c r="G401" t="n">
-        <v>0.9810505002082692</v>
+        <v>0.981050352064905</v>
       </c>
       <c r="H401" t="n">
         <v>478.7148398145708</v>
@@ -32293,7 +32293,7 @@
         <v>1505.06207824707</v>
       </c>
       <c r="G414" t="n">
-        <v>0.1827688736571798</v>
+        <v>0.1827688329555599</v>
       </c>
       <c r="H414" t="n">
         <v>1765.922465821425</v>
@@ -32672,22 +32672,22 @@
         <v>344.2162573242188</v>
       </c>
       <c r="E419" t="n">
-        <v>341.5193046061198</v>
+        <v>341.5193048095703</v>
       </c>
       <c r="F419" t="n">
-        <v>334.9288139343262</v>
+        <v>334.9288148498535</v>
       </c>
       <c r="G419" t="n">
-        <v>0.178560217271917</v>
+        <v>0.1785602625040905</v>
       </c>
       <c r="H419" t="n">
         <v>386.0870554430863</v>
       </c>
       <c r="I419" t="n">
-        <v>282.6708709611926</v>
+        <v>282.670901059285</v>
       </c>
       <c r="J419" t="n">
-        <v>14.44405251236969</v>
+        <v>14.44404032665245</v>
       </c>
       <c r="K419" t="n">
         <v>19.34684866865111</v>
@@ -32755,7 +32755,7 @@
         <v>514.1510260009766</v>
       </c>
       <c r="G420" t="n">
-        <v>-0.940248082138595</v>
+        <v>-0.9402479074055337</v>
       </c>
       <c r="H420" t="n">
         <v>750.0847124549373</v>
@@ -33057,22 +33057,22 @@
         <v>38790.08109375</v>
       </c>
       <c r="E424" t="n">
-        <v>36471.1833984375</v>
+        <v>36471.18342447917</v>
       </c>
       <c r="F424" t="n">
-        <v>36261.88126953125</v>
+        <v>36261.88124023438</v>
       </c>
       <c r="G424" t="n">
-        <v>-1.025693024803009</v>
+        <v>-1.025693183910437</v>
       </c>
       <c r="H424" t="n">
         <v>45150.8475731383</v>
       </c>
       <c r="I424" t="n">
-        <v>29525.27549507192</v>
+        <v>29525.27356749276</v>
       </c>
       <c r="J424" t="n">
-        <v>22.94550818351841</v>
+        <v>22.94551621010616</v>
       </c>
       <c r="K424" t="n">
         <v>24.38250020148292</v>
@@ -33291,10 +33291,10 @@
         <v>1662.974524739583</v>
       </c>
       <c r="F427" t="n">
-        <v>1774.630518188477</v>
+        <v>1774.630525512695</v>
       </c>
       <c r="G427" t="n">
-        <v>-2.406336982273416</v>
+        <v>-2.406336841549617</v>
       </c>
       <c r="H427" t="n">
         <v>2541.747782091032</v>
@@ -33753,10 +33753,10 @@
         <v>732.1738260904948</v>
       </c>
       <c r="F433" t="n">
-        <v>745.6483972167969</v>
+        <v>745.6483959960938</v>
       </c>
       <c r="G433" t="n">
-        <v>-0.5563545129803282</v>
+        <v>-0.5563547162532378</v>
       </c>
       <c r="H433" t="n">
         <v>879.2203373423794</v>
@@ -33981,16 +33981,16 @@
         <v>78.08859008789062</v>
       </c>
       <c r="E436" t="n">
-        <v>77.50556777954101</v>
+        <v>77.50556762695312</v>
       </c>
       <c r="F436" t="n">
-        <v>77.3435466003418</v>
+        <v>77.34354675292968</v>
       </c>
       <c r="G436" t="n">
-        <v>-0.7736157587643899</v>
+        <v>-0.7736157572499569</v>
       </c>
       <c r="H436" t="n">
-        <v>87.39771312453149</v>
+        <v>87.39772087555167</v>
       </c>
       <c r="I436" t="n">
         <v>71.42454681386315</v>
@@ -33999,7 +33999,7 @@
         <v>6.7560151256014</v>
       </c>
       <c r="K436" t="n">
-        <v>14.61995163872982</v>
+        <v>14.61996180400218</v>
       </c>
       <c r="L436" t="n">
         <v>46.38888888888889</v>
@@ -34289,22 +34289,22 @@
         <v>340.1293951416015</v>
       </c>
       <c r="E440" t="n">
-        <v>362.7056746419271</v>
+        <v>362.7056748453776</v>
       </c>
       <c r="F440" t="n">
         <v>353.6975523376465</v>
       </c>
       <c r="G440" t="n">
-        <v>0.2074144759972141</v>
+        <v>0.2074146059569903</v>
       </c>
       <c r="H440" t="n">
         <v>409.9712889887167</v>
       </c>
       <c r="I440" t="n">
-        <v>309.8384816659088</v>
+        <v>309.838511773213</v>
       </c>
       <c r="J440" t="n">
-        <v>7.313977983705233</v>
+        <v>7.3139675559035</v>
       </c>
       <c r="K440" t="n">
         <v>23.29963578608019</v>
@@ -34911,7 +34911,7 @@
         <v>1511.314482421875</v>
       </c>
       <c r="G448" t="n">
-        <v>-1.848489174260071</v>
+        <v>-1.848489213166316</v>
       </c>
       <c r="H448" t="n">
         <v>1970.727757857954</v>
@@ -34985,10 +34985,10 @@
         <v>1272.152047119141</v>
       </c>
       <c r="F449" t="n">
-        <v>1354.830379943848</v>
+        <v>1354.830377502441</v>
       </c>
       <c r="G449" t="n">
-        <v>-1.331222729958592</v>
+        <v>-1.331222951618438</v>
       </c>
       <c r="H449" t="n">
         <v>1729.008500794829</v>
@@ -35373,7 +35373,7 @@
         <v>130.1808089828491</v>
       </c>
       <c r="G454" t="n">
-        <v>-2.360696721468536</v>
+        <v>-2.360696609724988</v>
       </c>
       <c r="H454" t="n">
         <v>190.7660872777346</v>
@@ -35444,13 +35444,13 @@
         <v>300.4292059326172</v>
       </c>
       <c r="E455" t="n">
-        <v>274.8845959472656</v>
+        <v>274.8845961507162</v>
       </c>
       <c r="F455" t="n">
-        <v>291.2335159301758</v>
+        <v>291.2335166931152</v>
       </c>
       <c r="G455" t="n">
-        <v>-2.059731255553576</v>
+        <v>-2.059731099496231</v>
       </c>
       <c r="H455" t="n">
         <v>411.0263372414121</v>
@@ -36303,10 +36303,10 @@
         <v>387.7999877929688</v>
       </c>
       <c r="I466" t="n">
-        <v>221.2469540684675</v>
+        <v>221.246969139635</v>
       </c>
       <c r="J466" t="n">
-        <v>23.41412289385472</v>
+        <v>23.41411448698288</v>
       </c>
       <c r="K466" t="n">
         <v>42.02527197584256</v>
@@ -36599,22 +36599,22 @@
         <v>406.6723223876953</v>
       </c>
       <c r="E470" t="n">
-        <v>422.16287109375</v>
+        <v>422.1628702799479</v>
       </c>
       <c r="F470" t="n">
-        <v>417.9295042419433</v>
+        <v>417.9295037841797</v>
       </c>
       <c r="G470" t="n">
-        <v>-0.1955105471934226</v>
+        <v>-0.1955104383037032</v>
       </c>
       <c r="H470" t="n">
         <v>472.8081629796919</v>
       </c>
       <c r="I470" t="n">
-        <v>366.44040619655</v>
+        <v>366.4404365248346</v>
       </c>
       <c r="J470" t="n">
-        <v>10.61826131862089</v>
+        <v>10.61825216334826</v>
       </c>
       <c r="K470" t="n">
         <v>16.6419528457955</v>
@@ -36682,7 +36682,7 @@
         <v>326.1201480102539</v>
       </c>
       <c r="G471" t="n">
-        <v>-0.9030960732798521</v>
+        <v>-0.9030959354371371</v>
       </c>
       <c r="H471" t="n">
         <v>391.6499938964844</v>
@@ -36830,13 +36830,13 @@
         <v>4546.74939453125</v>
       </c>
       <c r="E473" t="n">
-        <v>4703.907934570312</v>
+        <v>4703.907931315104</v>
       </c>
       <c r="F473" t="n">
-        <v>4764.341051025391</v>
+        <v>4764.341053466796</v>
       </c>
       <c r="G473" t="n">
-        <v>-0.221264520042963</v>
+        <v>-0.2212644178962608</v>
       </c>
       <c r="H473" t="n">
         <v>5612.405266256894</v>
@@ -36984,25 +36984,25 @@
         <v>239.81611328125</v>
       </c>
       <c r="E475" t="n">
-        <v>227.154380086263</v>
+        <v>227.1543797810872</v>
       </c>
       <c r="F475" t="n">
-        <v>227.1902266693115</v>
+        <v>227.1902265167236</v>
       </c>
       <c r="G475" t="n">
-        <v>-1.029159526908618</v>
+        <v>-1.029159363123378</v>
       </c>
       <c r="H475" t="n">
-        <v>286.0804516993438</v>
+        <v>286.08038637852</v>
       </c>
       <c r="I475" t="n">
-        <v>171.9528178807998</v>
+        <v>171.952833032562</v>
       </c>
       <c r="J475" t="n">
-        <v>27.20931717722577</v>
+        <v>27.20930596807452</v>
       </c>
       <c r="K475" t="n">
-        <v>30.78561054908824</v>
+        <v>30.78558068677584</v>
       </c>
       <c r="L475" t="n">
         <v>42.36111111111111</v>
@@ -37600,16 +37600,16 @@
         <v>219.2686279296875</v>
       </c>
       <c r="E483" t="n">
-        <v>211.8142926025391</v>
+        <v>211.8142923990885</v>
       </c>
       <c r="F483" t="n">
-        <v>216.2095718383789</v>
+        <v>216.209571685791</v>
       </c>
       <c r="G483" t="n">
-        <v>-1.082969093368147</v>
+        <v>-1.082969059597283</v>
       </c>
       <c r="H483" t="n">
-        <v>272.099752952214</v>
+        <v>272.0997840702363</v>
       </c>
       <c r="I483" t="n">
         <v>173.9540675101702</v>
@@ -37618,7 +37618,7 @@
         <v>24.0557384719625</v>
       </c>
       <c r="K483" t="n">
-        <v>26.0888550066207</v>
+        <v>26.08886942646402</v>
       </c>
       <c r="L483" t="n">
         <v>36.38888888888889</v>
@@ -38370,13 +38370,13 @@
         <v>2860.08083984375</v>
       </c>
       <c r="E493" t="n">
-        <v>2827.4183203125</v>
+        <v>2827.418321940104</v>
       </c>
       <c r="F493" t="n">
-        <v>2762.587742919922</v>
+        <v>2762.587739257813</v>
       </c>
       <c r="G493" t="n">
-        <v>-0.9747212547986273</v>
+        <v>-0.9747214293970963</v>
       </c>
       <c r="H493" t="n">
         <v>3415.14446256242</v>
@@ -38447,13 +38447,13 @@
         <v>345.9271099853515</v>
       </c>
       <c r="E494" t="n">
-        <v>343.2607312011719</v>
+        <v>343.2607307942708</v>
       </c>
       <c r="F494" t="n">
-        <v>343.7914907836914</v>
+        <v>343.7914895629883</v>
       </c>
       <c r="G494" t="n">
-        <v>-0.7069631598965009</v>
+        <v>-0.7069629873549421</v>
       </c>
       <c r="H494" t="n">
         <v>381.3442016302781</v>
@@ -38524,13 +38524,13 @@
         <v>914.145732421875</v>
       </c>
       <c r="E495" t="n">
-        <v>968.4919584147135</v>
+        <v>968.4919596354167</v>
       </c>
       <c r="F495" t="n">
-        <v>947.483913269043</v>
+        <v>947.483916015625</v>
       </c>
       <c r="G495" t="n">
-        <v>0.7385911290077596</v>
+        <v>0.7385911268509071</v>
       </c>
       <c r="H495" t="n">
         <v>1224.72508309492</v>
@@ -39768,10 +39768,10 @@
         <v>272.3321550846217</v>
       </c>
       <c r="I511" t="n">
-        <v>150.8694736101529</v>
+        <v>150.869488714561</v>
       </c>
       <c r="J511" t="n">
-        <v>31.12659380137291</v>
+        <v>31.12658067353906</v>
       </c>
       <c r="K511" t="n">
         <v>37.6596838517907</v>
@@ -39836,10 +39836,10 @@
         <v>848.791337076823</v>
       </c>
       <c r="F512" t="n">
-        <v>861.6536868286133</v>
+        <v>861.6536874389649</v>
       </c>
       <c r="G512" t="n">
-        <v>-0.5120604213192825</v>
+        <v>-0.5120604209584267</v>
       </c>
       <c r="H512" t="n">
         <v>962.6932158005569</v>
@@ -40064,22 +40064,22 @@
         <v>239.4448541259766</v>
       </c>
       <c r="E515" t="n">
-        <v>261.3856382242839</v>
+        <v>261.3856383260091</v>
       </c>
       <c r="F515" t="n">
         <v>254.914808883667</v>
       </c>
       <c r="G515" t="n">
-        <v>-0.1794575144809074</v>
+        <v>-0.1794576934121217</v>
       </c>
       <c r="H515" t="n">
         <v>306.197022156633</v>
       </c>
       <c r="I515" t="n">
-        <v>219.1296196581114</v>
+        <v>219.1296348793021</v>
       </c>
       <c r="J515" t="n">
-        <v>7.082736812388979</v>
+        <v>7.082729374204</v>
       </c>
       <c r="K515" t="n">
         <v>30.49095679572507</v>
@@ -40686,7 +40686,7 @@
         <v>580.0119900512695</v>
       </c>
       <c r="G523" t="n">
-        <v>-0.2072193834312008</v>
+        <v>-0.2072195406239707</v>
       </c>
       <c r="H523" t="n">
         <v>732.5560380476754</v>
@@ -40911,13 +40911,13 @@
         <v>389.8279357910156</v>
       </c>
       <c r="E526" t="n">
-        <v>407.986787109375</v>
+        <v>407.9867854817708</v>
       </c>
       <c r="F526" t="n">
-        <v>392.4603887939453</v>
+        <v>392.4603883361817</v>
       </c>
       <c r="G526" t="n">
-        <v>-0.1262491229729212</v>
+        <v>-0.1262490455565701</v>
       </c>
       <c r="H526" t="n">
         <v>476.8288845013619</v>
@@ -41065,13 +41065,13 @@
         <v>19.81838497161865</v>
       </c>
       <c r="E528" t="n">
-        <v>20.66237737019857</v>
+        <v>20.66237734476725</v>
       </c>
       <c r="F528" t="n">
         <v>20.69657948493958</v>
       </c>
       <c r="G528" t="n">
-        <v>-1.314445276420295</v>
+        <v>-1.314445186669422</v>
       </c>
       <c r="H528" t="n">
         <v>23.83526224893035</v>
@@ -41222,10 +41222,10 @@
         <v>409.705214436849</v>
       </c>
       <c r="F530" t="n">
-        <v>419.2841236877441</v>
+        <v>419.2841244506836</v>
       </c>
       <c r="G530" t="n">
-        <v>-4.492260337543252</v>
+        <v>-4.492260296540007</v>
       </c>
       <c r="H530" t="n">
         <v>684.5682054144123</v>
@@ -42066,13 +42066,13 @@
         <v>2021.231184082031</v>
       </c>
       <c r="E541" t="n">
-        <v>2020.499153645833</v>
+        <v>2020.499156901042</v>
       </c>
       <c r="F541" t="n">
-        <v>2089.261745605469</v>
+        <v>2089.261746826172</v>
       </c>
       <c r="G541" t="n">
-        <v>-0.9082485435228604</v>
+        <v>-0.9082483708840905</v>
       </c>
       <c r="H541" t="n">
         <v>2486.766809421043</v>
@@ -42374,25 +42374,25 @@
         <v>194.9868051147461</v>
       </c>
       <c r="E545" t="n">
-        <v>194.0252744547526</v>
+        <v>194.0252748616537</v>
       </c>
       <c r="F545" t="n">
-        <v>198.689977722168</v>
+        <v>198.6899781799316</v>
       </c>
       <c r="G545" t="n">
-        <v>-1.998821715633559</v>
+        <v>-1.998821268574968</v>
       </c>
       <c r="H545" t="n">
-        <v>239.2187037807859</v>
+        <v>239.2186728978909</v>
       </c>
       <c r="I545" t="n">
-        <v>156.7442971017576</v>
+        <v>156.7443123050878</v>
       </c>
       <c r="J545" t="n">
-        <v>15.16846712149804</v>
+        <v>15.16845595079457</v>
       </c>
       <c r="K545" t="n">
-        <v>32.51645142869062</v>
+        <v>32.51643432094951</v>
       </c>
       <c r="L545" t="n">
         <v>24.16666666666667</v>
@@ -44071,10 +44071,10 @@
         <v>2368.14739827474</v>
       </c>
       <c r="F567" t="n">
-        <v>2550.787868041992</v>
+        <v>2550.78785949707</v>
       </c>
       <c r="G567" t="n">
-        <v>-2.539591693901633</v>
+        <v>-2.5395917931052</v>
       </c>
       <c r="H567" t="n">
         <v>3287.161392369851</v>
@@ -44459,7 +44459,7 @@
         <v>1286.435960388184</v>
       </c>
       <c r="G572" t="n">
-        <v>-2.642913711185302</v>
+        <v>-2.642913666214863</v>
       </c>
       <c r="H572" t="n">
         <v>1691.399159307065</v>
@@ -44761,22 +44761,22 @@
         <v>832.1171362304688</v>
       </c>
       <c r="E576" t="n">
-        <v>956.1952237955729</v>
+        <v>956.1952242024739</v>
       </c>
       <c r="F576" t="n">
-        <v>926.8351327514648</v>
+        <v>926.8351348876953</v>
       </c>
       <c r="G576" t="n">
-        <v>-0.3484423325116559</v>
+        <v>-0.3484425605944863</v>
       </c>
       <c r="H576" t="n">
         <v>1282.80960014975</v>
       </c>
       <c r="I576" t="n">
-        <v>743.4272688553443</v>
+        <v>743.4273285628773</v>
       </c>
       <c r="J576" t="n">
-        <v>3.352406856015211</v>
+        <v>3.352398555382452</v>
       </c>
       <c r="K576" t="n">
         <v>66.95641841746524</v>
@@ -46150,10 +46150,10 @@
         <v>145.620680847168</v>
       </c>
       <c r="F594" t="n">
-        <v>148.5189074707031</v>
+        <v>148.5189081573486</v>
       </c>
       <c r="G594" t="n">
-        <v>-1.27043819281637</v>
+        <v>-1.270438187017386</v>
       </c>
       <c r="H594" t="n">
         <v>184.9587904135824</v>
@@ -47000,10 +47000,10 @@
         <v>136805.216328125</v>
       </c>
       <c r="G605" t="n">
-        <v>-2.000747380343781</v>
+        <v>-2.00074721581035</v>
       </c>
       <c r="H605" t="n">
-        <v>163308.5022863474</v>
+        <v>163308.4863287346</v>
       </c>
       <c r="I605" t="n">
         <v>121787.4350540836</v>
@@ -47012,7 +47012,7 @@
         <v>6.698199155186857</v>
       </c>
       <c r="K605" t="n">
-        <v>25.67509506818073</v>
+        <v>25.67508278789843</v>
       </c>
       <c r="L605" t="n">
         <v>27.5</v>
@@ -47077,7 +47077,7 @@
         <v>34.24443413734436</v>
       </c>
       <c r="G606" t="n">
-        <v>-2.213592044327672</v>
+        <v>-2.213591991068165</v>
       </c>
       <c r="H606" t="n">
         <v>40.26070662850351</v>
@@ -47151,13 +47151,13 @@
         <v>1076.401049397786</v>
       </c>
       <c r="F607" t="n">
-        <v>1106.948691101074</v>
+        <v>1106.948689880371</v>
       </c>
       <c r="G607" t="n">
-        <v>-2.030551534078695</v>
+        <v>-2.030551536272451</v>
       </c>
       <c r="H607" t="n">
-        <v>1400.476774401248</v>
+        <v>1400.476649260813</v>
       </c>
       <c r="I607" t="n">
         <v>941.5197177909594</v>
@@ -47166,7 +47166,7 @@
         <v>8.431082761532505</v>
       </c>
       <c r="K607" t="n">
-        <v>37.18059956018131</v>
+        <v>37.18058730232718</v>
       </c>
       <c r="L607" t="n">
         <v>25.55555555555555</v>
@@ -48232,7 +48232,7 @@
         <v>98.11523609161377</v>
       </c>
       <c r="G621" t="n">
-        <v>-2.543952222772394</v>
+        <v>-2.543952259699156</v>
       </c>
       <c r="H621" t="n">
         <v>124.8273096544699</v>
@@ -48463,7 +48463,7 @@
         <v>538.8343041992188</v>
       </c>
       <c r="G624" t="n">
-        <v>-1.519035279946512</v>
+        <v>-1.519035389803924</v>
       </c>
       <c r="H624" t="n">
         <v>653.9340000086492</v>
@@ -49150,13 +49150,13 @@
         <v>451.2804327392578</v>
       </c>
       <c r="E633" t="n">
-        <v>466.0290077718099</v>
+        <v>466.0290081787109</v>
       </c>
       <c r="F633" t="n">
-        <v>469.1914036560058</v>
+        <v>469.1914038085937</v>
       </c>
       <c r="G633" t="n">
-        <v>-0.8325895566589581</v>
+        <v>-0.8325894924260835</v>
       </c>
       <c r="H633" t="n">
         <v>555.1842484654879</v>
@@ -49458,13 +49458,13 @@
         <v>7596.190888671875</v>
       </c>
       <c r="E637" t="n">
-        <v>7820.426324869792</v>
+        <v>7820.426318359375</v>
       </c>
       <c r="F637" t="n">
-        <v>7858.060397949219</v>
+        <v>7858.060393066407</v>
       </c>
       <c r="G637" t="n">
-        <v>-1.561341144436235</v>
+        <v>-1.561341024966423</v>
       </c>
       <c r="H637" t="n">
         <v>10437.38206257999</v>
@@ -50388,10 +50388,10 @@
         <v>2050.181427001953</v>
       </c>
       <c r="G649" t="n">
-        <v>-1.370371287507122</v>
+        <v>-1.370371345427668</v>
       </c>
       <c r="H649" t="n">
-        <v>2448.345231432346</v>
+        <v>2448.345479475883</v>
       </c>
       <c r="I649" t="n">
         <v>1761.237851420491</v>
@@ -50400,7 +50400,7 @@
         <v>3.858768973002169</v>
       </c>
       <c r="K649" t="n">
-        <v>33.84787321166374</v>
+        <v>33.84788677188371</v>
       </c>
       <c r="L649" t="n">
         <v>13.19444444444444</v>
@@ -50462,13 +50462,13 @@
         <v>191.1998132324219</v>
       </c>
       <c r="F650" t="n">
-        <v>205.2517964935303</v>
+        <v>205.251796875</v>
       </c>
       <c r="G650" t="n">
-        <v>-2.711629373369862</v>
+        <v>-2.711629333284471</v>
       </c>
       <c r="H650" t="n">
-        <v>263.220498300555</v>
+        <v>263.2205288662585</v>
       </c>
       <c r="I650" t="n">
         <v>167.0916913788894</v>
@@ -50477,7 +50477,7 @@
         <v>5.57077520777971</v>
       </c>
       <c r="K650" t="n">
-        <v>49.21797472114364</v>
+        <v>49.21799204864055</v>
       </c>
       <c r="L650" t="n">
         <v>12.77777777777778</v>
@@ -51466,7 +51466,7 @@
         <v>1755.072418823242</v>
       </c>
       <c r="G663" t="n">
-        <v>-3.916099530774209</v>
+        <v>-3.916099627092218</v>
       </c>
       <c r="H663" t="n">
         <v>2504.019782423858</v>
@@ -51928,10 +51928,10 @@
         <v>1078.484371643066</v>
       </c>
       <c r="G669" t="n">
-        <v>-1.750441389219159</v>
+        <v>-1.750441498478206</v>
       </c>
       <c r="H669" t="n">
-        <v>1284.135475005729</v>
+        <v>1284.135346691241</v>
       </c>
       <c r="I669" t="n">
         <v>859.5499877929688</v>
@@ -51940,7 +51940,7 @@
         <v>2.146473441806984</v>
       </c>
       <c r="K669" t="n">
-        <v>46.25688781386439</v>
+        <v>46.25687319945795</v>
       </c>
       <c r="L669" t="n">
         <v>8.194444444444445</v>
@@ -52849,10 +52849,10 @@
         <v>290.9107507324219</v>
       </c>
       <c r="F681" t="n">
-        <v>307.3070678710938</v>
+        <v>307.307067565918</v>
       </c>
       <c r="G681" t="n">
-        <v>-4.138879869675216</v>
+        <v>-4.138879873615275</v>
       </c>
       <c r="H681" t="n">
         <v>407.1428648264985</v>
@@ -53234,10 +53234,10 @@
         <v>509.8062060546875</v>
       </c>
       <c r="F686" t="n">
-        <v>557.0795727539063</v>
+        <v>557.079573059082</v>
       </c>
       <c r="G686" t="n">
-        <v>-4.791452797635277</v>
+        <v>-4.791452646163763</v>
       </c>
       <c r="H686" t="n">
         <v>845.3898333433813</v>
@@ -55470,7 +55470,7 @@
         <v>458.8093499755859</v>
       </c>
       <c r="G715" t="n">
-        <v>-5.259885633076578</v>
+        <v>-5.259885812181231</v>
       </c>
       <c r="H715" t="n">
         <v>606.8956852082865</v>

--- a/output/minervini_daily.xlsx
+++ b/output/minervini_daily.xlsx
@@ -1345,10 +1345,10 @@
         <v>812.7999877929688</v>
       </c>
       <c r="I12" t="n">
-        <v>262.0239102537355</v>
+        <v>262.023880250306</v>
       </c>
       <c r="J12" t="n">
-        <v>207.185715851131</v>
+        <v>207.1857510258829</v>
       </c>
       <c r="K12" t="n">
         <v>0.9814838041106055</v>
@@ -3338,19 +3338,19 @@
         <v>629.6343754069011</v>
       </c>
       <c r="F38" t="n">
-        <v>592.579342956543</v>
+        <v>592.5793426513671</v>
       </c>
       <c r="G38" t="n">
-        <v>6.256151013039757</v>
+        <v>6.256151074608107</v>
       </c>
       <c r="H38" t="n">
         <v>844</v>
       </c>
       <c r="I38" t="n">
-        <v>399.8349725758499</v>
+        <v>399.8350028638013</v>
       </c>
       <c r="J38" t="n">
-        <v>97.08130955215881</v>
+        <v>97.08129462302782</v>
       </c>
       <c r="K38" t="n">
         <v>7.106598984771573</v>
@@ -4262,10 +4262,10 @@
         <v>245.2917078653971</v>
       </c>
       <c r="F50" t="n">
-        <v>233.937264251709</v>
+        <v>233.937264175415</v>
       </c>
       <c r="G50" t="n">
-        <v>6.891633198212199</v>
+        <v>6.891633200614633</v>
       </c>
       <c r="H50" t="n">
         <v>388.75</v>
@@ -5565,25 +5565,25 @@
         <v>12097</v>
       </c>
       <c r="D67" t="n">
-        <v>11009.639140625</v>
+        <v>11009.6391015625</v>
       </c>
       <c r="E67" t="n">
-        <v>10596.02934895833</v>
+        <v>10596.02940104167</v>
       </c>
       <c r="F67" t="n">
-        <v>10190.40307617188</v>
+        <v>10190.40309814453</v>
       </c>
       <c r="G67" t="n">
-        <v>3.139076991845702</v>
+        <v>3.139077086807207</v>
       </c>
       <c r="H67" t="n">
         <v>12865.82946046676</v>
       </c>
       <c r="I67" t="n">
-        <v>6613.3742727433</v>
+        <v>6613.373792726331</v>
       </c>
       <c r="J67" t="n">
-        <v>82.91721443707181</v>
+        <v>82.91722771370935</v>
       </c>
       <c r="K67" t="n">
         <v>6.355538236478098</v>
@@ -6184,13 +6184,13 @@
         <v>156.7787719726562</v>
       </c>
       <c r="E75" t="n">
-        <v>138.6068893941244</v>
+        <v>138.606889444987</v>
       </c>
       <c r="F75" t="n">
-        <v>133.0773069763184</v>
+        <v>133.0773069000244</v>
       </c>
       <c r="G75" t="n">
-        <v>5.125220747062009</v>
+        <v>5.125220655114249</v>
       </c>
       <c r="H75" t="n">
         <v>173.2700042724609</v>
@@ -8035,10 +8035,10 @@
         <v>230.5883953857422</v>
       </c>
       <c r="F99" t="n">
-        <v>220.5138858032226</v>
+        <v>220.5138857269287</v>
       </c>
       <c r="G99" t="n">
-        <v>3.143815262521299</v>
+        <v>3.143815300451069</v>
       </c>
       <c r="H99" t="n">
         <v>289.6499938964844</v>
@@ -8269,7 +8269,7 @@
         <v>3017.200604248047</v>
       </c>
       <c r="G102" t="n">
-        <v>4.247965782822205</v>
+        <v>4.247965738853776</v>
       </c>
       <c r="H102" t="n">
         <v>3796</v>
@@ -8725,13 +8725,13 @@
         <v>4947.8980078125</v>
       </c>
       <c r="E108" t="n">
-        <v>4530.501004231771</v>
+        <v>4530.501002604166</v>
       </c>
       <c r="F108" t="n">
-        <v>4359.918782958985</v>
+        <v>4359.918780517578</v>
       </c>
       <c r="G108" t="n">
-        <v>3.335265458700043</v>
+        <v>3.335265610115368</v>
       </c>
       <c r="H108" t="n">
         <v>5250</v>
@@ -9264,22 +9264,22 @@
         <v>1839.062414550781</v>
       </c>
       <c r="E115" t="n">
-        <v>1600.098318684896</v>
+        <v>1600.098317057292</v>
       </c>
       <c r="F115" t="n">
         <v>1557.674750976563</v>
       </c>
       <c r="G115" t="n">
-        <v>2.630118703307027</v>
+        <v>2.630118662035263</v>
       </c>
       <c r="H115" t="n">
         <v>1988.900024414062</v>
       </c>
       <c r="I115" t="n">
-        <v>1266.16157090969</v>
+        <v>1266.161452106784</v>
       </c>
       <c r="J115" t="n">
-        <v>50.77064759029564</v>
+        <v>50.77066173698366</v>
       </c>
       <c r="K115" t="n">
         <v>4.185438680673781</v>
@@ -11349,16 +11349,16 @@
         <v>1871.105329589844</v>
       </c>
       <c r="G142" t="n">
-        <v>8.725931241183327</v>
+        <v>8.72593120262235</v>
       </c>
       <c r="H142" t="n">
         <v>2983.800048828125</v>
       </c>
       <c r="I142" t="n">
-        <v>1175.257587358084</v>
+        <v>1175.257470329055</v>
       </c>
       <c r="J142" t="n">
-        <v>106.2866837383004</v>
+        <v>106.2867042797826</v>
       </c>
       <c r="K142" t="n">
         <v>23.07375717774875</v>
@@ -12812,7 +12812,7 @@
         <v>994.3643133544922</v>
       </c>
       <c r="G161" t="n">
-        <v>3.331079135207449</v>
+        <v>3.331079102438195</v>
       </c>
       <c r="H161" t="n">
         <v>1153.699951171875</v>
@@ -13268,13 +13268,13 @@
         <v>7359.0525</v>
       </c>
       <c r="E167" t="n">
-        <v>6803.183053385416</v>
+        <v>6803.183046875</v>
       </c>
       <c r="F167" t="n">
-        <v>6370.405021972656</v>
+        <v>6370.40501953125</v>
       </c>
       <c r="G167" t="n">
-        <v>4.457206216596932</v>
+        <v>4.457206134747849</v>
       </c>
       <c r="H167" t="n">
         <v>7832.294844565128</v>
@@ -13807,13 +13807,13 @@
         <v>306.0007946777343</v>
       </c>
       <c r="E174" t="n">
-        <v>295.5614795939127</v>
+        <v>295.5614790852865</v>
       </c>
       <c r="F174" t="n">
-        <v>284.2275997161865</v>
+        <v>284.2275991058349</v>
       </c>
       <c r="G174" t="n">
-        <v>1.302283164395535</v>
+        <v>1.302283112135982</v>
       </c>
       <c r="H174" t="n">
         <v>359.3387168134344</v>
@@ -14112,16 +14112,16 @@
         <v>1846.5</v>
       </c>
       <c r="D178" t="n">
-        <v>1733.154272460938</v>
+        <v>1733.154282226563</v>
       </c>
       <c r="E178" t="n">
-        <v>1444.400016276042</v>
+        <v>1444.400021972656</v>
       </c>
       <c r="F178" t="n">
-        <v>1518.129978637695</v>
+        <v>1518.129982910156</v>
       </c>
       <c r="G178" t="n">
-        <v>0.7553147441439867</v>
+        <v>0.7553149052574648</v>
       </c>
       <c r="H178" t="n">
         <v>2021.199951171875</v>
@@ -14352,7 +14352,7 @@
         <v>454.349242553711</v>
       </c>
       <c r="G181" t="n">
-        <v>1.516439332328168</v>
+        <v>1.51643936693826</v>
       </c>
       <c r="H181" t="n">
         <v>529.9163379046904</v>
@@ -15584,7 +15584,7 @@
         <v>509.3152810668946</v>
       </c>
       <c r="G197" t="n">
-        <v>1.814851908357196</v>
+        <v>1.814851970470621</v>
       </c>
       <c r="H197" t="n">
         <v>609.0499877929688</v>
@@ -15963,13 +15963,13 @@
         <v>4730.212099609375</v>
       </c>
       <c r="E202" t="n">
-        <v>4370.84908203125</v>
+        <v>4370.849085286458</v>
       </c>
       <c r="F202" t="n">
-        <v>4368.026706542969</v>
+        <v>4368.026732177735</v>
       </c>
       <c r="G202" t="n">
-        <v>0.7103704847668979</v>
+        <v>0.7103703104996084</v>
       </c>
       <c r="H202" t="n">
         <v>5149.89990234375</v>
@@ -17044,10 +17044,10 @@
         <v>149.393951365153</v>
       </c>
       <c r="F216" t="n">
-        <v>151.3906976699829</v>
+        <v>151.3906978225708</v>
       </c>
       <c r="G216" t="n">
-        <v>-0.2625995598982134</v>
+        <v>-0.2625996097652794</v>
       </c>
       <c r="H216" t="n">
         <v>212.3300018310547</v>
@@ -17272,22 +17272,22 @@
         <v>2101.110002441406</v>
       </c>
       <c r="E219" t="n">
-        <v>1947.099948730469</v>
+        <v>1947.099949544271</v>
       </c>
       <c r="F219" t="n">
-        <v>1819.827434082031</v>
+        <v>1819.827437133789</v>
       </c>
       <c r="G219" t="n">
-        <v>4.255020255245023</v>
+        <v>4.255020393621489</v>
       </c>
       <c r="H219" t="n">
         <v>2295</v>
       </c>
       <c r="I219" t="n">
-        <v>1174.091262727543</v>
+        <v>1174.091384580817</v>
       </c>
       <c r="J219" t="n">
-        <v>65.65152012935054</v>
+        <v>65.6515029371794</v>
       </c>
       <c r="K219" t="n">
         <v>18.0009240162055</v>
@@ -17660,10 +17660,10 @@
         <v>1400.955205891927</v>
       </c>
       <c r="F224" t="n">
-        <v>1324.914420166016</v>
+        <v>1324.914421386719</v>
       </c>
       <c r="G224" t="n">
-        <v>2.299080518342556</v>
+        <v>2.29908039565101</v>
       </c>
       <c r="H224" t="n">
         <v>1766.733188761222</v>
@@ -18199,10 +18199,10 @@
         <v>1675.087139485677</v>
       </c>
       <c r="F231" t="n">
-        <v>1680.709582519531</v>
+        <v>1680.709583129883</v>
       </c>
       <c r="G231" t="n">
-        <v>1.039188158256055</v>
+        <v>1.039188269096125</v>
       </c>
       <c r="H231" t="n">
         <v>1952.5</v>
@@ -18276,10 +18276,10 @@
         <v>995.9606477864584</v>
       </c>
       <c r="F232" t="n">
-        <v>955.2263647460937</v>
+        <v>955.2263659667968</v>
       </c>
       <c r="G232" t="n">
-        <v>2.75466323431548</v>
+        <v>2.754663298163007</v>
       </c>
       <c r="H232" t="n">
         <v>1303.791320684363</v>
@@ -18353,10 +18353,10 @@
         <v>311.1581471761068</v>
       </c>
       <c r="F233" t="n">
-        <v>306.7464491271973</v>
+        <v>306.7464488220215</v>
       </c>
       <c r="G233" t="n">
-        <v>2.546704464855098</v>
+        <v>2.546704729002824</v>
       </c>
       <c r="H233" t="n">
         <v>380.4567148307952</v>
@@ -18812,16 +18812,16 @@
         <v>1877.341997070313</v>
       </c>
       <c r="E239" t="n">
-        <v>1770.329895833333</v>
+        <v>1770.329894205729</v>
       </c>
       <c r="F239" t="n">
-        <v>1768.468278808594</v>
+        <v>1768.468275146484</v>
       </c>
       <c r="G239" t="n">
-        <v>-0.2496195187905781</v>
+        <v>-0.2496195193062101</v>
       </c>
       <c r="H239" t="n">
-        <v>2269.472253037084</v>
+        <v>2269.472002658311</v>
       </c>
       <c r="I239" t="n">
         <v>1353.205955540699</v>
@@ -18830,7 +18830,7 @@
         <v>49.52639072635292</v>
       </c>
       <c r="K239" t="n">
-        <v>12.16132379430404</v>
+        <v>12.16131142014325</v>
       </c>
       <c r="L239" t="n">
         <v>65.69444444444444</v>
@@ -20432,10 +20432,10 @@
         <v>165.1017255655925</v>
       </c>
       <c r="F260" t="n">
-        <v>164.5213877868652</v>
+        <v>164.5213877105713</v>
       </c>
       <c r="G260" t="n">
-        <v>-0.1913095136006904</v>
+        <v>-0.1913096060812691</v>
       </c>
       <c r="H260" t="n">
         <v>181.8519567776652</v>
@@ -20583,16 +20583,16 @@
         <v>183.4490631103516</v>
       </c>
       <c r="E262" t="n">
-        <v>178.7532151285807</v>
+        <v>178.753215230306</v>
       </c>
       <c r="F262" t="n">
-        <v>178.1156211090088</v>
+        <v>178.1156213378906</v>
       </c>
       <c r="G262" t="n">
-        <v>0.3585763646668738</v>
+        <v>0.3585762347794175</v>
       </c>
       <c r="H262" t="n">
-        <v>198.2251721274962</v>
+        <v>198.2251564414815</v>
       </c>
       <c r="I262" t="n">
         <v>164.6038301743624</v>
@@ -20601,7 +20601,7 @@
         <v>14.23184902812982</v>
       </c>
       <c r="K262" t="n">
-        <v>5.422099353500553</v>
+        <v>5.422091011206853</v>
       </c>
       <c r="L262" t="n">
         <v>53.33333333333334</v>
@@ -20663,10 +20663,10 @@
         <v>338.9012768554687</v>
       </c>
       <c r="F263" t="n">
-        <v>333.269701385498</v>
+        <v>333.2697012329102</v>
       </c>
       <c r="G263" t="n">
-        <v>0.8907877718639989</v>
+        <v>0.8907876790666069</v>
       </c>
       <c r="H263" t="n">
         <v>428.7550602808859</v>
@@ -21199,13 +21199,13 @@
         <v>287.6611639404297</v>
       </c>
       <c r="E270" t="n">
-        <v>283.5088430786133</v>
+        <v>283.5088434855143</v>
       </c>
       <c r="F270" t="n">
-        <v>266.8796357727051</v>
+        <v>266.8796362304687</v>
       </c>
       <c r="G270" t="n">
-        <v>1.686196845817434</v>
+        <v>1.686196665518791</v>
       </c>
       <c r="H270" t="n">
         <v>367.499792159746</v>
@@ -22046,13 +22046,13 @@
         <v>1145.806799316406</v>
       </c>
       <c r="E281" t="n">
-        <v>1104.818503417969</v>
+        <v>1104.81850382487</v>
       </c>
       <c r="F281" t="n">
-        <v>1068.224574584961</v>
+        <v>1068.224576721191</v>
       </c>
       <c r="G281" t="n">
-        <v>1.540398089192774</v>
+        <v>1.540397909332314</v>
       </c>
       <c r="H281" t="n">
         <v>1238.748718225596</v>
@@ -23047,13 +23047,13 @@
         <v>4448.775986328125</v>
       </c>
       <c r="E294" t="n">
-        <v>4235.81109375</v>
+        <v>4235.811085611979</v>
       </c>
       <c r="F294" t="n">
-        <v>4294.135026855469</v>
+        <v>4294.135028076172</v>
       </c>
       <c r="G294" t="n">
-        <v>-0.1113606331303196</v>
+        <v>-0.1113609167381013</v>
       </c>
       <c r="H294" t="n">
         <v>5038.987542214121</v>
@@ -24205,19 +24205,19 @@
         <v>380.4406172688802</v>
       </c>
       <c r="F309" t="n">
-        <v>364.466918182373</v>
+        <v>364.4669171905518</v>
       </c>
       <c r="G309" t="n">
-        <v>4.415040818792693</v>
+        <v>4.415040808515558</v>
       </c>
       <c r="H309" t="n">
         <v>443.3731066930094</v>
       </c>
       <c r="I309" t="n">
-        <v>191.8556522941023</v>
+        <v>191.8556371798532</v>
       </c>
       <c r="J309" t="n">
-        <v>88.16229581112908</v>
+        <v>88.16231063441936</v>
       </c>
       <c r="K309" t="n">
         <v>22.81803509501646</v>
@@ -25055,7 +25055,7 @@
         <v>419.6957844543457</v>
       </c>
       <c r="G320" t="n">
-        <v>1.119874705040291</v>
+        <v>1.119874667864651</v>
       </c>
       <c r="H320" t="n">
         <v>478.7148398145708</v>
@@ -25434,16 +25434,16 @@
         <v>1264.286374511719</v>
       </c>
       <c r="E325" t="n">
-        <v>1089.335329589844</v>
+        <v>1089.335328776042</v>
       </c>
       <c r="F325" t="n">
-        <v>1146.378229980469</v>
+        <v>1146.378231811523</v>
       </c>
       <c r="G325" t="n">
-        <v>-0.1315402796544851</v>
+        <v>-0.1315403856481767</v>
       </c>
       <c r="H325" t="n">
-        <v>1423.548053270148</v>
+        <v>1423.547927723126</v>
       </c>
       <c r="I325" t="n">
         <v>905.5050975494345</v>
@@ -25452,7 +25452,7 @@
         <v>38.13285559773889</v>
       </c>
       <c r="K325" t="n">
-        <v>13.81100077537336</v>
+        <v>13.81099073803589</v>
       </c>
       <c r="L325" t="n">
         <v>57.36111111111111</v>
@@ -28828,7 +28828,7 @@
         <v>158.8517290496826</v>
       </c>
       <c r="G369" t="n">
-        <v>-0.3220223684912371</v>
+        <v>-0.3220223207716533</v>
       </c>
       <c r="H369" t="n">
         <v>194.1708646001337</v>
@@ -29364,10 +29364,10 @@
         <v>1145.544513753255</v>
       </c>
       <c r="F376" t="n">
-        <v>1167.715065002441</v>
+        <v>1167.715068664551</v>
       </c>
       <c r="G376" t="n">
-        <v>-0.147786137827266</v>
+        <v>-0.1477861894789823</v>
       </c>
       <c r="H376" t="n">
         <v>1378.852549646065</v>
@@ -29441,10 +29441,10 @@
         <v>731.3741756184896</v>
       </c>
       <c r="F377" t="n">
-        <v>745.8220916748047</v>
+        <v>745.822092590332</v>
       </c>
       <c r="G377" t="n">
-        <v>-0.3708869297216921</v>
+        <v>-0.3708867261926985</v>
       </c>
       <c r="H377" t="n">
         <v>879.2203373423794</v>
@@ -29672,10 +29672,10 @@
         <v>488.4894838460286</v>
       </c>
       <c r="F380" t="n">
-        <v>492.7654722595215</v>
+        <v>492.7654718017578</v>
       </c>
       <c r="G380" t="n">
-        <v>-0.174757954890048</v>
+        <v>-0.1747577699071856</v>
       </c>
       <c r="H380" t="n">
         <v>561.4378970396333</v>
@@ -32447,7 +32447,7 @@
         <v>669.793309020996</v>
       </c>
       <c r="G416" t="n">
-        <v>0.1474806416711161</v>
+        <v>0.1474805502767573</v>
       </c>
       <c r="H416" t="n">
         <v>792.3323631991859</v>
@@ -32752,19 +32752,19 @@
         <v>361.9558243815104</v>
       </c>
       <c r="F420" t="n">
-        <v>354.0407511901856</v>
+        <v>354.0407514953613</v>
       </c>
       <c r="G420" t="n">
-        <v>0.2685237890785785</v>
+        <v>0.2685239621694313</v>
       </c>
       <c r="H420" t="n">
         <v>409.9712889887167</v>
       </c>
       <c r="I420" t="n">
-        <v>309.8384816659088</v>
+        <v>309.838511773213</v>
       </c>
       <c r="J420" t="n">
-        <v>7.604449939172286</v>
+        <v>7.604439483145109</v>
       </c>
       <c r="K420" t="n">
         <v>22.96679558908645</v>
@@ -33060,10 +33060,10 @@
         <v>741.6845418294271</v>
       </c>
       <c r="F424" t="n">
-        <v>738.9757214355469</v>
+        <v>738.9757223510742</v>
       </c>
       <c r="G424" t="n">
-        <v>-0.2926391270771322</v>
+        <v>-0.2926390035483006</v>
       </c>
       <c r="H424" t="n">
         <v>837.8765073351432</v>
@@ -33211,16 +33211,16 @@
         <v>1095.7085546875</v>
       </c>
       <c r="E426" t="n">
-        <v>1084.780229899088</v>
+        <v>1084.780230712891</v>
       </c>
       <c r="F426" t="n">
-        <v>1084.756518249512</v>
+        <v>1084.756518554688</v>
       </c>
       <c r="G426" t="n">
-        <v>-1.181273015131401</v>
+        <v>-1.181273069747746</v>
       </c>
       <c r="H426" t="n">
-        <v>1341.921447537333</v>
+        <v>1341.921323996723</v>
       </c>
       <c r="I426" t="n">
         <v>885.652283987356</v>
@@ -33229,7 +33229,7 @@
         <v>22.42954356154576</v>
       </c>
       <c r="K426" t="n">
-        <v>23.7592351847292</v>
+        <v>23.75922379114774</v>
       </c>
       <c r="L426" t="n">
         <v>37.36111111111111</v>
@@ -34141,7 +34141,7 @@
         <v>169.8823271942139</v>
       </c>
       <c r="G438" t="n">
-        <v>2.074713976289044</v>
+        <v>2.074713929496341</v>
       </c>
       <c r="H438" t="n">
         <v>211.8067938496122</v>
@@ -34366,13 +34366,13 @@
         <v>156.6641122436523</v>
       </c>
       <c r="E441" t="n">
-        <v>159.7786432902018</v>
+        <v>159.7786433919271</v>
       </c>
       <c r="F441" t="n">
-        <v>155.0355158233642</v>
+        <v>155.0355159759521</v>
       </c>
       <c r="G441" t="n">
-        <v>0.8658909970862494</v>
+        <v>0.865891046293199</v>
       </c>
       <c r="H441" t="n">
         <v>203.5447632528218</v>
@@ -34597,13 +34597,13 @@
         <v>405.8715234375</v>
       </c>
       <c r="E444" t="n">
-        <v>421.2447578938802</v>
+        <v>421.2447585042318</v>
       </c>
       <c r="F444" t="n">
-        <v>417.7933146667481</v>
+        <v>417.7933151245117</v>
       </c>
       <c r="G444" t="n">
-        <v>-0.1533241182523848</v>
+        <v>-0.1533241544950825</v>
       </c>
       <c r="H444" t="n">
         <v>472.8081629796919</v>
@@ -35219,7 +35219,7 @@
         <v>283.8766855621338</v>
       </c>
       <c r="G452" t="n">
-        <v>-0.2354850840294187</v>
+        <v>-0.2354851375280242</v>
       </c>
       <c r="H452" t="n">
         <v>324.9500122070312</v>
@@ -35524,10 +35524,10 @@
         <v>2257.847731933594</v>
       </c>
       <c r="F456" t="n">
-        <v>2284.03543762207</v>
+        <v>2284.035449829102</v>
       </c>
       <c r="G456" t="n">
-        <v>0.08972680999632665</v>
+        <v>0.08972654181149675</v>
       </c>
       <c r="H456" t="n">
         <v>2765.379504159864</v>
@@ -35906,16 +35906,16 @@
         <v>19.62470390319824</v>
       </c>
       <c r="E461" t="n">
-        <v>20.61371273040772</v>
+        <v>20.61371276855469</v>
       </c>
       <c r="F461" t="n">
-        <v>20.64217185974121</v>
+        <v>20.6421718788147</v>
       </c>
       <c r="G461" t="n">
-        <v>-1.359108432032563</v>
+        <v>-1.359108475746817</v>
       </c>
       <c r="H461" t="n">
-        <v>23.83526024888653</v>
+        <v>23.83526224893035</v>
       </c>
       <c r="I461" t="n">
         <v>18.76000022888184</v>
@@ -35924,7 +35924,7 @@
         <v>4.69082702574708</v>
       </c>
       <c r="K461" t="n">
-        <v>21.36079933612049</v>
+        <v>21.36080951964332</v>
       </c>
       <c r="L461" t="n">
         <v>36.66666666666666</v>
@@ -36060,22 +36060,22 @@
         <v>38156.859609375</v>
       </c>
       <c r="E463" t="n">
-        <v>36543.7383203125</v>
+        <v>36543.73829427084</v>
       </c>
       <c r="F463" t="n">
-        <v>36194.472578125</v>
+        <v>36194.47250976563</v>
       </c>
       <c r="G463" t="n">
-        <v>-1.097501694004765</v>
+        <v>-1.097501907190834</v>
       </c>
       <c r="H463" t="n">
         <v>45150.8475731383</v>
       </c>
       <c r="I463" t="n">
-        <v>29525.27549507192</v>
+        <v>29525.27356749276</v>
       </c>
       <c r="J463" t="n">
-        <v>19.77872994242777</v>
+        <v>19.7787377622701</v>
       </c>
       <c r="K463" t="n">
         <v>27.67099554117998</v>
@@ -36291,13 +36291,13 @@
         <v>905.76228515625</v>
       </c>
       <c r="E466" t="n">
-        <v>968.156815999349</v>
+        <v>968.1568168131511</v>
       </c>
       <c r="F466" t="n">
-        <v>946.9251007080078</v>
+        <v>946.9251034545898</v>
       </c>
       <c r="G466" t="n">
-        <v>0.5072747137508271</v>
+        <v>0.5072746797161187</v>
       </c>
       <c r="H466" t="n">
         <v>1224.72508309492</v>
@@ -36368,22 +36368,22 @@
         <v>238.5343508911133</v>
       </c>
       <c r="E467" t="n">
-        <v>226.7821342976888</v>
+        <v>226.782133992513</v>
       </c>
       <c r="F467" t="n">
-        <v>226.7291128540039</v>
+        <v>226.7291130065918</v>
       </c>
       <c r="G467" t="n">
-        <v>-1.411910019889007</v>
+        <v>-1.411909953539581</v>
       </c>
       <c r="H467" t="n">
         <v>286.0804516993438</v>
       </c>
       <c r="I467" t="n">
-        <v>171.9528178807998</v>
+        <v>171.952833032562</v>
       </c>
       <c r="J467" t="n">
-        <v>23.62693699990319</v>
+        <v>23.62692610641624</v>
       </c>
       <c r="K467" t="n">
         <v>34.57543006641926</v>
@@ -36685,7 +36685,7 @@
         <v>-0.7619443260455383</v>
       </c>
       <c r="H471" t="n">
-        <v>796.6710965617623</v>
+        <v>796.6711586352184</v>
       </c>
       <c r="I471" t="n">
         <v>553.7186859929476</v>
@@ -36694,7 +36694,7 @@
         <v>20.85559493210862</v>
       </c>
       <c r="K471" t="n">
-        <v>19.04827884481495</v>
+        <v>19.04828812058528</v>
       </c>
       <c r="L471" t="n">
         <v>32.5</v>
@@ -37446,13 +37446,13 @@
         <v>300.7577362060547</v>
       </c>
       <c r="E481" t="n">
-        <v>273.6666663614909</v>
+        <v>273.6666665649414</v>
       </c>
       <c r="F481" t="n">
-        <v>289.1837825775146</v>
+        <v>289.1837824249267</v>
       </c>
       <c r="G481" t="n">
-        <v>-2.473801726559632</v>
+        <v>-2.473801627459249</v>
       </c>
       <c r="H481" t="n">
         <v>411.0263372414121</v>
@@ -38527,19 +38527,19 @@
         <v>260.6732721964518</v>
       </c>
       <c r="F495" t="n">
-        <v>254.7806270599365</v>
+        <v>254.7806271362305</v>
       </c>
       <c r="G495" t="n">
-        <v>-0.2343422992972632</v>
+        <v>-0.2343422396177242</v>
       </c>
       <c r="H495" t="n">
         <v>306.197022156633</v>
       </c>
       <c r="I495" t="n">
-        <v>220.307140654885</v>
+        <v>220.3071254131767</v>
       </c>
       <c r="J495" t="n">
-        <v>5.534482136561958</v>
+        <v>5.534489437850021</v>
       </c>
       <c r="K495" t="n">
         <v>31.69764393833676</v>
@@ -38601,13 +38601,13 @@
         <v>1342.618000488281</v>
       </c>
       <c r="E496" t="n">
-        <v>1439.711361490885</v>
+        <v>1439.711363932292</v>
       </c>
       <c r="F496" t="n">
-        <v>1405.491257324219</v>
+        <v>1405.491254882812</v>
       </c>
       <c r="G496" t="n">
-        <v>-0.156757952874087</v>
+        <v>-0.1567580397263013</v>
       </c>
       <c r="H496" t="n">
         <v>1817.803954384172</v>
@@ -39066,19 +39066,19 @@
         <v>406.7520330810547</v>
       </c>
       <c r="F502" t="n">
-        <v>392.559633026123</v>
+        <v>392.5596336364746</v>
       </c>
       <c r="G502" t="n">
-        <v>-0.1889086820711428</v>
+        <v>-0.1889085268849011</v>
       </c>
       <c r="H502" t="n">
         <v>476.8288845013619</v>
       </c>
       <c r="I502" t="n">
-        <v>317.6634042148347</v>
+        <v>317.6633741663369</v>
       </c>
       <c r="J502" t="n">
-        <v>11.26557466720157</v>
+        <v>11.2655851920642</v>
       </c>
       <c r="K502" t="n">
         <v>34.90702165319553</v>
@@ -39451,10 +39451,10 @@
         <v>2445.858313802084</v>
       </c>
       <c r="F507" t="n">
-        <v>2453.707322998047</v>
+        <v>2453.707316894531</v>
       </c>
       <c r="G507" t="n">
-        <v>-0.9390714178847293</v>
+        <v>-0.9390715666567906</v>
       </c>
       <c r="H507" t="n">
         <v>3039.742428602358</v>
@@ -39605,13 +39605,13 @@
         <v>211.5760208129883</v>
       </c>
       <c r="F509" t="n">
-        <v>215.6173415374756</v>
+        <v>215.6173418426514</v>
       </c>
       <c r="G509" t="n">
-        <v>-1.2442409978764</v>
+        <v>-1.244240961628351</v>
       </c>
       <c r="H509" t="n">
-        <v>272.0997840702363</v>
+        <v>272.099752952214</v>
       </c>
       <c r="I509" t="n">
         <v>173.9540675101702</v>
@@ -39620,7 +39620,7 @@
         <v>20.23288497364768</v>
       </c>
       <c r="K509" t="n">
-        <v>30.09791633314986</v>
+        <v>30.09790145482176</v>
       </c>
       <c r="L509" t="n">
         <v>32.77777777777778</v>
@@ -39679,16 +39679,16 @@
         <v>711.817275390625</v>
       </c>
       <c r="E510" t="n">
-        <v>739.6160351562499</v>
+        <v>739.6160359700521</v>
       </c>
       <c r="F510" t="n">
-        <v>761.8982751464844</v>
+        <v>761.8982760620117</v>
       </c>
       <c r="G510" t="n">
-        <v>-3.954038722355002</v>
+        <v>-3.954038680841809</v>
       </c>
       <c r="H510" t="n">
-        <v>1117.559425954049</v>
+        <v>1117.559301306357</v>
       </c>
       <c r="I510" t="n">
         <v>612.1496526863262</v>
@@ -39697,7 +39697,7 @@
         <v>17.97768879517707</v>
       </c>
       <c r="K510" t="n">
-        <v>54.74375617064948</v>
+        <v>54.74373891120745</v>
       </c>
       <c r="L510" t="n">
         <v>32.63888888888889</v>
@@ -39756,16 +39756,16 @@
         <v>434.2975555419922</v>
       </c>
       <c r="E511" t="n">
-        <v>425.6674149576823</v>
+        <v>425.6674151611328</v>
       </c>
       <c r="F511" t="n">
-        <v>444.9950192260742</v>
+        <v>444.9950204467773</v>
       </c>
       <c r="G511" t="n">
-        <v>-1.851809553357686</v>
+        <v>-1.851809647466673</v>
       </c>
       <c r="H511" t="n">
-        <v>533.7088183031568</v>
+        <v>533.7087547028075</v>
       </c>
       <c r="I511" t="n">
         <v>363.2227809620478</v>
@@ -39774,7 +39774,7 @@
         <v>14.98452624317181</v>
       </c>
       <c r="K511" t="n">
-        <v>27.78853731659288</v>
+        <v>27.78852208844724</v>
       </c>
       <c r="L511" t="n">
         <v>32.36111111111111</v>
@@ -39910,13 +39910,13 @@
         <v>341.3380230712891</v>
       </c>
       <c r="E513" t="n">
-        <v>341.7155631510417</v>
+        <v>341.7155609130859</v>
       </c>
       <c r="F513" t="n">
-        <v>343.0791802978516</v>
+        <v>343.0791777038574</v>
       </c>
       <c r="G513" t="n">
-        <v>-0.8730202810524612</v>
+        <v>-0.8730202001900556</v>
       </c>
       <c r="H513" t="n">
         <v>381.3442016302781</v>
@@ -40147,7 +40147,7 @@
         <v>580.7664199829102</v>
       </c>
       <c r="G516" t="n">
-        <v>-0.002444009938962211</v>
+        <v>-0.002444167572479561</v>
       </c>
       <c r="H516" t="n">
         <v>732.5560380476754</v>
@@ -40221,10 +40221,10 @@
         <v>2010.541654459635</v>
       </c>
       <c r="F517" t="n">
-        <v>2081.286514282227</v>
+        <v>2081.286513061523</v>
       </c>
       <c r="G517" t="n">
-        <v>-1.20087137035757</v>
+        <v>-1.200871542806969</v>
       </c>
       <c r="H517" t="n">
         <v>2486.766809421043</v>
@@ -40609,7 +40609,7 @@
         <v>3548.134403076172</v>
       </c>
       <c r="G522" t="n">
-        <v>-0.5441753380015402</v>
+        <v>-0.5441754060628745</v>
       </c>
       <c r="H522" t="n">
         <v>4586.205351504792</v>
@@ -40757,13 +40757,13 @@
         <v>1279.910549316406</v>
       </c>
       <c r="E524" t="n">
-        <v>1260.421268310547</v>
+        <v>1260.421276448568</v>
       </c>
       <c r="F524" t="n">
-        <v>1346.872137756348</v>
+        <v>1346.872145690918</v>
       </c>
       <c r="G524" t="n">
-        <v>-1.743534610643105</v>
+        <v>-1.743534731800211</v>
       </c>
       <c r="H524" t="n">
         <v>1729.008500794829</v>
@@ -43230,7 +43230,7 @@
         <v>-2.598127384172166</v>
       </c>
       <c r="H556" t="n">
-        <v>3859.801118967803</v>
+        <v>3859.800859322344</v>
       </c>
       <c r="I556" t="n">
         <v>2401.113876815865</v>
@@ -43239,7 +43239,7 @@
         <v>9.32426093347274</v>
       </c>
       <c r="K556" t="n">
-        <v>47.04004262734487</v>
+        <v>47.04003273608927</v>
       </c>
       <c r="L556" t="n">
         <v>15.13888888888889</v>
@@ -43538,7 +43538,7 @@
         <v>-2.761912463228844</v>
       </c>
       <c r="H560" t="n">
-        <v>1486.026544311489</v>
+        <v>1486.026668543064</v>
       </c>
       <c r="I560" t="n">
         <v>863.7720549794727</v>
@@ -43547,7 +43547,7 @@
         <v>12.54705669277125</v>
       </c>
       <c r="K560" t="n">
-        <v>52.8597960183308</v>
+        <v>52.85980879738461</v>
       </c>
       <c r="L560" t="n">
         <v>13.75</v>
@@ -43834,28 +43834,28 @@
         <v>493.5499877929688</v>
       </c>
       <c r="D564" t="n">
-        <v>528.5924688720703</v>
+        <v>528.5924725341797</v>
       </c>
       <c r="E564" t="n">
-        <v>512.7890637207031</v>
+        <v>512.7890651448567</v>
       </c>
       <c r="F564" t="n">
-        <v>547.5376293945312</v>
+        <v>547.5376295471192</v>
       </c>
       <c r="G564" t="n">
-        <v>-3.526872705255546</v>
+        <v>-3.526872548685667</v>
       </c>
       <c r="H564" t="n">
-        <v>872.0426229622601</v>
+        <v>872.0425606177564</v>
       </c>
       <c r="I564" t="n">
-        <v>406.1171468902937</v>
+        <v>406.117116732523</v>
       </c>
       <c r="J564" t="n">
-        <v>21.52897053772853</v>
+        <v>21.52897956232433</v>
       </c>
       <c r="K564" t="n">
-        <v>76.68780154606327</v>
+        <v>76.68778891421132</v>
       </c>
       <c r="L564" t="n">
         <v>11.38888888888889</v>
@@ -43997,7 +43997,7 @@
         <v>392.4845338439941</v>
       </c>
       <c r="G566" t="n">
-        <v>-2.971196872078119</v>
+        <v>-2.971196725672132</v>
       </c>
       <c r="H566" t="n">
         <v>574.7140242073417</v>
@@ -44536,7 +44536,7 @@
         <v>324.9440606689453</v>
       </c>
       <c r="G573" t="n">
-        <v>-1.264636204831637</v>
+        <v>-1.264636296387656</v>
       </c>
       <c r="H573" t="n">
         <v>391.6499938964844</v>
@@ -44610,10 +44610,10 @@
         <v>144.5362440999349</v>
       </c>
       <c r="F574" t="n">
-        <v>147.9464302062988</v>
+        <v>147.9464297485352</v>
       </c>
       <c r="G574" t="n">
-        <v>-1.583224155409146</v>
+        <v>-1.583224360024915</v>
       </c>
       <c r="H574" t="n">
         <v>184.9587904135824</v>
@@ -44841,10 +44841,10 @@
         <v>132474.8955729167</v>
       </c>
       <c r="F577" t="n">
-        <v>136182.188203125</v>
+        <v>136182.18796875</v>
       </c>
       <c r="G577" t="n">
-        <v>-1.985175129331251</v>
+        <v>-1.985175298018704</v>
       </c>
       <c r="H577" t="n">
         <v>163308.4863287346</v>
@@ -46301,13 +46301,13 @@
         <v>482.4010290527344</v>
       </c>
       <c r="E596" t="n">
-        <v>533.6281469726563</v>
+        <v>533.6281477864584</v>
       </c>
       <c r="F596" t="n">
-        <v>537.3891613769531</v>
+        <v>537.3891604614258</v>
       </c>
       <c r="G596" t="n">
-        <v>-1.523104604707326</v>
+        <v>-1.523105102909528</v>
       </c>
       <c r="H596" t="n">
         <v>653.9340000086492</v>
@@ -46458,10 +46458,10 @@
         <v>3058.431098632812</v>
       </c>
       <c r="F598" t="n">
-        <v>3200.081337890625</v>
+        <v>3200.081343994141</v>
       </c>
       <c r="G598" t="n">
-        <v>-1.891928957432043</v>
+        <v>-1.89192884374304</v>
       </c>
       <c r="H598" t="n">
         <v>3923.39201752828</v>
@@ -46846,10 +46846,10 @@
         <v>1102.225216369629</v>
       </c>
       <c r="G603" t="n">
-        <v>-1.987856344786876</v>
+        <v>-1.987856397981702</v>
       </c>
       <c r="H603" t="n">
-        <v>1400.476774401248</v>
+        <v>1400.476649260813</v>
       </c>
       <c r="I603" t="n">
         <v>941.5197177909594</v>
@@ -46858,7 +46858,7 @@
         <v>6.211264735511857</v>
       </c>
       <c r="K603" t="n">
-        <v>40.04767744012483</v>
+        <v>40.04766492608125</v>
       </c>
       <c r="L603" t="n">
         <v>23.61111111111111</v>
@@ -46991,28 +46991,28 @@
         <v>172.7599945068359</v>
       </c>
       <c r="D605" t="n">
-        <v>191.9940634155273</v>
+        <v>191.9940640258789</v>
       </c>
       <c r="E605" t="n">
-        <v>193.6329964192708</v>
+        <v>193.6329960123698</v>
       </c>
       <c r="F605" t="n">
-        <v>197.4191024017334</v>
+        <v>197.4191023254394</v>
       </c>
       <c r="G605" t="n">
-        <v>-2.340041734823051</v>
+        <v>-2.340041809422588</v>
       </c>
       <c r="H605" t="n">
-        <v>239.2186728978909</v>
+        <v>239.2187037807859</v>
       </c>
       <c r="I605" t="n">
-        <v>156.7443123050878</v>
+        <v>156.7442971017576</v>
       </c>
       <c r="J605" t="n">
-        <v>10.21771186859726</v>
+        <v>10.21772255910594</v>
       </c>
       <c r="K605" t="n">
-        <v>38.46878936339935</v>
+        <v>38.46880723958363</v>
       </c>
       <c r="L605" t="n">
         <v>23.19444444444445</v>
@@ -47231,7 +47231,7 @@
         <v>1904.033421020508</v>
       </c>
       <c r="G608" t="n">
-        <v>-1.326595208340176</v>
+        <v>-1.326595270761888</v>
       </c>
       <c r="H608" t="n">
         <v>2484.339731207416</v>
@@ -47305,10 +47305,10 @@
         <v>7781.855380859375</v>
       </c>
       <c r="F609" t="n">
-        <v>7839.586875</v>
+        <v>7839.586865234375</v>
       </c>
       <c r="G609" t="n">
-        <v>-1.336765209043311</v>
+        <v>-1.336765150056229</v>
       </c>
       <c r="H609" t="n">
         <v>10255.65092965882</v>
@@ -47764,16 +47764,16 @@
         <v>117.7908987426758</v>
       </c>
       <c r="E615" t="n">
-        <v>122.0843817138672</v>
+        <v>122.0843815612793</v>
       </c>
       <c r="F615" t="n">
-        <v>125.1413471984863</v>
+        <v>125.1413470077515</v>
       </c>
       <c r="G615" t="n">
-        <v>-2.823724603322753</v>
+        <v>-2.82372466507681</v>
       </c>
       <c r="H615" t="n">
-        <v>161.4130431297806</v>
+        <v>161.4130274594467</v>
       </c>
       <c r="I615" t="n">
         <v>107.3616553935714</v>
@@ -47782,7 +47782,7 @@
         <v>4.050183163589316</v>
       </c>
       <c r="K615" t="n">
-        <v>44.49292315160045</v>
+        <v>44.49290912390899</v>
       </c>
       <c r="L615" t="n">
         <v>20.13888888888889</v>
@@ -49079,7 +49079,7 @@
         <v>2200.836365966797</v>
       </c>
       <c r="G632" t="n">
-        <v>-1.984191191530749</v>
+        <v>-1.984191457961626</v>
       </c>
       <c r="H632" t="n">
         <v>2619.749708059458</v>
@@ -49381,16 +49381,16 @@
         <v>91.70302947998047</v>
       </c>
       <c r="E636" t="n">
-        <v>93.59483790079753</v>
+        <v>93.59483810424804</v>
       </c>
       <c r="F636" t="n">
-        <v>97.34520011901856</v>
+        <v>97.34520015716552</v>
       </c>
       <c r="G636" t="n">
-        <v>-2.89382119993663</v>
+        <v>-2.893821235787553</v>
       </c>
       <c r="H636" t="n">
-        <v>124.8273096544699</v>
+        <v>124.8273017901132</v>
       </c>
       <c r="I636" t="n">
         <v>76.65010804466255</v>
@@ -49399,7 +49399,7 @@
         <v>8.153796048890971</v>
       </c>
       <c r="K636" t="n">
-        <v>50.57576279477218</v>
+        <v>50.57575330821413</v>
       </c>
       <c r="L636" t="n">
         <v>14.58333333333333</v>
@@ -49692,13 +49692,13 @@
         <v>1246.893626302083</v>
       </c>
       <c r="F640" t="n">
-        <v>1282.838676147461</v>
+        <v>1282.838677368164</v>
       </c>
       <c r="G640" t="n">
-        <v>-1.90601480613215</v>
+        <v>-1.906014667007649</v>
       </c>
       <c r="H640" t="n">
-        <v>1608.140938678776</v>
+        <v>1608.140814494163</v>
       </c>
       <c r="I640" t="n">
         <v>1096.199951171875</v>
@@ -49707,7 +49707,7 @@
         <v>1.350123105944601</v>
       </c>
       <c r="K640" t="n">
-        <v>44.74715919700951</v>
+        <v>44.74714801927657</v>
       </c>
       <c r="L640" t="n">
         <v>13.61111111111111</v>
@@ -49772,7 +49772,7 @@
         <v>1739.980589599609</v>
       </c>
       <c r="G641" t="n">
-        <v>-4.036565949634308</v>
+        <v>-4.036566111150941</v>
       </c>
       <c r="H641" t="n">
         <v>2504.019782423858</v>
@@ -50003,10 +50003,10 @@
         <v>311.2939810943603</v>
       </c>
       <c r="G644" t="n">
-        <v>-2.675343997180257</v>
+        <v>-2.675344043609884</v>
       </c>
       <c r="H644" t="n">
-        <v>408.5542426067486</v>
+        <v>408.554305468849</v>
       </c>
       <c r="I644" t="n">
         <v>243.9284560598348</v>
@@ -50015,7 +50015,7 @@
         <v>6.547632078125321</v>
       </c>
       <c r="K644" t="n">
-        <v>57.19671112015177</v>
+        <v>57.19673530718596</v>
       </c>
       <c r="L644" t="n">
         <v>12.77777777777778</v>
@@ -50080,7 +50080,7 @@
         <v>301.0580475616455</v>
       </c>
       <c r="G645" t="n">
-        <v>-3.298790831064236</v>
+        <v>-3.298790736273993</v>
       </c>
       <c r="H645" t="n">
         <v>398.6210131186603</v>
@@ -50773,7 +50773,7 @@
         <v>451.5902569580078</v>
       </c>
       <c r="G654" t="n">
-        <v>-2.790567191803683</v>
+        <v>-2.790567319521753</v>
       </c>
       <c r="H654" t="n">
         <v>538.5337830249387</v>
@@ -51235,7 +51235,7 @@
         <v>1072.215469360352</v>
       </c>
       <c r="G660" t="n">
-        <v>-2.102908797700664</v>
+        <v>-2.102908743145271</v>
       </c>
       <c r="H660" t="n">
         <v>1255.178432949836</v>
@@ -53160,7 +53160,7 @@
         <v>442.0350219726562</v>
       </c>
       <c r="G685" t="n">
-        <v>-3.177441598701747</v>
+        <v>-3.177441695783523</v>
       </c>
       <c r="H685" t="n">
         <v>602.0840578111723</v>
@@ -54614,16 +54614,16 @@
         <v>410.3500061035156</v>
       </c>
       <c r="D704" t="n">
-        <v>468.8275451660156</v>
+        <v>468.8275463867187</v>
       </c>
       <c r="E704" t="n">
-        <v>504.5648966471354</v>
+        <v>504.5649005126953</v>
       </c>
       <c r="F704" t="n">
-        <v>513.8932041931153</v>
+        <v>513.8932070922851</v>
       </c>
       <c r="G704" t="n">
-        <v>-4.560797302434693</v>
+        <v>-4.560797277878081</v>
       </c>
       <c r="H704" t="n">
         <v>814.1878618458627</v>
@@ -54925,13 +54925,13 @@
         <v>355.488359375</v>
       </c>
       <c r="E708" t="n">
-        <v>426.6048728434245</v>
+        <v>426.6048714192708</v>
       </c>
       <c r="F708" t="n">
         <v>453.1180693054199</v>
       </c>
       <c r="G708" t="n">
-        <v>-5.319656303628806</v>
+        <v>-5.319656364003977</v>
       </c>
       <c r="H708" t="n">
         <v>606.7970321970149</v>
@@ -55393,7 +55393,7 @@
         <v>401.4955911254883</v>
       </c>
       <c r="G714" t="n">
-        <v>-4.772801303014118</v>
+        <v>-4.77280123408681</v>
       </c>
       <c r="H714" t="n">
         <v>541.6977805031639</v>
@@ -55775,10 +55775,10 @@
         <v>683.9870397949219</v>
       </c>
       <c r="F719" t="n">
-        <v>800.392173461914</v>
+        <v>800.392176208496</v>
       </c>
       <c r="G719" t="n">
-        <v>-7.543116415850893</v>
+        <v>-7.543116457105059</v>
       </c>
       <c r="H719" t="n">
         <v>1313.886868193049</v>
